--- a/research/traditional_assets/database/data/netherlands/netherlands_software_system_application.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_software_system_application.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,34 +588,37 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.282</v>
+        <v>-0.116</v>
+      </c>
+      <c r="E2">
+        <v>-0.48</v>
       </c>
       <c r="G2">
-        <v>-0.03488927527370694</v>
+        <v>0.4031145723194059</v>
       </c>
       <c r="H2">
-        <v>-0.04891377037277643</v>
+        <v>-0.08279683030706561</v>
       </c>
       <c r="I2">
-        <v>-0.07285858952557464</v>
+        <v>-0.1757343083328718</v>
       </c>
       <c r="J2">
-        <v>-0.07285858952557464</v>
+        <v>-0.1757343083328718</v>
       </c>
       <c r="K2">
-        <v>-24.3</v>
+        <v>-166.093</v>
       </c>
       <c r="L2">
-        <v>-0.09285973594206776</v>
+        <v>-0.2139053342073642</v>
       </c>
       <c r="M2">
-        <v>0.499</v>
+        <v>3.75</v>
       </c>
       <c r="N2">
-        <v>0.0003923850563414615</v>
+        <v>0.002979785137626343</v>
       </c>
       <c r="O2">
-        <v>-0.02053497942386831</v>
+        <v>-0.02257771248637811</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,79 +630,73 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0.499</v>
+        <v>3.75</v>
       </c>
       <c r="T2">
         <v>1</v>
       </c>
       <c r="U2">
-        <v>77.066</v>
+        <v>213.603</v>
       </c>
       <c r="V2">
-        <v>0.06060029409220655</v>
+        <v>0.1697309452673066</v>
       </c>
       <c r="W2">
-        <v>-0.1213592233009709</v>
+        <v>-0.3315076836581709</v>
       </c>
       <c r="X2">
-        <v>0.06387264093579843</v>
+        <v>0.1177104864933</v>
       </c>
       <c r="Y2">
-        <v>-0.1852318642367693</v>
+        <v>-0.4492181701514709</v>
       </c>
       <c r="Z2">
-        <v>4.449971091385232</v>
-      </c>
-      <c r="AA2">
-        <v>-0.1535910637926521</v>
+        <v>15.42775680508643</v>
       </c>
       <c r="AB2">
-        <v>0.06303612851033388</v>
-      </c>
-      <c r="AC2">
-        <v>-0.2138984626119346</v>
+        <v>0.1165670751374978</v>
       </c>
       <c r="AD2">
-        <v>52.55399999999999</v>
+        <v>148.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>52.55399999999999</v>
+        <v>148.8</v>
       </c>
       <c r="AG2">
-        <v>-24.51200000000001</v>
+        <v>-64.803</v>
       </c>
       <c r="AH2">
-        <v>0.03968544036536521</v>
+        <v>0.1057358876698312</v>
       </c>
       <c r="AI2">
-        <v>0.2703617581693966</v>
+        <v>0.3295170184024626</v>
       </c>
       <c r="AJ2">
-        <v>-0.01965365563447023</v>
+        <v>-0.05428855544674144</v>
       </c>
       <c r="AK2">
-        <v>-0.2089363950970866</v>
+        <v>-0.2723192711594465</v>
       </c>
       <c r="AL2">
-        <v>2.782</v>
+        <v>7.417999999999999</v>
       </c>
       <c r="AM2">
-        <v>2.657</v>
+        <v>7.033999999999999</v>
       </c>
       <c r="AN2">
-        <v>-6.859044635865309</v>
+        <v>-1.631704187821434</v>
       </c>
       <c r="AO2">
-        <v>-6.853342918763479</v>
+        <v>-18.39498517120518</v>
       </c>
       <c r="AP2">
-        <v>3.199164708953277</v>
+        <v>0.7106137532486045</v>
       </c>
       <c r="AQ2">
-        <v>-7.175762137749341</v>
+        <v>-19.39920386693205</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tymlez Group Limited (ASX:TYM)</t>
+          <t>MKB Nedsense NV (ENXTAM:NEDSE)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -718,23 +715,26 @@
           <t>Software (System &amp; Application)</t>
         </is>
       </c>
+      <c r="E3">
+        <v>-0.48</v>
+      </c>
       <c r="G3">
-        <v>-9.127272727272725</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>-9.127272727272725</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>-8.290909090909089</v>
+        <v>0.2796610169491526</v>
       </c>
       <c r="J3">
-        <v>-8.290909090909089</v>
+        <v>0.2796610169491526</v>
       </c>
       <c r="K3">
-        <v>-2.56</v>
+        <v>0.14</v>
       </c>
       <c r="L3">
-        <v>-9.309090909090909</v>
+        <v>0.5932203389830509</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +743,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,73 +752,70 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>4.29</v>
+        <v>0.049</v>
       </c>
       <c r="V3">
-        <v>0.1810126582278481</v>
+        <v>0.0035</v>
       </c>
       <c r="W3">
-        <v>12.2488038277512</v>
+        <v>0.01907356948228883</v>
       </c>
       <c r="X3">
-        <v>0.06387264093579843</v>
+        <v>0.1168334971930334</v>
       </c>
       <c r="Y3">
-        <v>12.1849311868154</v>
+        <v>-0.0977599277107446</v>
       </c>
       <c r="Z3">
-        <v>-1.797385620915033</v>
+        <v>0.0509719222462203</v>
       </c>
       <c r="AA3">
-        <v>14.90196078431372</v>
+        <v>0.0142548596112311</v>
       </c>
       <c r="AB3">
-        <v>0.06314409905281256</v>
+        <v>0.1168334971930334</v>
       </c>
       <c r="AC3">
-        <v>14.83881668526091</v>
+        <v>-0.1025786375818023</v>
       </c>
       <c r="AD3">
-        <v>0.484</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.484</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-3.806</v>
+        <v>-0.049</v>
       </c>
       <c r="AH3">
-        <v>0.02001323188885213</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.1236586612161472</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.191313964009249</v>
+        <v>-0.003512293025589564</v>
       </c>
       <c r="AK3">
-        <v>10.12234042553192</v>
+        <v>-0.004875136802308228</v>
       </c>
       <c r="AL3">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.027</v>
-      </c>
-      <c r="AO3">
-        <v>-84.44444444444444</v>
+        <v>-0.075</v>
       </c>
       <c r="AQ3">
-        <v>-84.44444444444444</v>
+        <v>-0.8800000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -829,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MKB Nedsense NV (ENXTAM:NEDSE)</t>
+          <t>CM.com N.V. (ENXTAM:CMCOM)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,31 +835,31 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>-0.06085043988269795</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>-0.06085043988269795</v>
       </c>
       <c r="I4">
-        <v>-5.266666666666667</v>
+        <v>-0.125733137829912</v>
       </c>
       <c r="J4">
-        <v>-5.266666666666667</v>
+        <v>-0.125733137829912</v>
       </c>
       <c r="K4">
-        <v>-0.42</v>
+        <v>-35.9</v>
       </c>
       <c r="L4">
-        <v>-7</v>
+        <v>-0.1315982404692082</v>
       </c>
       <c r="M4">
-        <v>0.499</v>
+        <v>3.75</v>
       </c>
       <c r="N4">
-        <v>0.04056910569105691</v>
+        <v>0.01070205479452055</v>
       </c>
       <c r="O4">
-        <v>-1.188095238095238</v>
+        <v>-0.1044568245125348</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -874,73 +871,79 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>0.499</v>
+        <v>3.75</v>
       </c>
       <c r="T4">
         <v>1</v>
       </c>
       <c r="U4">
-        <v>0.095</v>
+        <v>101.4</v>
       </c>
       <c r="V4">
-        <v>0.007723577235772357</v>
+        <v>0.2893835616438357</v>
       </c>
       <c r="W4">
-        <v>-0.05526315789473684</v>
+        <v>-0.3094827586206896</v>
       </c>
       <c r="X4">
-        <v>0.06313688609809345</v>
+        <v>0.136976517211328</v>
       </c>
       <c r="Y4">
-        <v>-0.1184000439928303</v>
+        <v>-0.4464592758320177</v>
       </c>
       <c r="Z4">
-        <v>0.01234567901234568</v>
+        <v>5.969365426695844</v>
       </c>
       <c r="AA4">
-        <v>-0.06502057613168725</v>
+        <v>-0.7505470459518601</v>
       </c>
       <c r="AB4">
-        <v>0.06313688609809345</v>
+        <v>0.1121560673954041</v>
       </c>
       <c r="AC4">
-        <v>-0.1281574622297807</v>
+        <v>-0.8627031133472641</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>121.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>121.9</v>
       </c>
       <c r="AG4">
-        <v>-0.095</v>
+        <v>20.5</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.2580986661020538</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>0.603166749134092</v>
       </c>
       <c r="AJ4">
-        <v>-0.007783695206882425</v>
+        <v>0.05527096252359127</v>
       </c>
       <c r="AK4">
-        <v>-0.01282916948008103</v>
+        <v>0.2035749751737835</v>
       </c>
       <c r="AL4">
-        <v>0.137</v>
+        <v>4.6</v>
       </c>
       <c r="AM4">
-        <v>0.08200000000000002</v>
+        <v>4.290999999999999</v>
+      </c>
+      <c r="AN4">
+        <v>-4.481617647058824</v>
       </c>
       <c r="AO4">
-        <v>-2.306569343065693</v>
+        <v>-7.456521739130435</v>
+      </c>
+      <c r="AP4">
+        <v>-0.7536764705882353</v>
       </c>
       <c r="AQ4">
-        <v>-3.853658536585365</v>
+        <v>-7.993474714518761</v>
       </c>
     </row>
     <row r="5">
@@ -951,7 +954,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GeoJunxion N.V. (ENXTAM:GOJXN)</t>
+          <t>TomTom N.V. (ENXTAM:TOM2)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -960,25 +963,25 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.282</v>
+        <v>-0.116</v>
       </c>
       <c r="G5">
-        <v>-0.9025641025641026</v>
+        <v>0.6583084577114429</v>
       </c>
       <c r="H5">
-        <v>-0.9025641025641026</v>
+        <v>-0.09253731343283582</v>
       </c>
       <c r="I5">
-        <v>-0.9025641025641026</v>
+        <v>-0.1998009950248756</v>
       </c>
       <c r="J5">
-        <v>-0.9025641025641026</v>
+        <v>-0.1998009950248756</v>
       </c>
       <c r="K5">
-        <v>-1.25</v>
+        <v>-130.1</v>
       </c>
       <c r="L5">
-        <v>-0.6410256410256411</v>
+        <v>-0.2589054726368159</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1002,73 +1005,64 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.881</v>
+        <v>111.6</v>
       </c>
       <c r="V5">
-        <v>0.1490693739424704</v>
+        <v>0.1256756756756757</v>
       </c>
       <c r="W5">
-        <v>-0.1213592233009709</v>
+        <v>-0.3535326086956522</v>
       </c>
       <c r="X5">
-        <v>0.07819413339026235</v>
+        <v>0.1185874757935667</v>
       </c>
       <c r="Y5">
-        <v>-0.1995533566912332</v>
-      </c>
-      <c r="Z5">
-        <v>0.1701719172702679</v>
-      </c>
-      <c r="AA5">
-        <v>-0.1535910637926521</v>
+        <v>-0.4721200844892188</v>
       </c>
       <c r="AB5">
-        <v>0.06030739881928258</v>
-      </c>
-      <c r="AC5">
-        <v>-0.2138984626119346</v>
+        <v>0.1163006530819622</v>
       </c>
       <c r="AD5">
-        <v>2.47</v>
+        <v>26.9</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>2.47</v>
+        <v>26.9</v>
       </c>
       <c r="AG5">
-        <v>1.589</v>
+        <v>-84.69999999999999</v>
       </c>
       <c r="AH5">
-        <v>0.2947494033412888</v>
+        <v>0.02940212045032244</v>
       </c>
       <c r="AI5">
-        <v>0.2011400651465798</v>
+        <v>0.1162991785559879</v>
       </c>
       <c r="AJ5">
-        <v>0.2118949193225763</v>
+        <v>-0.1054400597535167</v>
       </c>
       <c r="AK5">
-        <v>0.1393981928239319</v>
+        <v>-0.7076023391812863</v>
       </c>
       <c r="AL5">
-        <v>0.18</v>
+        <v>2.48</v>
       </c>
       <c r="AM5">
-        <v>0.18</v>
+        <v>2.48</v>
       </c>
       <c r="AN5">
-        <v>-3.004866180048662</v>
+        <v>-0.426984126984127</v>
       </c>
       <c r="AO5">
-        <v>-9.777777777777779</v>
+        <v>-40.48387096774194</v>
       </c>
       <c r="AP5">
-        <v>-1.933090024330901</v>
+        <v>1.344444444444444</v>
       </c>
       <c r="AQ5">
-        <v>-9.777777777777779</v>
+        <v>-40.48387096774194</v>
       </c>
     </row>
     <row r="6">
@@ -1079,7 +1073,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CM.com N.V. (ENXTAM:CMCOM)</t>
+          <t>GeoJunxion N.V. (ENXTAM:GOJXN)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1088,22 +1082,22 @@
         </is>
       </c>
       <c r="G6">
-        <v>-0.02510766580534023</v>
+        <v>-1.261930010604454</v>
       </c>
       <c r="H6">
-        <v>-0.02510766580534023</v>
+        <v>-1.261930010604454</v>
       </c>
       <c r="I6">
-        <v>-0.04250645994832041</v>
+        <v>-1.930010604453871</v>
       </c>
       <c r="J6">
-        <v>-0.04250645994832041</v>
+        <v>-1.930010604453871</v>
       </c>
       <c r="K6">
-        <v>-14.7</v>
+        <v>-0.233</v>
       </c>
       <c r="L6">
-        <v>-0.06330749354005168</v>
+        <v>-0.247083775185578</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1127,183 +1121,58 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>59.8</v>
+        <v>0.554</v>
       </c>
       <c r="V6">
-        <v>0.06567819879187259</v>
-      </c>
-      <c r="W6">
-        <v>-0.1872611464968153</v>
+        <v>0.09111842105263158</v>
       </c>
       <c r="X6">
-        <v>0.06373833640179281</v>
-      </c>
-      <c r="Y6">
-        <v>-0.2509994828986081</v>
-      </c>
-      <c r="Z6">
-        <v>5.445590994371481</v>
-      </c>
-      <c r="AA6">
-        <v>-0.2314727954971857</v>
+        <v>0.1168334971930334</v>
       </c>
       <c r="AB6">
-        <v>0.06303612851033388</v>
-      </c>
-      <c r="AC6">
-        <v>-0.2945089240075196</v>
+        <v>0.1168334971930334</v>
       </c>
       <c r="AD6">
-        <v>15.2</v>
+        <v>0</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>15.2</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>-44.59999999999999</v>
+        <v>-0.554</v>
       </c>
       <c r="AH6">
-        <v>0.0164200064815815</v>
+        <v>0</v>
       </c>
       <c r="AI6">
-        <v>0.1158536585365854</v>
+        <v>0</v>
       </c>
       <c r="AJ6">
-        <v>-0.05150710243677099</v>
+        <v>-0.1002533478103511</v>
       </c>
       <c r="AK6">
-        <v>-0.6246498599439775</v>
+        <v>-0.07370941990420438</v>
       </c>
       <c r="AL6">
-        <v>0.168</v>
+        <v>0.338</v>
       </c>
       <c r="AM6">
-        <v>0.113</v>
+        <v>0.338</v>
       </c>
       <c r="AN6">
-        <v>-5.241379310344827</v>
+        <v>-0</v>
       </c>
       <c r="AO6">
-        <v>-58.74999999999999</v>
+        <v>-5.384615384615384</v>
       </c>
       <c r="AP6">
-        <v>15.37931034482759</v>
+        <v>0.5579053373615308</v>
       </c>
       <c r="AQ6">
-        <v>-87.34513274336281</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>MotorK Ltd. (ENXTAM:MTRK)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Software (System &amp; Application)</t>
-        </is>
-      </c>
-      <c r="G7">
-        <v>0.03566176470588234</v>
-      </c>
-      <c r="H7">
-        <v>-0.09926470588235295</v>
-      </c>
-      <c r="I7">
-        <v>-0.1779411764705882</v>
-      </c>
-      <c r="J7">
-        <v>-0.1779411764705882</v>
-      </c>
-      <c r="K7">
-        <v>-5.37</v>
-      </c>
-      <c r="L7">
-        <v>-0.1974264705882353</v>
-      </c>
-      <c r="M7">
-        <v>-0</v>
-      </c>
-      <c r="N7">
-        <v>-0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>-0</v>
-      </c>
-      <c r="Q7">
-        <v>-0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>12</v>
-      </c>
-      <c r="V7">
-        <v>0.03758221108675227</v>
-      </c>
-      <c r="X7">
-        <v>0.06701835074366443</v>
-      </c>
-      <c r="AB7">
-        <v>0.06276232504936426</v>
-      </c>
-      <c r="AD7">
-        <v>34.4</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>34.4</v>
-      </c>
-      <c r="AG7">
-        <v>22.4</v>
-      </c>
-      <c r="AH7">
-        <v>0.09725756290641786</v>
-      </c>
-      <c r="AI7">
-        <v>0.8711066092681692</v>
-      </c>
-      <c r="AJ7">
-        <v>0.06555458004097162</v>
-      </c>
-      <c r="AK7">
-        <v>0.8148417606402328</v>
-      </c>
-      <c r="AL7">
-        <v>2.27</v>
-      </c>
-      <c r="AM7">
-        <v>2.255</v>
-      </c>
-      <c r="AN7">
-        <v>-8.730964467005077</v>
-      </c>
-      <c r="AO7">
-        <v>-2.13215859030837</v>
-      </c>
-      <c r="AP7">
-        <v>-5.685279187817258</v>
-      </c>
-      <c r="AQ7">
-        <v>-2.146341463414634</v>
+        <v>-5.384615384615384</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/netherlands/netherlands_software_system_application.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_software_system_application.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,37 +588,37 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.116</v>
-      </c>
-      <c r="E2">
-        <v>-0.48</v>
+        <v>0.19745</v>
+      </c>
+      <c r="F2">
+        <v>0.18</v>
       </c>
       <c r="G2">
-        <v>0.4031145723194059</v>
+        <v>0.2074406603262303</v>
       </c>
       <c r="H2">
-        <v>-0.08279683030706561</v>
+        <v>-0.127374666071951</v>
       </c>
       <c r="I2">
-        <v>-0.1757343083328718</v>
+        <v>-0.1010950273754958</v>
       </c>
       <c r="J2">
-        <v>-0.1757343083328718</v>
+        <v>-0.1010950273754958</v>
       </c>
       <c r="K2">
-        <v>-166.093</v>
+        <v>-257.492</v>
       </c>
       <c r="L2">
-        <v>-0.2139053342073642</v>
+        <v>-0.1234955851954169</v>
       </c>
       <c r="M2">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.002979785137626343</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.02257771248637811</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -630,73 +630,76 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>3.75</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>213.603</v>
+        <v>752.409</v>
       </c>
       <c r="V2">
-        <v>0.1697309452673066</v>
+        <v>0.06050322253806535</v>
       </c>
       <c r="W2">
-        <v>-0.3315076836581709</v>
+        <v>-0.1096654275092937</v>
       </c>
       <c r="X2">
-        <v>0.1177104864933</v>
+        <v>0.100040004556449</v>
       </c>
       <c r="Y2">
-        <v>-0.4492181701514709</v>
+        <v>-0.2097054320657426</v>
       </c>
       <c r="Z2">
-        <v>15.42775680508643</v>
+        <v>23.94301987758805</v>
+      </c>
+      <c r="AA2">
+        <v>-0.6014285714285713</v>
       </c>
       <c r="AB2">
-        <v>0.1165670751374978</v>
+        <v>0.09673998864370735</v>
+      </c>
+      <c r="AC2">
+        <v>-0.6939298616421785</v>
       </c>
       <c r="AD2">
-        <v>148.8</v>
+        <v>747.607</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>24.97582464365017</v>
       </c>
       <c r="AF2">
-        <v>148.8</v>
+        <v>772.5828246436502</v>
       </c>
       <c r="AG2">
-        <v>-64.803</v>
+        <v>20.17382464365016</v>
       </c>
       <c r="AH2">
-        <v>0.1057358876698312</v>
+        <v>0.05849163446568792</v>
       </c>
       <c r="AI2">
-        <v>0.3295170184024626</v>
+        <v>0.5147762678714387</v>
       </c>
       <c r="AJ2">
-        <v>-0.05428855544674144</v>
+        <v>0.001619603890266909</v>
       </c>
       <c r="AK2">
-        <v>-0.2723192711594465</v>
+        <v>0.02695580110544713</v>
       </c>
       <c r="AL2">
-        <v>7.417999999999999</v>
+        <v>31.585</v>
       </c>
       <c r="AM2">
-        <v>7.033999999999999</v>
+        <v>2.706</v>
       </c>
       <c r="AN2">
-        <v>-1.631704187821434</v>
+        <v>-5.11359097127223</v>
       </c>
       <c r="AO2">
-        <v>-18.39498517120518</v>
+        <v>-6.930220041158778</v>
       </c>
       <c r="AP2">
-        <v>0.7106137532486045</v>
+        <v>-0.1379878566597139</v>
       </c>
       <c r="AQ2">
-        <v>-19.39920386693205</v>
+        <v>-80.89098300073913</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MKB Nedsense NV (ENXTAM:NEDSE)</t>
+          <t>MKB Nedsense N.V. (ENXTAM:NEDSE)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -715,26 +718,8 @@
           <t>Software (System &amp; Application)</t>
         </is>
       </c>
-      <c r="E3">
-        <v>-0.48</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0.2796610169491526</v>
-      </c>
-      <c r="J3">
-        <v>0.2796610169491526</v>
-      </c>
       <c r="K3">
-        <v>0.14</v>
-      </c>
-      <c r="L3">
-        <v>0.5932203389830509</v>
+        <v>-0.107</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +728,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,37 +737,37 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.049</v>
+        <v>0.011</v>
       </c>
       <c r="V3">
-        <v>0.0035</v>
+        <v>0.001009174311926605</v>
       </c>
       <c r="W3">
-        <v>0.01907356948228883</v>
+        <v>-0.01116910229645094</v>
       </c>
       <c r="X3">
-        <v>0.1168334971930334</v>
+        <v>0.09759992688016936</v>
       </c>
       <c r="Y3">
-        <v>-0.0977599277107446</v>
+        <v>-0.1087690291766203</v>
       </c>
       <c r="Z3">
-        <v>0.0509719222462203</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>0.0142548596112311</v>
+        <v>-0.02205498066269468</v>
       </c>
       <c r="AB3">
-        <v>0.1168334971930334</v>
+        <v>0.09759992688016936</v>
       </c>
       <c r="AC3">
-        <v>-0.1025786375818023</v>
+        <v>-0.119654907542864</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -794,7 +779,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.049</v>
+        <v>-0.011</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -803,19 +788,19 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.003512293025589564</v>
+        <v>-0.001010193773532923</v>
       </c>
       <c r="AK3">
-        <v>-0.004875136802308228</v>
+        <v>-0.001112347052280311</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.075</v>
+        <v>-0.105</v>
       </c>
       <c r="AQ3">
-        <v>-0.8800000000000001</v>
+        <v>2.009523809523809</v>
       </c>
     </row>
     <row r="4">
@@ -826,7 +811,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CM.com N.V. (ENXTAM:CMCOM)</t>
+          <t>GeoJunxion N.V. (ENXTAM:GOJXN)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -835,31 +820,31 @@
         </is>
       </c>
       <c r="G4">
-        <v>-0.06085043988269795</v>
+        <v>-1.752212389380531</v>
       </c>
       <c r="H4">
-        <v>-0.06085043988269795</v>
+        <v>-1.752212389380531</v>
       </c>
       <c r="I4">
-        <v>-0.125733137829912</v>
+        <v>-1.929203539823009</v>
       </c>
       <c r="J4">
-        <v>-0.125733137829912</v>
+        <v>-1.929203539823009</v>
       </c>
       <c r="K4">
-        <v>-35.9</v>
+        <v>-0.885</v>
       </c>
       <c r="L4">
-        <v>-0.1315982404692082</v>
+        <v>-0.7831858407079647</v>
       </c>
       <c r="M4">
-        <v>3.75</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.01070205479452055</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>-0.1044568245125348</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -871,79 +856,76 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>3.75</v>
-      </c>
-      <c r="T4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>101.4</v>
+        <v>0.898</v>
       </c>
       <c r="V4">
-        <v>0.2893835616438357</v>
+        <v>0.1778217821782178</v>
       </c>
       <c r="W4">
-        <v>-0.3094827586206896</v>
+        <v>-0.1096654275092937</v>
       </c>
       <c r="X4">
-        <v>0.136976517211328</v>
+        <v>0.1019801604826958</v>
       </c>
       <c r="Y4">
-        <v>-0.4464592758320177</v>
+        <v>-0.2116455879919895</v>
       </c>
       <c r="Z4">
-        <v>5.969365426695844</v>
+        <v>0.150345928685471</v>
       </c>
       <c r="AA4">
-        <v>-0.7505470459518601</v>
+        <v>-0.2900478978179883</v>
       </c>
       <c r="AB4">
-        <v>0.1121560673954041</v>
+        <v>0.09611861729487381</v>
       </c>
       <c r="AC4">
-        <v>-0.8627031133472641</v>
+        <v>-0.3861665151128621</v>
       </c>
       <c r="AD4">
-        <v>121.9</v>
+        <v>0.507</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>121.9</v>
+        <v>0.507</v>
       </c>
       <c r="AG4">
-        <v>20.5</v>
+        <v>-0.391</v>
       </c>
       <c r="AH4">
-        <v>0.2580986661020538</v>
+        <v>0.09123627856757244</v>
       </c>
       <c r="AI4">
-        <v>0.603166749134092</v>
+        <v>0.06081324217344369</v>
       </c>
       <c r="AJ4">
-        <v>0.05527096252359127</v>
+        <v>-0.08392358875295128</v>
       </c>
       <c r="AK4">
-        <v>0.2035749751737835</v>
+        <v>-0.05256082806828875</v>
       </c>
       <c r="AL4">
-        <v>4.6</v>
+        <v>0.345</v>
       </c>
       <c r="AM4">
-        <v>4.290999999999999</v>
+        <v>0.34</v>
       </c>
       <c r="AN4">
-        <v>-4.481617647058824</v>
+        <v>-0.250990099009901</v>
       </c>
       <c r="AO4">
-        <v>-7.456521739130435</v>
+        <v>-6.318840579710145</v>
       </c>
       <c r="AP4">
-        <v>-0.7536764705882353</v>
+        <v>0.1935643564356436</v>
       </c>
       <c r="AQ4">
-        <v>-7.993474714518761</v>
+        <v>-6.411764705882354</v>
       </c>
     </row>
     <row r="5">
@@ -954,7 +936,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TomTom N.V. (ENXTAM:TOM2)</t>
+          <t>CM.com N.V. (ENXTAM:CMCOM)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -962,26 +944,23 @@
           <t>Software (System &amp; Application)</t>
         </is>
       </c>
-      <c r="D5">
-        <v>-0.116</v>
-      </c>
       <c r="G5">
-        <v>0.6583084577114429</v>
+        <v>-0.136144190537496</v>
       </c>
       <c r="H5">
-        <v>-0.09253731343283582</v>
+        <v>-0.136144190537496</v>
       </c>
       <c r="I5">
-        <v>-0.1998009950248756</v>
+        <v>-0.1355004827808175</v>
       </c>
       <c r="J5">
-        <v>-0.1998009950248756</v>
+        <v>-0.1355004827808175</v>
       </c>
       <c r="K5">
-        <v>-130.1</v>
+        <v>-44.7</v>
       </c>
       <c r="L5">
-        <v>-0.2589054726368159</v>
+        <v>-0.1438686836176376</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1005,64 +984,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>111.6</v>
+        <v>67</v>
       </c>
       <c r="V5">
-        <v>0.1256756756756757</v>
+        <v>0.2396280400572246</v>
       </c>
       <c r="W5">
-        <v>-0.3535326086956522</v>
+        <v>-0.557356608478803</v>
       </c>
       <c r="X5">
-        <v>0.1185874757935667</v>
+        <v>0.1175733956046721</v>
       </c>
       <c r="Y5">
-        <v>-0.4721200844892188</v>
+        <v>-0.674930004083475</v>
+      </c>
+      <c r="Z5">
+        <v>4.438571428571428</v>
+      </c>
+      <c r="AA5">
+        <v>-0.6014285714285713</v>
       </c>
       <c r="AB5">
-        <v>0.1163006530819622</v>
+        <v>0.09250129021360726</v>
+      </c>
+      <c r="AC5">
+        <v>-0.6939298616421785</v>
       </c>
       <c r="AD5">
-        <v>26.9</v>
+        <v>128</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>26.9</v>
+        <v>128</v>
       </c>
       <c r="AG5">
-        <v>-84.69999999999999</v>
+        <v>61</v>
       </c>
       <c r="AH5">
-        <v>0.02940212045032244</v>
+        <v>0.3140333660451423</v>
       </c>
       <c r="AI5">
-        <v>0.1162991785559879</v>
+        <v>0.7587433313574393</v>
       </c>
       <c r="AJ5">
-        <v>-0.1054400597535167</v>
+        <v>0.1790957134468585</v>
       </c>
       <c r="AK5">
-        <v>-0.7076023391812863</v>
+        <v>0.599803343166175</v>
       </c>
       <c r="AL5">
-        <v>2.48</v>
+        <v>4.79</v>
       </c>
       <c r="AM5">
-        <v>2.48</v>
+        <v>4.611</v>
       </c>
       <c r="AN5">
-        <v>-0.426984126984127</v>
+        <v>-3.516483516483516</v>
       </c>
       <c r="AO5">
-        <v>-40.48387096774194</v>
+        <v>-8.789144050104385</v>
       </c>
       <c r="AP5">
-        <v>1.344444444444444</v>
+        <v>-1.675824175824176</v>
       </c>
       <c r="AQ5">
-        <v>-40.48387096774194</v>
+        <v>-9.130340490132292</v>
       </c>
     </row>
     <row r="6">
@@ -1073,7 +1061,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GeoJunxion N.V. (ENXTAM:GOJXN)</t>
+          <t>Elastic N.V. (NYSE:ESTC)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1081,23 +1069,29 @@
           <t>Software (System &amp; Application)</t>
         </is>
       </c>
+      <c r="D6">
+        <v>0.405</v>
+      </c>
+      <c r="F6">
+        <v>0.18</v>
+      </c>
       <c r="G6">
-        <v>-1.261930010604454</v>
+        <v>0.1365950470273535</v>
       </c>
       <c r="H6">
-        <v>-1.261930010604454</v>
+        <v>-0.1395288635775304</v>
       </c>
       <c r="I6">
-        <v>-1.930010604453871</v>
+        <v>-0.1068212657940547</v>
       </c>
       <c r="J6">
-        <v>-1.930010604453871</v>
+        <v>-0.1068212657940547</v>
       </c>
       <c r="K6">
-        <v>-0.233</v>
+        <v>-192.6</v>
       </c>
       <c r="L6">
-        <v>-0.247083775185578</v>
+        <v>-0.1661920786953145</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1121,58 +1115,183 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0.554</v>
+        <v>589.7</v>
       </c>
       <c r="V6">
-        <v>0.09111842105263158</v>
+        <v>0.05251861351572798</v>
+      </c>
+      <c r="W6">
+        <v>-0.4918283963227783</v>
       </c>
       <c r="X6">
-        <v>0.1168334971930334</v>
+        <v>0.09990440737797801</v>
+      </c>
+      <c r="Y6">
+        <v>-0.5917328037007563</v>
       </c>
       <c r="AB6">
-        <v>0.1168334971930334</v>
+        <v>0.09750539742234063</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>568.1</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>24.97582464365017</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>593.0758246436502</v>
       </c>
       <c r="AG6">
-        <v>-0.554</v>
+        <v>3.375824643650162</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.05016935562371105</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>0.5658171183687422</v>
       </c>
       <c r="AJ6">
-        <v>-0.1002533478103511</v>
+        <v>0.0003005601871293818</v>
       </c>
       <c r="AK6">
-        <v>-0.07370941990420438</v>
+        <v>0.007363146456574931</v>
       </c>
       <c r="AL6">
-        <v>0.338</v>
+        <v>25.2</v>
       </c>
       <c r="AM6">
-        <v>0.338</v>
+        <v>-0.9000000000000021</v>
       </c>
       <c r="AN6">
-        <v>-0</v>
+        <v>-5.726814516129032</v>
       </c>
       <c r="AO6">
-        <v>-5.384615384615384</v>
+        <v>-5.234126984126984</v>
       </c>
       <c r="AP6">
-        <v>0.5579053373615308</v>
+        <v>-0.03403049035937664</v>
       </c>
       <c r="AQ6">
-        <v>-5.384615384615384</v>
+        <v>146.5555555555552</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TomTom N.V. (ENXTAM:TOM2)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Software (System &amp; Application)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>-0.0101</v>
+      </c>
+      <c r="G7">
+        <v>0.5184763145043139</v>
+      </c>
+      <c r="H7">
+        <v>-0.09702099951163927</v>
+      </c>
+      <c r="I7">
+        <v>-0.06918443757121928</v>
+      </c>
+      <c r="J7">
+        <v>-0.06918443757121928</v>
+      </c>
+      <c r="K7">
+        <v>-19.2</v>
+      </c>
+      <c r="L7">
+        <v>-0.03125508709099788</v>
+      </c>
+      <c r="M7">
+        <v>-0</v>
+      </c>
+      <c r="N7">
+        <v>-0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>-0</v>
+      </c>
+      <c r="Q7">
+        <v>-0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>94.8</v>
+      </c>
+      <c r="V7">
+        <v>0.1039587674087071</v>
+      </c>
+      <c r="W7">
+        <v>-0.09393346379647749</v>
+      </c>
+      <c r="X7">
+        <v>0.100040004556449</v>
+      </c>
+      <c r="Y7">
+        <v>-0.1939734683529264</v>
+      </c>
+      <c r="AB7">
+        <v>0.09673998864370735</v>
+      </c>
+      <c r="AD7">
+        <v>51</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>51</v>
+      </c>
+      <c r="AG7">
+        <v>-43.8</v>
+      </c>
+      <c r="AH7">
+        <v>0.05296500155779416</v>
+      </c>
+      <c r="AI7">
+        <v>0.1919458035378246</v>
+      </c>
+      <c r="AJ7">
+        <v>-0.0504550167031448</v>
+      </c>
+      <c r="AK7">
+        <v>-0.2562902282036278</v>
+      </c>
+      <c r="AL7">
+        <v>1.25</v>
+      </c>
+      <c r="AM7">
+        <v>-1.24</v>
+      </c>
+      <c r="AN7">
+        <v>-5.944055944055944</v>
+      </c>
+      <c r="AO7">
+        <v>-34</v>
+      </c>
+      <c r="AP7">
+        <v>5.104895104895104</v>
+      </c>
+      <c r="AQ7">
+        <v>34.27419354838709</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/netherlands/netherlands_software_system_application.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_software_system_application.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -581,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -590,118 +590,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.321</v>
+        <v>0.248</v>
+      </c>
+      <c r="E2">
+        <v>-0.278</v>
       </c>
       <c r="F2">
         <v>0.15</v>
       </c>
       <c r="G2">
-        <v>0.1847059678709021</v>
+        <v>0.2677050377220735</v>
       </c>
       <c r="H2">
-        <v>-0.07596132877807661</v>
+        <v>0.04351029052902989</v>
       </c>
       <c r="I2">
-        <v>-0.07022688874283731</v>
+        <v>0.03254486498210215</v>
       </c>
       <c r="J2">
-        <v>-0.07022688874283731</v>
+        <v>0.03116206507195252</v>
       </c>
       <c r="K2">
-        <v>60.3</v>
+        <v>134.716</v>
       </c>
       <c r="L2">
-        <v>0.04383223086428727</v>
+        <v>0.04430485486703545</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>142.4</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.008154248139955302</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>1.057038510644615</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>142.4</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.008154248139955302</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.057038510644615</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>658.5</v>
+        <v>961.908</v>
       </c>
       <c r="V2">
-        <v>0.06413253082451938</v>
+        <v>0.05508171713348402</v>
       </c>
       <c r="W2">
-        <v>0.1324983520105471</v>
+        <v>0.07715826691436448</v>
       </c>
       <c r="X2">
-        <v>0.1035566364082629</v>
+        <v>0.103688994193661</v>
       </c>
       <c r="Y2">
-        <v>0.02894171560228426</v>
+        <v>-0.02653072727929649</v>
       </c>
       <c r="Z2">
-        <v>8.958966747329747</v>
+        <v>6.590864275119108</v>
       </c>
       <c r="AA2">
-        <v>-0.6291603610155051</v>
+        <v>-0.09493081538409681</v>
       </c>
       <c r="AB2">
-        <v>0.1006584695486945</v>
+        <v>0.1002964873625249</v>
       </c>
       <c r="AC2">
-        <v>-0.7298188305641996</v>
+        <v>-0.19212016247981</v>
       </c>
       <c r="AD2">
-        <v>569.2</v>
+        <v>1154.3</v>
       </c>
       <c r="AE2">
         <v>23.55565421760637</v>
       </c>
       <c r="AF2">
-        <v>592.7556542176064</v>
+        <v>1177.855654217606</v>
       </c>
       <c r="AG2">
-        <v>-65.74434578239357</v>
+        <v>215.9476542176063</v>
       </c>
       <c r="AH2">
-        <v>0.05457875941986585</v>
+        <v>0.0631857974861708</v>
       </c>
       <c r="AI2">
-        <v>0.4221137742527841</v>
+        <v>0.4629233985285123</v>
       </c>
       <c r="AJ2">
-        <v>-0.006444225361112823</v>
+        <v>0.01221476052538325</v>
       </c>
       <c r="AK2">
-        <v>-0.08815802523330224</v>
+        <v>0.1364617400075536</v>
       </c>
       <c r="AL2">
-        <v>26.5</v>
+        <v>57.58</v>
       </c>
       <c r="AM2">
-        <v>-10.6</v>
+        <v>19.599</v>
       </c>
       <c r="AN2">
-        <v>-7.489473684210527</v>
+        <v>7.157118055555555</v>
       </c>
       <c r="AO2">
-        <v>-3.958490566037736</v>
+        <v>1.574661340743313</v>
       </c>
       <c r="AP2">
-        <v>0.8650571813472837</v>
+        <v>1.338961149662738</v>
       </c>
       <c r="AQ2">
-        <v>9.896226415094338</v>
+        <v>4.626205418643808</v>
       </c>
     </row>
     <row r="3">
@@ -712,126 +718,504 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Topicus.com Inc. (TSXV:TOI)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Software (System &amp; Application)</t>
+        </is>
+      </c>
+      <c r="G3">
+        <v>0.4199334587009982</v>
+      </c>
+      <c r="H3">
+        <v>0.1862433097063504</v>
+      </c>
+      <c r="I3">
+        <v>0.1513091277303631</v>
+      </c>
+      <c r="J3">
+        <v>0.1255932123814527</v>
+      </c>
+      <c r="K3">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="L3">
+        <v>0.06755388398669175</v>
+      </c>
+      <c r="M3">
+        <v>142.4</v>
+      </c>
+      <c r="N3">
+        <v>0.020293861961835</v>
+      </c>
+      <c r="O3">
+        <v>1.524625267665953</v>
+      </c>
+      <c r="P3">
+        <v>142.4</v>
+      </c>
+      <c r="Q3">
+        <v>0.020293861961835</v>
+      </c>
+      <c r="R3">
+        <v>1.524625267665953</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>261.7</v>
+      </c>
+      <c r="V3">
+        <v>0.03729567187789479</v>
+      </c>
+      <c r="W3">
+        <v>0.2812405901836796</v>
+      </c>
+      <c r="X3">
+        <v>0.1038584843610963</v>
+      </c>
+      <c r="Y3">
+        <v>0.1773821058225833</v>
+      </c>
+      <c r="Z3">
+        <v>6.056066579062636</v>
+      </c>
+      <c r="AA3">
+        <v>0.7606008560604314</v>
+      </c>
+      <c r="AB3">
+        <v>0.09996961091904663</v>
+      </c>
+      <c r="AC3">
+        <v>0.6606312451413847</v>
+      </c>
+      <c r="AD3">
+        <v>463</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>463</v>
+      </c>
+      <c r="AG3">
+        <v>201.3</v>
+      </c>
+      <c r="AH3">
+        <v>0.06189922325164775</v>
+      </c>
+      <c r="AI3">
+        <v>0.4688132847306602</v>
+      </c>
+      <c r="AJ3">
+        <v>0.02788783907345322</v>
+      </c>
+      <c r="AK3">
+        <v>0.2773109243697479</v>
+      </c>
+      <c r="AL3">
+        <v>26.1</v>
+      </c>
+      <c r="AM3">
+        <v>26.1</v>
+      </c>
+      <c r="AN3">
+        <v>1.886715566422168</v>
+      </c>
+      <c r="AO3">
+        <v>8.015325670498083</v>
+      </c>
+      <c r="AP3">
+        <v>0.8202933985330073</v>
+      </c>
+      <c r="AQ3">
+        <v>8.015325670498083</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MKB Nedsense N.V. (ENXTAM:NEDSE)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Software (System &amp; Application)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>-0.3</v>
+      </c>
+      <c r="E4">
+        <v>-0.278</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0.2653846153846154</v>
+      </c>
+      <c r="J4">
+        <v>0.2653846153846154</v>
+      </c>
+      <c r="K4">
+        <v>0.216</v>
+      </c>
+      <c r="L4">
+        <v>0.8307692307692307</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>-0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>-0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0.008</v>
+      </c>
+      <c r="V4">
+        <v>0.001144492131616595</v>
+      </c>
+      <c r="W4">
+        <v>0.02181818181818182</v>
+      </c>
+      <c r="X4">
+        <v>0.1011486268241594</v>
+      </c>
+      <c r="Y4">
+        <v>-0.07933044500597761</v>
+      </c>
+      <c r="Z4">
+        <v>0.02629183941753463</v>
+      </c>
+      <c r="AA4">
+        <v>0.006977449691576499</v>
+      </c>
+      <c r="AB4">
+        <v>0.1011486268241594</v>
+      </c>
+      <c r="AC4">
+        <v>-0.09417117713258293</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>-0.008</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.001145803494700659</v>
+      </c>
+      <c r="AK4">
+        <v>-0.0008062890546260835</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>-0.149</v>
+      </c>
+      <c r="AQ4">
+        <v>-0.4630872483221477</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CM.com N.V. (ENXTAM:CMCOM)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Software (System &amp; Application)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.248</v>
+      </c>
+      <c r="G5">
+        <v>-0.07337823466855724</v>
+      </c>
+      <c r="H5">
+        <v>-0.07337823466855724</v>
+      </c>
+      <c r="I5">
+        <v>-0.04856433888691952</v>
+      </c>
+      <c r="J5">
+        <v>-0.04856433888691952</v>
+      </c>
+      <c r="K5">
+        <v>-19.2</v>
+      </c>
+      <c r="L5">
+        <v>-0.06806097128677772</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>41.7</v>
+      </c>
+      <c r="V5">
+        <v>0.243006993006993</v>
+      </c>
+      <c r="W5">
+        <v>-0.4717444717444717</v>
+      </c>
+      <c r="X5">
+        <v>0.1303705729939762</v>
+      </c>
+      <c r="Y5">
+        <v>-0.6021150447384479</v>
+      </c>
+      <c r="Z5">
+        <v>4.053160919540231</v>
+      </c>
+      <c r="AA5">
+        <v>-0.1968390804597701</v>
+      </c>
+      <c r="AB5">
+        <v>0.09323006736726699</v>
+      </c>
+      <c r="AC5">
+        <v>-0.2900691478270371</v>
+      </c>
+      <c r="AD5">
+        <v>122.1</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>122.1</v>
+      </c>
+      <c r="AG5">
+        <v>80.39999999999999</v>
+      </c>
+      <c r="AH5">
+        <v>0.4157303370786517</v>
+      </c>
+      <c r="AI5">
+        <v>0.8562412342215989</v>
+      </c>
+      <c r="AJ5">
+        <v>0.319047619047619</v>
+      </c>
+      <c r="AK5">
+        <v>0.796828543111992</v>
+      </c>
+      <c r="AL5">
+        <v>4.98</v>
+      </c>
+      <c r="AM5">
+        <v>4.248</v>
+      </c>
+      <c r="AN5">
+        <v>-15.03694581280788</v>
+      </c>
+      <c r="AO5">
+        <v>-2.751004016064257</v>
+      </c>
+      <c r="AP5">
+        <v>-9.901477832512315</v>
+      </c>
+      <c r="AQ5">
+        <v>-3.225047080979284</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Elastic N.V. (NYSE:ESTC)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Software (System &amp; Application)</t>
         </is>
       </c>
-      <c r="D3">
+      <c r="D6">
         <v>0.321</v>
       </c>
-      <c r="F3">
+      <c r="F6">
         <v>0.15</v>
       </c>
-      <c r="G3">
+      <c r="G6">
         <v>0.1847059678709021</v>
       </c>
-      <c r="H3">
+      <c r="H6">
         <v>-0.07596132877807661</v>
       </c>
-      <c r="I3">
+      <c r="I6">
         <v>-0.07022688874283731</v>
       </c>
-      <c r="J3">
+      <c r="J6">
         <v>-0.07022688874283731</v>
       </c>
-      <c r="K3">
+      <c r="K6">
         <v>60.3</v>
       </c>
-      <c r="L3">
+      <c r="L6">
         <v>0.04383223086428727</v>
       </c>
-      <c r="M3">
+      <c r="M6">
         <v>-0</v>
       </c>
-      <c r="N3">
+      <c r="N6">
         <v>-0</v>
       </c>
-      <c r="O3">
+      <c r="O6">
         <v>-0</v>
       </c>
-      <c r="P3">
+      <c r="P6">
         <v>-0</v>
       </c>
-      <c r="Q3">
+      <c r="Q6">
         <v>-0</v>
       </c>
-      <c r="R3">
+      <c r="R6">
         <v>-0</v>
       </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="U3">
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="U6">
         <v>658.5</v>
       </c>
-      <c r="V3">
+      <c r="V6">
         <v>0.06413253082451938</v>
       </c>
-      <c r="W3">
+      <c r="W6">
         <v>0.1324983520105471</v>
       </c>
-      <c r="X3">
-        <v>0.1035566364082629</v>
-      </c>
-      <c r="Y3">
-        <v>0.02894171560228426</v>
-      </c>
-      <c r="Z3">
+      <c r="X6">
+        <v>0.1035195040262256</v>
+      </c>
+      <c r="Y6">
+        <v>0.02897884798432154</v>
+      </c>
+      <c r="Z6">
         <v>8.958966747329747</v>
       </c>
-      <c r="AA3">
+      <c r="AA6">
         <v>-0.6291603610155051</v>
       </c>
-      <c r="AB3">
-        <v>0.1006584695486945</v>
-      </c>
-      <c r="AC3">
-        <v>-0.7298188305641996</v>
-      </c>
-      <c r="AD3">
+      <c r="AB6">
+        <v>0.1006233638060031</v>
+      </c>
+      <c r="AC6">
+        <v>-0.7297837248215082</v>
+      </c>
+      <c r="AD6">
         <v>569.2</v>
       </c>
-      <c r="AE3">
+      <c r="AE6">
         <v>23.55565421760637</v>
       </c>
-      <c r="AF3">
+      <c r="AF6">
         <v>592.7556542176064</v>
       </c>
-      <c r="AG3">
+      <c r="AG6">
         <v>-65.74434578239357</v>
       </c>
-      <c r="AH3">
+      <c r="AH6">
         <v>0.05457875941986585</v>
       </c>
-      <c r="AI3">
+      <c r="AI6">
         <v>0.4221137742527841</v>
       </c>
-      <c r="AJ3">
+      <c r="AJ6">
         <v>-0.006444225361112823</v>
       </c>
-      <c r="AK3">
+      <c r="AK6">
         <v>-0.08815802523330224</v>
       </c>
-      <c r="AL3">
+      <c r="AL6">
         <v>26.5</v>
       </c>
-      <c r="AM3">
+      <c r="AM6">
         <v>-10.6</v>
       </c>
-      <c r="AN3">
+      <c r="AN6">
         <v>-7.489473684210527</v>
       </c>
-      <c r="AO3">
+      <c r="AO6">
         <v>-3.958490566037736</v>
       </c>
-      <c r="AP3">
+      <c r="AP6">
         <v>0.8650571813472837</v>
       </c>
-      <c r="AQ3">
+      <c r="AQ6">
         <v>9.896226415094338</v>
       </c>
     </row>
@@ -1127,37 +1511,43 @@
         <v>2.42145593869732</v>
       </c>
       <c r="F2">
-        <v>2.42145593869732</v>
+        <v>3.05580861470646</v>
       </c>
       <c r="G2">
         <v>1.88671556642217</v>
       </c>
       <c r="H2">
-        <v>1.88671556642217</v>
+        <v>1.52402200488998</v>
       </c>
       <c r="I2">
         <v>0.0618992232516478</v>
       </c>
       <c r="J2">
-        <v>0.0618992232516478</v>
+        <v>0.05</v>
       </c>
       <c r="K2">
         <v>7016.9</v>
       </c>
       <c r="L2">
-        <v>7016.9</v>
+        <v>7075.82949340925</v>
       </c>
       <c r="M2">
         <v>7218.2</v>
       </c>
       <c r="N2">
-        <v>7218.2</v>
+        <v>7188.12449340925</v>
       </c>
       <c r="O2">
         <v>463</v>
       </c>
       <c r="P2">
-        <v>463</v>
+        <v>373.995</v>
+      </c>
+      <c r="Q2">
+        <v>0.0999696109190466</v>
+      </c>
+      <c r="R2">
+        <v>0.100196259538128</v>
       </c>
       <c r="S2">
         <v>0.0410326</v>
@@ -1172,14 +1562,20 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
-        </is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.103858484361096</v>
+      </c>
+      <c r="X2">
+        <v>0.103310136355924</v>
       </c>
       <c r="Y2">
         <v>1.34084259494449</v>
       </c>
       <c r="Z2">
-        <v>1.34084259494449</v>
+        <v>1.32817866872804</v>
       </c>
       <c r="AA2">
         <v>463</v>
@@ -1210,6 +1606,9 @@
       </c>
       <c r="AJ2">
         <v>7016.9</v>
+      </c>
+      <c r="AK2">
+        <v>0.0433</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1396,6 +1795,15 @@
       <c r="A2">
         <v>0</v>
       </c>
+      <c r="B2">
+        <v>0.1011486268241594</v>
+      </c>
+      <c r="C2">
+        <v>7326.14058274612</v>
+      </c>
+      <c r="D2">
+        <v>7064.440582746121</v>
+      </c>
       <c r="E2">
         <v>-463</v>
       </c>
@@ -1438,17 +1846,20 @@
       <c r="R2">
         <v>0</v>
       </c>
+      <c r="S2">
+        <v>0.1011486268241594</v>
+      </c>
       <c r="T2">
         <v>1.278259280003682</v>
       </c>
       <c r="U2">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.258</v>
       </c>
       <c r="W2">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1466,6 +1877,15 @@
       <c r="A3">
         <v>0.01</v>
       </c>
+      <c r="B3">
+        <v>0.1009210533669531</v>
+      </c>
+      <c r="C3">
+        <v>7280.507918809068</v>
+      </c>
+      <c r="D3">
+        <v>7093.606918809068</v>
+      </c>
       <c r="E3">
         <v>-388.201</v>
       </c>
@@ -1491,34 +1911,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M3">
-        <v>3.8671083</v>
+        <v>3.7623897</v>
       </c>
       <c r="N3">
-        <v>59.33289170000002</v>
+        <v>59.43761030000002</v>
       </c>
       <c r="O3">
-        <v>15.3078860586</v>
+        <v>15.3349034574</v>
       </c>
       <c r="P3">
-        <v>44.02500564140001</v>
+        <v>44.10270684260001</v>
       </c>
       <c r="Q3">
-        <v>226.2250056414</v>
+        <v>226.3027068426</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
+      <c r="S3">
+        <v>0.1015634619868213</v>
+      </c>
       <c r="T3">
         <v>1.28783976874876</v>
       </c>
       <c r="U3">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.258</v>
       </c>
       <c r="W3">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1526,7 +1949,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>16.34296096646686</v>
+        <v>16.79783463153751</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1536,6 +1959,15 @@
       <c r="A4">
         <v>0.02</v>
       </c>
+      <c r="B4">
+        <v>0.1007157399097468</v>
+      </c>
+      <c r="C4">
+        <v>7232.229784465382</v>
+      </c>
+      <c r="D4">
+        <v>7120.127784465382</v>
+      </c>
       <c r="E4">
         <v>-313.402</v>
       </c>
@@ -1561,34 +1993,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M4">
-        <v>7.898774399999999</v>
+        <v>7.749176399999999</v>
       </c>
       <c r="N4">
-        <v>55.30122560000002</v>
+        <v>55.45082360000002</v>
       </c>
       <c r="O4">
-        <v>14.2677162048</v>
+        <v>14.30631248880001</v>
       </c>
       <c r="P4">
-        <v>41.03350939520001</v>
+        <v>41.14451111120002</v>
       </c>
       <c r="Q4">
-        <v>223.2335093952</v>
+        <v>223.3445111112</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
+      <c r="S4">
+        <v>0.101986763173211</v>
+      </c>
       <c r="T4">
         <v>1.297615777672309</v>
       </c>
       <c r="U4">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V4">
         <v>0.258</v>
       </c>
       <c r="W4">
-        <v>0.0391776</v>
+        <v>0.0384356</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1596,7 +2031,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>8.001241306499402</v>
+        <v>8.155705424385491</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1606,6 +2041,15 @@
       <c r="A5">
         <v>0.03</v>
       </c>
+      <c r="B5">
+        <v>0.1005549464525404</v>
+      </c>
+      <c r="C5">
+        <v>7178.339762309191</v>
+      </c>
+      <c r="D5">
+        <v>7141.036762309191</v>
+      </c>
       <c r="E5">
         <v>-238.603</v>
       </c>
@@ -1631,34 +2075,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M5">
-        <v>12.6784305</v>
+        <v>12.1847571</v>
       </c>
       <c r="N5">
-        <v>50.52156950000002</v>
+        <v>51.01524290000002</v>
       </c>
       <c r="O5">
-        <v>13.03456493100001</v>
+        <v>13.16193266820001</v>
       </c>
       <c r="P5">
-        <v>37.48700456900001</v>
+        <v>37.85331023180001</v>
       </c>
       <c r="Q5">
-        <v>219.687004569</v>
+        <v>220.0533102318</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
+      <c r="S5">
+        <v>0.1024187922191138</v>
+      </c>
       <c r="T5">
         <v>1.307593353790158</v>
       </c>
       <c r="U5">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V5">
         <v>0.258</v>
       </c>
       <c r="W5">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1666,7 +2113,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>4.984844141394317</v>
+        <v>5.186808360750993</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1676,6 +2123,15 @@
       <c r="A6">
         <v>0.04</v>
       </c>
+      <c r="B6">
+        <v>0.1003867329953341</v>
+      </c>
+      <c r="C6">
+        <v>7125.546447865207</v>
+      </c>
+      <c r="D6">
+        <v>7163.042447865208</v>
+      </c>
       <c r="E6">
         <v>-163.804</v>
       </c>
@@ -1701,34 +2157,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M6">
-        <v>17.3234484</v>
+        <v>16.5455388</v>
       </c>
       <c r="N6">
-        <v>45.87655160000002</v>
+        <v>46.65446120000001</v>
       </c>
       <c r="O6">
-        <v>11.83615031280001</v>
+        <v>12.0368509896</v>
       </c>
       <c r="P6">
-        <v>34.04040128720001</v>
+        <v>34.61761021040001</v>
       </c>
       <c r="Q6">
-        <v>216.2404012872</v>
+        <v>216.8176102104</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
+      <c r="S6">
+        <v>0.1028598218701397</v>
+      </c>
       <c r="T6">
         <v>1.317778796077129</v>
       </c>
       <c r="U6">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V6">
         <v>0.258</v>
       </c>
       <c r="W6">
-        <v>0.0429618</v>
+        <v>0.0410326</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1736,7 +2195,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>3.648234378092992</v>
+        <v>3.819760768383077</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1746,6 +2205,15 @@
       <c r="A7">
         <v>0.05</v>
       </c>
+      <c r="B7">
+        <v>0.1001962595381277</v>
+      </c>
+      <c r="C7">
+        <v>7075.829493409246</v>
+      </c>
+      <c r="D7">
+        <v>7188.124493409246</v>
+      </c>
       <c r="E7">
         <v>-89.005</v>
       </c>
@@ -1771,42 +2239,45 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M7">
-        <v>22.6266975</v>
+        <v>20.6819235</v>
       </c>
       <c r="N7">
-        <v>40.57330250000002</v>
+        <v>42.51807650000002</v>
       </c>
       <c r="O7">
-        <v>10.46791204500001</v>
+        <v>10.96966373700001</v>
       </c>
       <c r="P7">
-        <v>30.10539045500001</v>
+        <v>31.54841276300002</v>
       </c>
       <c r="Q7">
-        <v>212.305390455</v>
+        <v>213.748412763</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
+      <c r="S7">
+        <v>0.103310136355924</v>
+      </c>
       <c r="T7">
         <v>1.328178668728036</v>
       </c>
       <c r="U7">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V7">
         <v>0.258</v>
       </c>
       <c r="W7">
-        <v>0.044891</v>
+        <v>0.0410326</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y7">
-        <v>2.793160601541609</v>
+        <v>3.055808614706462</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1816,6 +2287,15 @@
       <c r="A8">
         <v>0.06</v>
       </c>
+      <c r="B8">
+        <v>0.1002729060809214</v>
+      </c>
+      <c r="C8">
+        <v>6990.916384740764</v>
+      </c>
+      <c r="D8">
+        <v>7178.010384740764</v>
+      </c>
       <c r="E8">
         <v>-14.20600000000002</v>
       </c>
@@ -1841,42 +2321,45 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M8">
-        <v>30.4731126</v>
+        <v>27.5110722</v>
       </c>
       <c r="N8">
-        <v>32.72688740000002</v>
+        <v>35.68892780000002</v>
       </c>
       <c r="O8">
-        <v>8.443536949200004</v>
+        <v>9.207743372400005</v>
       </c>
       <c r="P8">
-        <v>24.28335045080001</v>
+        <v>26.48118442760001</v>
       </c>
       <c r="Q8">
-        <v>206.4833504508</v>
+        <v>208.6811844276</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
+      <c r="S8">
+        <v>0.1037700320009803</v>
+      </c>
       <c r="T8">
         <v>1.338799815265133</v>
       </c>
       <c r="U8">
-        <v>0.0679</v>
+        <v>0.0613</v>
       </c>
       <c r="V8">
         <v>0.258</v>
       </c>
       <c r="W8">
-        <v>0.0503818</v>
+        <v>0.0454846</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y8">
-        <v>2.073959454998372</v>
+        <v>2.297256884084657</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1886,6 +2369,15 @@
       <c r="A9">
         <v>0.07000000000000001</v>
       </c>
+      <c r="B9">
+        <v>0.1008800826237151</v>
+      </c>
+      <c r="C9">
+        <v>6836.99042410568</v>
+      </c>
+      <c r="D9">
+        <v>7098.88342410568</v>
+      </c>
       <c r="E9">
         <v>60.59300000000007</v>
       </c>
@@ -1911,42 +2403,45 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M9">
-        <v>68.53832370000001</v>
+        <v>39.68834940000001</v>
       </c>
       <c r="N9">
-        <v>-5.338323699999989</v>
+        <v>23.51165060000001</v>
       </c>
       <c r="O9">
-        <v>-1.377287514599997</v>
+        <v>6.066005854800003</v>
       </c>
       <c r="P9">
-        <v>-3.961036185399992</v>
+        <v>17.44564474520001</v>
       </c>
       <c r="Q9">
-        <v>178.2389638146</v>
+        <v>199.6456447452</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
+      <c r="S9">
+        <v>0.1042398178749625</v>
+      </c>
       <c r="T9">
-        <v>1.351582788975787</v>
+        <v>1.349649373555715</v>
       </c>
       <c r="U9">
-        <v>0.1309</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V9">
-        <v>0.2379048555574756</v>
+        <v>0.258</v>
       </c>
       <c r="W9">
-        <v>0.09975825440752645</v>
+        <v>0.0562436</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y9">
-        <v>0.9221118432460292</v>
+        <v>1.592406863864185</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -1956,6 +2451,15 @@
       <c r="A10">
         <v>0.08</v>
       </c>
+      <c r="B10">
+        <v>0.1037753715814084</v>
+      </c>
+      <c r="C10">
+        <v>6407.67332048465</v>
+      </c>
+      <c r="D10">
+        <v>6744.36532048465</v>
+      </c>
       <c r="E10">
         <v>135.3919999999999</v>
       </c>
@@ -1981,34 +2485,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M10">
-        <v>78.32951279999999</v>
+        <v>70.9692912</v>
       </c>
       <c r="N10">
-        <v>-15.12951279999997</v>
+        <v>-7.769291199999984</v>
       </c>
       <c r="O10">
-        <v>-3.903414302399993</v>
+        <v>-2.004477129599996</v>
       </c>
       <c r="P10">
-        <v>-11.22609849759998</v>
+        <v>-5.764814070399988</v>
       </c>
       <c r="Q10">
-        <v>170.9739015024</v>
+        <v>176.4351859296</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
+      <c r="S10">
+        <v>0.1048557541009582</v>
+      </c>
       <c r="T10">
-        <v>1.366273906247264</v>
+        <v>1.363874228659544</v>
       </c>
       <c r="U10">
-        <v>0.1309</v>
+        <v>0.1186</v>
       </c>
       <c r="V10">
-        <v>0.2081667486127912</v>
+        <v>0.2297557115802223</v>
       </c>
       <c r="W10">
-        <v>0.1036509726065856</v>
+        <v>0.09135097260658565</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2016,7 +2523,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>0.8068478628402758</v>
+        <v>0.8905260138768304</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2026,6 +2533,15 @@
       <c r="A11">
         <v>0.09</v>
       </c>
+      <c r="B11">
+        <v>0.1123178296332762</v>
+      </c>
+      <c r="C11">
+        <v>5466.738757217717</v>
+      </c>
+      <c r="D11">
+        <v>5878.229757217717</v>
+      </c>
       <c r="E11">
         <v>210.1909999999999</v>
       </c>
@@ -2051,34 +2567,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M11">
-        <v>145.2746178</v>
+        <v>135.1767528</v>
       </c>
       <c r="N11">
-        <v>-82.07461779999997</v>
+        <v>-71.97675279999996</v>
       </c>
       <c r="O11">
-        <v>-21.17525139239999</v>
+        <v>-18.57000222239999</v>
       </c>
       <c r="P11">
-        <v>-60.89936640759998</v>
+        <v>-53.40675057759996</v>
       </c>
       <c r="Q11">
-        <v>121.3006335924</v>
+        <v>128.7932494224</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
+      <c r="S11">
+        <v>0.1059623646425817</v>
+      </c>
       <c r="T11">
-        <v>1.390491026763986</v>
+        <v>1.389431054101193</v>
       </c>
       <c r="U11">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V11">
-        <v>0.1122398409779193</v>
+        <v>0.1206242912501743</v>
       </c>
       <c r="W11">
-        <v>0.191578642316965</v>
+        <v>0.176578642316965</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2086,7 +2605,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>0.4350381433252687</v>
+        <v>0.4675360125975746</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2096,6 +2615,15 @@
       <c r="A12">
         <v>0.1</v>
       </c>
+      <c r="B12">
+        <v>0.1138678296332762</v>
+      </c>
+      <c r="C12">
+        <v>5258.084216754983</v>
+      </c>
+      <c r="D12">
+        <v>5744.374216754983</v>
+      </c>
       <c r="E12">
         <v>284.99</v>
       </c>
@@ -2121,34 +2649,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M12">
-        <v>161.416242</v>
+        <v>150.196392</v>
       </c>
       <c r="N12">
-        <v>-98.21624199999999</v>
+        <v>-86.99639199999999</v>
       </c>
       <c r="O12">
-        <v>-25.339790436</v>
+        <v>-22.445069136</v>
       </c>
       <c r="P12">
-        <v>-72.87645156399999</v>
+        <v>-64.55132286399999</v>
       </c>
       <c r="Q12">
-        <v>109.323548436</v>
+        <v>117.648677136</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
+      <c r="S12">
+        <v>0.1066308353608326</v>
+      </c>
       <c r="T12">
-        <v>1.405940927061364</v>
+        <v>1.40486917692454</v>
       </c>
       <c r="U12">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V12">
-        <v>0.1010158568801274</v>
+        <v>0.1085618621251568</v>
       </c>
       <c r="W12">
-        <v>0.1940007780852685</v>
+        <v>0.1790007780852685</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2156,7 +2687,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>0.3915343289927418</v>
+        <v>0.420782411337817</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2166,6 +2697,15 @@
       <c r="A13">
         <v>0.11</v>
       </c>
+      <c r="B13">
+        <v>0.1154178296332762</v>
+      </c>
+      <c r="C13">
+        <v>5055.390105935349</v>
+      </c>
+      <c r="D13">
+        <v>5616.479105935349</v>
+      </c>
       <c r="E13">
         <v>359.789</v>
       </c>
@@ -2191,34 +2731,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M13">
-        <v>177.5578662</v>
+        <v>165.2160312</v>
       </c>
       <c r="N13">
-        <v>-114.3578662</v>
+        <v>-102.0160312</v>
       </c>
       <c r="O13">
-        <v>-29.5043294796</v>
+        <v>-26.3201360496</v>
       </c>
       <c r="P13">
-        <v>-84.85353672039999</v>
+        <v>-75.69589515039999</v>
       </c>
       <c r="Q13">
-        <v>97.3464632796</v>
+        <v>106.5041048496</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
+      <c r="S13">
+        <v>0.1073143278929767</v>
+      </c>
       <c r="T13">
-        <v>1.421738016129469</v>
+        <v>1.420654223856276</v>
       </c>
       <c r="U13">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V13">
-        <v>0.09183259716375215</v>
+        <v>0.09869260193196072</v>
       </c>
       <c r="W13">
-        <v>0.1959825255320623</v>
+        <v>0.1809825255320623</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2226,7 +2769,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>0.3559402990843107</v>
+        <v>0.382529464852561</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2236,6 +2779,15 @@
       <c r="A14">
         <v>0.12</v>
       </c>
+      <c r="B14">
+        <v>0.1169678296332762</v>
+      </c>
+      <c r="C14">
+        <v>4858.266979162636</v>
+      </c>
+      <c r="D14">
+        <v>5494.154979162636</v>
+      </c>
       <c r="E14">
         <v>434.588</v>
       </c>
@@ -2261,34 +2813,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M14">
-        <v>193.6994904</v>
+        <v>180.2356704</v>
       </c>
       <c r="N14">
-        <v>-130.4994904</v>
+        <v>-117.0356704</v>
       </c>
       <c r="O14">
-        <v>-33.6688685232</v>
+        <v>-30.1952029632</v>
       </c>
       <c r="P14">
-        <v>-96.8306218768</v>
+        <v>-86.8404674368</v>
       </c>
       <c r="Q14">
-        <v>85.36937812319999</v>
+        <v>95.35953256319999</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
+      <c r="S14">
+        <v>0.108013354346306</v>
+      </c>
       <c r="T14">
-        <v>1.437894129949122</v>
+        <v>1.436798021854643</v>
       </c>
       <c r="U14">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V14">
-        <v>0.08417988073343947</v>
+        <v>0.09046821843763067</v>
       </c>
       <c r="W14">
-        <v>0.1976339817377238</v>
+        <v>0.1826339817377238</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2296,7 +2851,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>0.3262786074939514</v>
+        <v>0.3506520094481809</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2306,6 +2861,15 @@
       <c r="A15">
         <v>0.13</v>
       </c>
+      <c r="B15">
+        <v>0.1185178296332761</v>
+      </c>
+      <c r="C15">
+        <v>4666.358595389099</v>
+      </c>
+      <c r="D15">
+        <v>5377.045595389099</v>
+      </c>
       <c r="E15">
         <v>509.3869999999999</v>
       </c>
@@ -2331,34 +2895,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M15">
-        <v>209.8411146</v>
+        <v>195.2553096</v>
       </c>
       <c r="N15">
-        <v>-146.6411146</v>
+        <v>-132.0553096</v>
       </c>
       <c r="O15">
-        <v>-37.8334075668</v>
+        <v>-34.0702698768</v>
       </c>
       <c r="P15">
-        <v>-108.8077070332</v>
+        <v>-97.98503972319999</v>
       </c>
       <c r="Q15">
-        <v>73.3922929668</v>
+        <v>84.2149602768</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
+      <c r="S15">
+        <v>0.1087284503732751</v>
+      </c>
       <c r="T15">
-        <v>1.454421648684169</v>
+        <v>1.453312941646075</v>
       </c>
       <c r="U15">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V15">
-        <v>0.07770450529240568</v>
+        <v>0.08350912471165908</v>
       </c>
       <c r="W15">
-        <v>0.1990313677578989</v>
+        <v>0.1840313677578989</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2366,7 +2933,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.3011802530713398</v>
+        <v>0.3236787779521669</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2376,6 +2943,15 @@
       <c r="A16">
         <v>0.14</v>
       </c>
+      <c r="B16">
+        <v>0.1200678296332762</v>
+      </c>
+      <c r="C16">
+        <v>4479.338453152852</v>
+      </c>
+      <c r="D16">
+        <v>5264.824453152852</v>
+      </c>
       <c r="E16">
         <v>584.1860000000001</v>
       </c>
@@ -2401,34 +2977,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M16">
-        <v>225.9827388</v>
+        <v>210.2749488</v>
       </c>
       <c r="N16">
-        <v>-162.7827388</v>
+        <v>-147.0749488</v>
       </c>
       <c r="O16">
-        <v>-41.99794661040001</v>
+        <v>-37.94533679040001</v>
       </c>
       <c r="P16">
-        <v>-120.7847921896</v>
+        <v>-109.1296120096</v>
       </c>
       <c r="Q16">
-        <v>61.41520781039996</v>
+        <v>73.07038799039998</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
+      <c r="S16">
+        <v>0.1094601765404062</v>
+      </c>
       <c r="T16">
-        <v>1.471333528320032</v>
+        <v>1.470211929339635</v>
       </c>
       <c r="U16">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V16">
-        <v>0.07215418348580525</v>
+        <v>0.07754418723225485</v>
       </c>
       <c r="W16">
-        <v>0.2002291272037632</v>
+        <v>0.1852291272037632</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2436,7 +3015,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.2796673778519583</v>
+        <v>0.3005588652412978</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2446,6 +3025,15 @@
       <c r="A17">
         <v>0.15</v>
       </c>
+      <c r="B17">
+        <v>0.1216178296332762</v>
+      </c>
+      <c r="C17">
+        <v>4296.906750636064</v>
+      </c>
+      <c r="D17">
+        <v>5157.191750636064</v>
+      </c>
       <c r="E17">
         <v>658.9849999999999</v>
       </c>
@@ -2471,34 +3059,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M17">
-        <v>242.124363</v>
+        <v>225.294588</v>
       </c>
       <c r="N17">
-        <v>-178.924363</v>
+        <v>-162.094588</v>
       </c>
       <c r="O17">
-        <v>-46.16248565399999</v>
+        <v>-41.82040370399999</v>
       </c>
       <c r="P17">
-        <v>-132.761877346</v>
+        <v>-120.274184296</v>
       </c>
       <c r="Q17">
-        <v>49.43812265400001</v>
+        <v>61.92581570400003</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
+      <c r="S17">
+        <v>0.1102091197938227</v>
+      </c>
       <c r="T17">
-        <v>1.488643334535561</v>
+        <v>1.487508540273042</v>
       </c>
       <c r="U17">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V17">
-        <v>0.06734390458675157</v>
+        <v>0.07237457475010454</v>
       </c>
       <c r="W17">
-        <v>0.201267185390179</v>
+        <v>0.186267185390179</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2506,7 +3097,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.2610228859951612</v>
+        <v>0.2805216075585447</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2516,6 +3107,15 @@
       <c r="A18">
         <v>0.16</v>
       </c>
+      <c r="B18">
+        <v>0.1231678296332762</v>
+      </c>
+      <c r="C18">
+        <v>4118.787711139341</v>
+      </c>
+      <c r="D18">
+        <v>5053.871711139341</v>
+      </c>
       <c r="E18">
         <v>733.7839999999999</v>
       </c>
@@ -2541,34 +3141,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M18">
-        <v>258.2659872</v>
+        <v>240.3142272</v>
       </c>
       <c r="N18">
-        <v>-195.0659872</v>
+        <v>-177.1142272</v>
       </c>
       <c r="O18">
-        <v>-50.3270246976</v>
+        <v>-45.69547061759999</v>
       </c>
       <c r="P18">
-        <v>-144.7389625024</v>
+        <v>-131.4187565824</v>
       </c>
       <c r="Q18">
-        <v>37.46103749760002</v>
+        <v>50.78124341760002</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
+      <c r="S18">
+        <v>0.1109758950294635</v>
+      </c>
       <c r="T18">
-        <v>1.506365278994318</v>
+        <v>1.505216975276293</v>
       </c>
       <c r="U18">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V18">
-        <v>0.06313491055007961</v>
+        <v>0.06785116382822301</v>
       </c>
       <c r="W18">
-        <v>0.2021754863032929</v>
+        <v>0.1871754863032928</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2576,7 +3179,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.2447089556204636</v>
+        <v>0.2629890070861357</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2586,6 +3189,15 @@
       <c r="A19">
         <v>0.17</v>
       </c>
+      <c r="B19">
+        <v>0.1247178296332762</v>
+      </c>
+      <c r="C19">
+        <v>3944.727223733167</v>
+      </c>
+      <c r="D19">
+        <v>4954.610223733167</v>
+      </c>
       <c r="E19">
         <v>808.5830000000001</v>
       </c>
@@ -2611,34 +3223,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M19">
-        <v>274.4076114000001</v>
+        <v>255.3338664</v>
       </c>
       <c r="N19">
-        <v>-211.2076114</v>
+        <v>-192.1338664</v>
       </c>
       <c r="O19">
-        <v>-54.49156374120001</v>
+        <v>-49.5705375312</v>
       </c>
       <c r="P19">
-        <v>-156.7160476588001</v>
+        <v>-142.5633288688</v>
       </c>
       <c r="Q19">
-        <v>25.48395234119994</v>
+        <v>39.63667113119999</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
+      <c r="S19">
+        <v>0.1117611467768064</v>
+      </c>
       <c r="T19">
-        <v>1.52451425825931</v>
+        <v>1.52335211955673</v>
       </c>
       <c r="U19">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V19">
-        <v>0.05942109228242785</v>
+        <v>0.06385991889715105</v>
       </c>
       <c r="W19">
-        <v>0.2029769282854521</v>
+        <v>0.1879769282854521</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2646,7 +3261,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.230314311172201</v>
+        <v>0.2475190654928335</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2656,6 +3271,15 @@
       <c r="A20">
         <v>0.18</v>
       </c>
+      <c r="B20">
+        <v>0.1262678296332762</v>
+      </c>
+      <c r="C20">
+        <v>3774.490756589023</v>
+      </c>
+      <c r="D20">
+        <v>4859.172756589023</v>
+      </c>
       <c r="E20">
         <v>883.3819999999998</v>
       </c>
@@ -2681,34 +3305,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M20">
-        <v>290.5492356</v>
+        <v>270.3535055999999</v>
       </c>
       <c r="N20">
-        <v>-227.3492356</v>
+        <v>-207.1535055999999</v>
       </c>
       <c r="O20">
-        <v>-58.65610278479999</v>
+        <v>-53.44560444479998</v>
       </c>
       <c r="P20">
-        <v>-168.6931328152</v>
+        <v>-153.7079011551999</v>
       </c>
       <c r="Q20">
-        <v>13.50686718480003</v>
+        <v>28.49209884480004</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
+      <c r="S20">
+        <v>0.1125655510057918</v>
+      </c>
       <c r="T20">
-        <v>1.543105895555155</v>
+        <v>1.541929584429373</v>
       </c>
       <c r="U20">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V20">
-        <v>0.05611992048895965</v>
+        <v>0.06031214562508713</v>
       </c>
       <c r="W20">
-        <v>0.2036893211584825</v>
+        <v>0.1886893211584825</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2716,7 +3343,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.2175190716626343</v>
+        <v>0.2337680062987874</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2726,6 +3353,15 @@
       <c r="A21">
         <v>0.19</v>
       </c>
+      <c r="B21">
+        <v>0.1278178296332762</v>
+      </c>
+      <c r="C21">
+        <v>3607.86150691783</v>
+      </c>
+      <c r="D21">
+        <v>4767.34250691783</v>
+      </c>
       <c r="E21">
         <v>958.181</v>
       </c>
@@ -2751,34 +3387,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M21">
-        <v>306.6908598000001</v>
+        <v>285.3731448</v>
       </c>
       <c r="N21">
-        <v>-243.4908598</v>
+        <v>-222.1731448</v>
       </c>
       <c r="O21">
-        <v>-62.82064182840001</v>
+        <v>-57.32067135840001</v>
       </c>
       <c r="P21">
-        <v>-180.6702179716</v>
+        <v>-164.8524734416</v>
       </c>
       <c r="Q21">
-        <v>1.52978202839995</v>
+        <v>17.34752655839998</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
+      <c r="S21">
+        <v>0.1133898170675917</v>
+      </c>
       <c r="T21">
-        <v>1.562156585623737</v>
+        <v>1.560965752138377</v>
       </c>
       <c r="U21">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V21">
-        <v>0.05316624046322492</v>
+        <v>0.05713782217113515</v>
       </c>
       <c r="W21">
-        <v>0.2043267253080361</v>
+        <v>0.1893267253080361</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -2786,7 +3425,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.206070699469864</v>
+        <v>0.2214644270199037</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -2796,6 +3435,15 @@
       <c r="A22">
         <v>0.2</v>
       </c>
+      <c r="B22">
+        <v>0.1293678296332761</v>
+      </c>
+      <c r="C22">
+        <v>3444.638756795928</v>
+      </c>
+      <c r="D22">
+        <v>4678.918756795928</v>
+      </c>
       <c r="E22">
         <v>1032.98</v>
       </c>
@@ -2821,42 +3469,45 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M22">
-        <v>367.7118840000001</v>
+        <v>300.392784</v>
       </c>
       <c r="N22">
-        <v>-304.511884</v>
+        <v>-237.192784</v>
       </c>
       <c r="O22">
-        <v>-78.564066072</v>
+        <v>-61.195738272</v>
       </c>
       <c r="P22">
-        <v>-225.947817928</v>
+        <v>-175.997045728</v>
       </c>
       <c r="Q22">
-        <v>-43.74781792800002</v>
+        <v>6.202954271999999</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
+      <c r="S22">
+        <v>0.1142346897809366</v>
+      </c>
       <c r="T22">
-        <v>1.583653505156471</v>
+        <v>1.580477824040107</v>
       </c>
       <c r="U22">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V22">
-        <v>0.04434341317073125</v>
+        <v>0.05428093106257841</v>
       </c>
       <c r="W22">
-        <v>0.2349003890426343</v>
+        <v>0.1899003890426343</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y22">
-        <v>0.1718736944601987</v>
+        <v>0.2103912056689086</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -2866,6 +3517,15 @@
       <c r="A23">
         <v>0.21</v>
       </c>
+      <c r="B23">
+        <v>0.1309178296332761</v>
+      </c>
+      <c r="C23">
+        <v>3284.636408633977</v>
+      </c>
+      <c r="D23">
+        <v>4593.715408633977</v>
+      </c>
       <c r="E23">
         <v>1107.779</v>
       </c>
@@ -2891,42 +3551,45 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M23">
-        <v>386.0974782</v>
+        <v>315.4124232</v>
       </c>
       <c r="N23">
-        <v>-322.8974781999999</v>
+        <v>-252.2124232</v>
       </c>
       <c r="O23">
-        <v>-83.30754937559998</v>
+        <v>-65.07080518559999</v>
       </c>
       <c r="P23">
-        <v>-239.5899288243999</v>
+        <v>-187.1416180144</v>
       </c>
       <c r="Q23">
-        <v>-57.38992882439993</v>
+        <v>-4.941618014399978</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
+      <c r="S23">
+        <v>0.1151009516768979</v>
+      </c>
       <c r="T23">
-        <v>1.603699752057186</v>
+        <v>1.600483872445678</v>
       </c>
       <c r="U23">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V23">
-        <v>0.04223182206736311</v>
+        <v>0.05169612482150324</v>
       </c>
       <c r="W23">
-        <v>0.2354194181358422</v>
+        <v>0.1904194181358422</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y23">
-        <v>0.163689232819237</v>
+        <v>0.200372576827532</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -2936,6 +3599,15 @@
       <c r="A24">
         <v>0.22</v>
       </c>
+      <c r="B24">
+        <v>0.140257018034376</v>
+      </c>
+      <c r="C24">
+        <v>2755.645919689714</v>
+      </c>
+      <c r="D24">
+        <v>4139.523919689715</v>
+      </c>
       <c r="E24">
         <v>1182.578</v>
       </c>
@@ -2961,34 +3633,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M24">
-        <v>404.4830724</v>
+        <v>388.0272924</v>
       </c>
       <c r="N24">
-        <v>-341.2830724</v>
+        <v>-324.8272924</v>
       </c>
       <c r="O24">
-        <v>-88.05103267920001</v>
+        <v>-83.80544143920001</v>
       </c>
       <c r="P24">
-        <v>-253.2320397208</v>
+        <v>-241.0218509608</v>
       </c>
       <c r="Q24">
-        <v>-71.03203972080004</v>
+        <v>-58.82185096080002</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
+      <c r="S24">
+        <v>0.1161037695203195</v>
+      </c>
       <c r="T24">
-        <v>1.624260005288688</v>
+        <v>1.623643637882667</v>
       </c>
       <c r="U24">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.04031219379157387</v>
+        <v>0.04202178640359991</v>
       </c>
       <c r="W24">
-        <v>0.2358912627660311</v>
+        <v>0.2258912627660312</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -2996,7 +3671,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.1562488131456351</v>
+        <v>0.1628751410992244</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3006,6 +3681,15 @@
       <c r="A25">
         <v>0.23</v>
       </c>
+      <c r="B25">
+        <v>0.1421570180343761</v>
+      </c>
+      <c r="C25">
+        <v>2599.222398634024</v>
+      </c>
+      <c r="D25">
+        <v>4057.899398634023</v>
+      </c>
       <c r="E25">
         <v>1257.377</v>
       </c>
@@ -3031,34 +3715,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M25">
-        <v>422.8686666</v>
+        <v>405.6648966</v>
       </c>
       <c r="N25">
-        <v>-359.6686666000001</v>
+        <v>-342.4648966</v>
       </c>
       <c r="O25">
-        <v>-92.79451598280002</v>
+        <v>-88.3559433228</v>
       </c>
       <c r="P25">
-        <v>-266.8741506172</v>
+        <v>-254.1089532772</v>
       </c>
       <c r="Q25">
-        <v>-84.67415061720004</v>
+        <v>-71.9089532772</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
+      <c r="S25">
+        <v>0.1170168054881158</v>
+      </c>
       <c r="T25">
-        <v>1.645354291071658</v>
+        <v>1.64472991889413</v>
       </c>
       <c r="U25">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.03855948971367935</v>
+        <v>0.04019475221213904</v>
       </c>
       <c r="W25">
-        <v>0.2363220774283776</v>
+        <v>0.2263220774283776</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3066,7 +3753,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.1494553864871292</v>
+        <v>0.1557936132253451</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3076,6 +3763,15 @@
       <c r="A26">
         <v>0.24</v>
       </c>
+      <c r="B26">
+        <v>0.144057018034376</v>
+      </c>
+      <c r="C26">
+        <v>2445.955631021667</v>
+      </c>
+      <c r="D26">
+        <v>3979.431631021667</v>
+      </c>
       <c r="E26">
         <v>1332.176</v>
       </c>
@@ -3101,34 +3797,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M26">
-        <v>441.2542608</v>
+        <v>423.3025008</v>
       </c>
       <c r="N26">
-        <v>-378.0542608</v>
+        <v>-360.1025008</v>
       </c>
       <c r="O26">
-        <v>-97.53799928639999</v>
+        <v>-92.90644520640001</v>
       </c>
       <c r="P26">
-        <v>-280.5162615135999</v>
+        <v>-267.1960555936</v>
       </c>
       <c r="Q26">
-        <v>-98.31626151359995</v>
+        <v>-84.99605559360003</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
+      <c r="S26">
+        <v>0.1179538687182226</v>
+      </c>
       <c r="T26">
-        <v>1.667003689638391</v>
+        <v>1.666371102037474</v>
       </c>
       <c r="U26">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.03695284430894272</v>
+        <v>0.03851997086996658</v>
       </c>
       <c r="W26">
-        <v>0.2367169908688619</v>
+        <v>0.2267169908688619</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3136,7 +3835,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.1432280787168323</v>
+        <v>0.149302212674289</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3146,6 +3845,15 @@
       <c r="A27">
         <v>0.25</v>
       </c>
+      <c r="B27">
+        <v>0.1459570180343761</v>
+      </c>
+      <c r="C27">
+        <v>2295.665963993759</v>
+      </c>
+      <c r="D27">
+        <v>3903.940963993759</v>
+      </c>
       <c r="E27">
         <v>1406.975</v>
       </c>
@@ -3171,34 +3879,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M27">
-        <v>459.639855</v>
+        <v>440.940105</v>
       </c>
       <c r="N27">
-        <v>-396.439855</v>
+        <v>-377.740105</v>
       </c>
       <c r="O27">
-        <v>-102.28148259</v>
+        <v>-97.45694709</v>
       </c>
       <c r="P27">
-        <v>-294.15837241</v>
+        <v>-280.28315791</v>
       </c>
       <c r="Q27">
-        <v>-111.95837241</v>
+        <v>-98.08315791000001</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
+      <c r="S27">
+        <v>0.1189159203011323</v>
+      </c>
       <c r="T27">
-        <v>1.689230405500236</v>
+        <v>1.688589383397974</v>
       </c>
       <c r="U27">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.03547473053658501</v>
+        <v>0.03697917203516791</v>
       </c>
       <c r="W27">
-        <v>0.2370803112341074</v>
+        <v>0.2270803112341074</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3206,7 +3917,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.1374989555681589</v>
+        <v>0.1433301241673176</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3216,6 +3927,15 @@
       <c r="A28">
         <v>0.26</v>
       </c>
+      <c r="B28">
+        <v>0.1478570180343761</v>
+      </c>
+      <c r="C28">
+        <v>2148.187123112167</v>
+      </c>
+      <c r="D28">
+        <v>3831.261123112167</v>
+      </c>
       <c r="E28">
         <v>1481.774</v>
       </c>
@@ -3241,34 +3961,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M28">
-        <v>478.0254492</v>
+        <v>458.5777092</v>
       </c>
       <c r="N28">
-        <v>-414.8254492</v>
+        <v>-395.3777092</v>
       </c>
       <c r="O28">
-        <v>-107.0249658936</v>
+        <v>-102.0074489736</v>
       </c>
       <c r="P28">
-        <v>-307.8004833064</v>
+        <v>-293.3702602264</v>
       </c>
       <c r="Q28">
-        <v>-125.6004833064</v>
+        <v>-111.1702602264</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
+      <c r="S28">
+        <v>0.1199039732781746</v>
+      </c>
       <c r="T28">
-        <v>1.712057843412401</v>
+        <v>1.711408158849298</v>
       </c>
       <c r="U28">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.03411031782363943</v>
+        <v>0.03555689618766146</v>
       </c>
       <c r="W28">
-        <v>0.2374156838789495</v>
+        <v>0.2274156838789494</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3276,7 +3999,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.1322105342001528</v>
+        <v>0.1378174270839591</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3286,6 +4009,15 @@
       <c r="A29">
         <v>0.27</v>
       </c>
+      <c r="B29">
+        <v>0.149757018034376</v>
+      </c>
+      <c r="C29">
+        <v>2003.364989786951</v>
+      </c>
+      <c r="D29">
+        <v>3761.237989786951</v>
+      </c>
       <c r="E29">
         <v>1556.573</v>
       </c>
@@ -3311,34 +4043,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M29">
-        <v>496.4110434</v>
+        <v>476.2153134</v>
       </c>
       <c r="N29">
-        <v>-433.2110434</v>
+        <v>-413.0153134</v>
       </c>
       <c r="O29">
-        <v>-111.7684491972</v>
+        <v>-106.5579508572</v>
       </c>
       <c r="P29">
-        <v>-321.4425942028</v>
+        <v>-306.4573625428</v>
       </c>
       <c r="Q29">
-        <v>-139.2425942028</v>
+        <v>-124.2573625428</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
+      <c r="S29">
+        <v>0.1209190961997934</v>
+      </c>
       <c r="T29">
-        <v>1.735510690582434</v>
+        <v>1.734852106230795</v>
       </c>
       <c r="U29">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.03284697271906019</v>
+        <v>0.03423997410663696</v>
       </c>
       <c r="W29">
-        <v>0.237726214105655</v>
+        <v>0.227726214105655</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3346,7 +4081,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.1273138477482954</v>
+        <v>0.1327130779327015</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3356,6 +4091,15 @@
       <c r="A30">
         <v>0.28</v>
       </c>
+      <c r="B30">
+        <v>0.1516570180343761</v>
+      </c>
+      <c r="C30">
+        <v>1861.056510365618</v>
+      </c>
+      <c r="D30">
+        <v>3693.728510365618</v>
+      </c>
       <c r="E30">
         <v>1631.372</v>
       </c>
@@ -3381,34 +4125,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M30">
-        <v>514.7966376000002</v>
+        <v>493.8529176000001</v>
       </c>
       <c r="N30">
-        <v>-451.5966376000001</v>
+        <v>-430.6529176</v>
       </c>
       <c r="O30">
-        <v>-116.5119325008</v>
+        <v>-111.1084527408</v>
       </c>
       <c r="P30">
-        <v>-335.0847050992001</v>
+        <v>-319.5444648592</v>
       </c>
       <c r="Q30">
-        <v>-152.8847050992001</v>
+        <v>-137.3444648592001</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
+      <c r="S30">
+        <v>0.1219624169803461</v>
+      </c>
       <c r="T30">
-        <v>1.759615005729412</v>
+        <v>1.75894727437289</v>
       </c>
       <c r="U30">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.03167386655052232</v>
+        <v>0.03301711788854278</v>
       </c>
       <c r="W30">
-        <v>0.2380145636018816</v>
+        <v>0.2280145636018816</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3416,7 +4163,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.1227669246144276</v>
+        <v>0.1279733251493906</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3426,6 +4173,15 @@
       <c r="A31">
         <v>0.29</v>
       </c>
+      <c r="B31">
+        <v>0.153557018034376</v>
+      </c>
+      <c r="C31">
+        <v>1721.128720633745</v>
+      </c>
+      <c r="D31">
+        <v>3628.599720633745</v>
+      </c>
       <c r="E31">
         <v>1706.171</v>
       </c>
@@ -3451,34 +4207,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M31">
-        <v>533.1822318</v>
+        <v>511.4905218</v>
       </c>
       <c r="N31">
-        <v>-469.9822317999999</v>
+        <v>-448.2905218</v>
       </c>
       <c r="O31">
-        <v>-121.2554158044</v>
+        <v>-115.6589546244</v>
       </c>
       <c r="P31">
-        <v>-348.7268159956</v>
+        <v>-332.6315671756</v>
       </c>
       <c r="Q31">
-        <v>-166.5268159956</v>
+        <v>-150.4315671756</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
+      <c r="S31">
+        <v>0.1230351270786608</v>
+      </c>
       <c r="T31">
-        <v>1.784398315669263</v>
+        <v>1.783721179645747</v>
       </c>
       <c r="U31">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.03058166425567673</v>
+        <v>0.03187859658204131</v>
       </c>
       <c r="W31">
-        <v>0.2382830269259547</v>
+        <v>0.2282830269259547</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3486,7 +4245,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.1185335823863439</v>
+        <v>0.1235604518683772</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3496,6 +4255,15 @@
       <c r="A32">
         <v>0.3</v>
       </c>
+      <c r="B32">
+        <v>0.1554570180343761</v>
+      </c>
+      <c r="C32">
+        <v>1583.457871728982</v>
+      </c>
+      <c r="D32">
+        <v>3565.727871728982</v>
+      </c>
       <c r="E32">
         <v>1780.97</v>
       </c>
@@ -3521,34 +4289,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M32">
-        <v>551.567826</v>
+        <v>529.128126</v>
       </c>
       <c r="N32">
-        <v>-488.3678259999999</v>
+        <v>-465.9281259999999</v>
       </c>
       <c r="O32">
-        <v>-125.998899108</v>
+        <v>-120.209456508</v>
       </c>
       <c r="P32">
-        <v>-362.3689268919999</v>
+        <v>-345.7186694919999</v>
       </c>
       <c r="Q32">
-        <v>-180.1689268919999</v>
+        <v>-163.518669492</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
+      <c r="S32">
+        <v>0.1241384860369274</v>
+      </c>
       <c r="T32">
-        <v>1.809889720178824</v>
+        <v>1.809202910783543</v>
       </c>
       <c r="U32">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.02956227544715417</v>
+        <v>0.03081597669597327</v>
       </c>
       <c r="W32">
-        <v>0.2385335926950895</v>
+        <v>0.2285335926950895</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3556,7 +4327,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.1145824629734659</v>
+        <v>0.1194417701394314</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3566,6 +4337,15 @@
       <c r="A33">
         <v>0.31</v>
       </c>
+      <c r="B33">
+        <v>0.157357018034376</v>
+      </c>
+      <c r="C33">
+        <v>1447.92864537785</v>
+      </c>
+      <c r="D33">
+        <v>3504.997645377849</v>
+      </c>
       <c r="E33">
         <v>1855.769</v>
       </c>
@@ -3591,34 +4371,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M33">
-        <v>569.9534202</v>
+        <v>546.7657302</v>
       </c>
       <c r="N33">
-        <v>-506.7534201999999</v>
+        <v>-483.5657302</v>
       </c>
       <c r="O33">
-        <v>-130.7423824116</v>
+        <v>-124.7599583916</v>
       </c>
       <c r="P33">
-        <v>-376.0110377884</v>
+        <v>-358.8057718084</v>
       </c>
       <c r="Q33">
-        <v>-193.8110377884</v>
+        <v>-176.6057718084</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
+      <c r="S33">
+        <v>0.1252738264142742</v>
+      </c>
       <c r="T33">
-        <v>1.836120005978517</v>
+        <v>1.835423242823885</v>
       </c>
       <c r="U33">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.0286086536585363</v>
+        <v>0.02982191293158703</v>
       </c>
       <c r="W33">
-        <v>0.2387679929307318</v>
+        <v>0.2287679929307318</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -3626,7 +4409,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.1108862544904509</v>
+        <v>0.1155888098123529</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -3636,6 +4419,15 @@
       <c r="A34">
         <v>0.32</v>
       </c>
+      <c r="B34">
+        <v>0.159257018034376</v>
+      </c>
+      <c r="C34">
+        <v>1314.433447984401</v>
+      </c>
+      <c r="D34">
+        <v>3446.301447984401</v>
+      </c>
       <c r="E34">
         <v>1930.568</v>
       </c>
@@ -3661,34 +4453,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M34">
-        <v>588.3390144</v>
+        <v>564.4033343999999</v>
       </c>
       <c r="N34">
-        <v>-525.1390144</v>
+        <v>-501.2033343999999</v>
       </c>
       <c r="O34">
-        <v>-135.4858657152</v>
+        <v>-129.3104602752</v>
       </c>
       <c r="P34">
-        <v>-389.6531486847999</v>
+        <v>-371.8928741248</v>
       </c>
       <c r="Q34">
-        <v>-207.4531486847999</v>
+        <v>-189.6928741248</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
+      <c r="S34">
+        <v>0.1264425591556606</v>
+      </c>
       <c r="T34">
-        <v>1.863121770772319</v>
+        <v>1.862414761100706</v>
       </c>
       <c r="U34">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.02771463323170703</v>
+        <v>0.02888997815247494</v>
       </c>
       <c r="W34">
-        <v>0.2389877431516464</v>
+        <v>0.2289877431516464</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -3696,7 +4491,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.1074210590376242</v>
+        <v>0.1119766595057169</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -3706,6 +4501,15 @@
       <c r="A35">
         <v>0.33</v>
       </c>
+      <c r="B35">
+        <v>0.161157018034376</v>
+      </c>
+      <c r="C35">
+        <v>1182.871774479619</v>
+      </c>
+      <c r="D35">
+        <v>3389.53877447962</v>
+      </c>
       <c r="E35">
         <v>2005.367</v>
       </c>
@@ -3731,34 +4535,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M35">
-        <v>606.7246086000001</v>
+        <v>582.0409386000001</v>
       </c>
       <c r="N35">
-        <v>-543.5246086000001</v>
+        <v>-518.8409386000001</v>
       </c>
       <c r="O35">
-        <v>-140.2293490188</v>
+        <v>-133.8609621588</v>
       </c>
       <c r="P35">
-        <v>-403.2952595812001</v>
+        <v>-384.9799764412001</v>
       </c>
       <c r="Q35">
-        <v>-221.0952595812001</v>
+        <v>-202.7799764412001</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
+      <c r="S35">
+        <v>0.127646179441566</v>
+      </c>
       <c r="T35">
-        <v>1.890929558395786</v>
+        <v>1.890211996341016</v>
       </c>
       <c r="U35">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.02687479586104924</v>
+        <v>0.0280145242690666</v>
       </c>
       <c r="W35">
-        <v>0.2391941751773541</v>
+        <v>0.2291941751773541</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -3766,7 +4573,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.1041658754304234</v>
+        <v>0.108583427399483</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -3776,6 +4583,15 @@
       <c r="A36">
         <v>0.34</v>
       </c>
+      <c r="B36">
+        <v>0.1630570180343761</v>
+      </c>
+      <c r="C36">
+        <v>1053.149634018864</v>
+      </c>
+      <c r="D36">
+        <v>3334.615634018865</v>
+      </c>
       <c r="E36">
         <v>2080.166</v>
       </c>
@@ -3801,34 +4617,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M36">
-        <v>625.1102028000001</v>
+        <v>599.6785428000001</v>
       </c>
       <c r="N36">
-        <v>-561.9102028000001</v>
+        <v>-536.4785428</v>
       </c>
       <c r="O36">
-        <v>-144.9728323224</v>
+        <v>-138.4114640424</v>
       </c>
       <c r="P36">
-        <v>-416.9373704776001</v>
+        <v>-398.0670787576</v>
       </c>
       <c r="Q36">
-        <v>-234.7373704776001</v>
+        <v>-215.8670787576</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
+      <c r="S36">
+        <v>0.1288862730694685</v>
+      </c>
       <c r="T36">
-        <v>1.919580006250268</v>
+        <v>1.918851572043152</v>
       </c>
       <c r="U36">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.02608436068866544</v>
+        <v>0.02719056767291759</v>
       </c>
       <c r="W36">
-        <v>0.239388464142726</v>
+        <v>0.229388464142726</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -3836,7 +4655,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.1011021732118816</v>
+        <v>0.1053897971818512</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -3846,6 +4665,15 @@
       <c r="A37">
         <v>0.35</v>
       </c>
+      <c r="B37">
+        <v>0.1649570180343761</v>
+      </c>
+      <c r="C37">
+        <v>925.1790306240218</v>
+      </c>
+      <c r="D37">
+        <v>3281.444030624022</v>
+      </c>
       <c r="E37">
         <v>2154.965</v>
       </c>
@@ -3871,34 +4699,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M37">
-        <v>643.495797</v>
+        <v>617.3161470000001</v>
       </c>
       <c r="N37">
-        <v>-580.295797</v>
+        <v>-554.1161470000001</v>
       </c>
       <c r="O37">
-        <v>-149.716315626</v>
+        <v>-142.961965926</v>
       </c>
       <c r="P37">
-        <v>-430.579481374</v>
+        <v>-411.154181074</v>
       </c>
       <c r="Q37">
-        <v>-248.379481374</v>
+        <v>-228.954181074</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
+      <c r="S37">
+        <v>0.1301645234243834</v>
+      </c>
       <c r="T37">
-        <v>1.949112006346426</v>
+        <v>1.948372365459201</v>
       </c>
       <c r="U37">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.02533909324041786</v>
+        <v>0.02641369431083422</v>
       </c>
       <c r="W37">
-        <v>0.2395716508815053</v>
+        <v>0.2295716508815053</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -3906,7 +4737,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.09821353969154212</v>
+        <v>0.1023786601195126</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -3916,6 +4747,15 @@
       <c r="A38">
         <v>0.36</v>
       </c>
+      <c r="B38">
+        <v>0.1668570180343761</v>
+      </c>
+      <c r="C38">
+        <v>798.87749273386</v>
+      </c>
+      <c r="D38">
+        <v>3229.94149273386</v>
+      </c>
       <c r="E38">
         <v>2229.764</v>
       </c>
@@ -3941,34 +4781,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M38">
-        <v>661.8813911999999</v>
+        <v>634.9537511999999</v>
       </c>
       <c r="N38">
-        <v>-598.6813911999999</v>
+        <v>-571.7537511999999</v>
       </c>
       <c r="O38">
-        <v>-154.4597989296</v>
+        <v>-147.5124678096</v>
       </c>
       <c r="P38">
-        <v>-444.2215922703999</v>
+        <v>-424.2412833903999</v>
       </c>
       <c r="Q38">
-        <v>-262.0215922703999</v>
+        <v>-242.0412833903999</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
+      <c r="S38">
+        <v>0.1314827191028894</v>
+      </c>
       <c r="T38">
-        <v>1.979566881445589</v>
+        <v>1.978815683669501</v>
       </c>
       <c r="U38">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.02463522953929515</v>
+        <v>0.02567998057997772</v>
       </c>
       <c r="W38">
-        <v>0.2397446605792413</v>
+        <v>0.2297446605792413</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -3976,7 +4819,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.09548538581122157</v>
+        <v>0.09953480844952611</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -3986,6 +4829,15 @@
       <c r="A39">
         <v>0.37</v>
       </c>
+      <c r="B39">
+        <v>0.168757018034376</v>
+      </c>
+      <c r="C39">
+        <v>674.1676463722597</v>
+      </c>
+      <c r="D39">
+        <v>3180.03064637226</v>
+      </c>
       <c r="E39">
         <v>2304.563</v>
       </c>
@@ -4011,34 +4863,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M39">
-        <v>680.2669854</v>
+        <v>652.5913554</v>
       </c>
       <c r="N39">
-        <v>-617.0669853999999</v>
+        <v>-589.3913554</v>
       </c>
       <c r="O39">
-        <v>-159.2032822332</v>
+        <v>-152.0629696932</v>
       </c>
       <c r="P39">
-        <v>-457.8637031668</v>
+        <v>-437.3283857068</v>
       </c>
       <c r="Q39">
-        <v>-275.6637031668</v>
+        <v>-255.1283857068</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
+      <c r="S39">
+        <v>0.1328427622632527</v>
+      </c>
       <c r="T39">
-        <v>2.010988577976471</v>
+        <v>2.010225456426159</v>
       </c>
       <c r="U39">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.0239694125247196</v>
+        <v>0.02498592705078913</v>
       </c>
       <c r="W39">
-        <v>0.2399083184014239</v>
+        <v>0.2299083184014239</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4046,7 +4901,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.09290469970821558</v>
+        <v>0.09684467849143075</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4056,6 +4911,15 @@
       <c r="A40">
         <v>0.38</v>
       </c>
+      <c r="B40">
+        <v>0.1706570180343761</v>
+      </c>
+      <c r="C40">
+        <v>550.9768272880979</v>
+      </c>
+      <c r="D40">
+        <v>3131.638827288098</v>
+      </c>
       <c r="E40">
         <v>2379.362</v>
       </c>
@@ -4081,34 +4945,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M40">
-        <v>698.6525796000001</v>
+        <v>670.2289596000001</v>
       </c>
       <c r="N40">
-        <v>-635.4525796</v>
+        <v>-607.0289596</v>
       </c>
       <c r="O40">
-        <v>-163.9467655368</v>
+        <v>-156.6134715768</v>
       </c>
       <c r="P40">
-        <v>-471.5058140632</v>
+        <v>-450.4154880232</v>
       </c>
       <c r="Q40">
-        <v>-289.3058140632</v>
+        <v>-268.2154880232</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
+      <c r="S40">
+        <v>0.1342466777836277</v>
+      </c>
       <c r="T40">
-        <v>2.043423877621253</v>
+        <v>2.042648447658839</v>
       </c>
       <c r="U40">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.02333863851091119</v>
+        <v>0.02432840265471574</v>
       </c>
       <c r="W40">
-        <v>0.240063362654018</v>
+        <v>0.2300633626540181</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4116,7 +4983,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.09045983918957823</v>
+        <v>0.09429613432060369</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4126,6 +4993,15 @@
       <c r="A41">
         <v>0.39</v>
       </c>
+      <c r="B41">
+        <v>0.1725570180343761</v>
+      </c>
+      <c r="C41">
+        <v>429.236727977654</v>
+      </c>
+      <c r="D41">
+        <v>3084.697727977654</v>
+      </c>
       <c r="E41">
         <v>2454.161</v>
       </c>
@@ -4151,34 +5027,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M41">
-        <v>717.0381738000001</v>
+        <v>687.8665638</v>
       </c>
       <c r="N41">
-        <v>-653.8381738</v>
+        <v>-624.6665637999999</v>
       </c>
       <c r="O41">
-        <v>-168.6902488404</v>
+        <v>-161.1639734604</v>
       </c>
       <c r="P41">
-        <v>-485.1479249596</v>
+        <v>-463.5025903395999</v>
       </c>
       <c r="Q41">
-        <v>-302.9479249596</v>
+        <v>-281.3025903395999</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
+      <c r="S41">
+        <v>0.1356966233210642</v>
+      </c>
       <c r="T41">
-        <v>2.076922629713405</v>
+        <v>2.076134487784394</v>
       </c>
       <c r="U41">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.02274021188242628</v>
+        <v>0.02370459745844097</v>
       </c>
       <c r="W41">
-        <v>0.2402104559192997</v>
+        <v>0.2302104559192996</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4186,7 +5065,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.08814035613343529</v>
+        <v>0.09187828472263948</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4196,6 +5075,15 @@
       <c r="A42">
         <v>0.4</v>
       </c>
+      <c r="B42">
+        <v>0.1744570180343761</v>
+      </c>
+      <c r="C42">
+        <v>308.8830759835309</v>
+      </c>
+      <c r="D42">
+        <v>3039.143075983531</v>
+      </c>
       <c r="E42">
         <v>2528.96</v>
       </c>
@@ -4221,34 +5109,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M42">
-        <v>735.4237680000001</v>
+        <v>705.504168</v>
       </c>
       <c r="N42">
-        <v>-672.2237680000001</v>
+        <v>-642.304168</v>
       </c>
       <c r="O42">
-        <v>-173.433732144</v>
+        <v>-165.714475344</v>
       </c>
       <c r="P42">
-        <v>-498.790035856</v>
+        <v>-476.589692656</v>
       </c>
       <c r="Q42">
-        <v>-316.590035856</v>
+        <v>-294.389692656</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
+      <c r="S42">
+        <v>0.1371949003764154</v>
+      </c>
       <c r="T42">
-        <v>2.111538006875295</v>
+        <v>2.110736729247467</v>
       </c>
       <c r="U42">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.02217170658536563</v>
+        <v>0.02311198252197995</v>
       </c>
       <c r="W42">
-        <v>0.2403501945213171</v>
+        <v>0.2303501945213171</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4256,7 +5147,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.08593684723009931</v>
+        <v>0.08958132760457349</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4266,6 +5157,15 @@
       <c r="A43">
         <v>0.41</v>
       </c>
+      <c r="B43">
+        <v>0.176357018034376</v>
+      </c>
+      <c r="C43">
+        <v>189.8553402839443</v>
+      </c>
+      <c r="D43">
+        <v>2994.914340283945</v>
+      </c>
       <c r="E43">
         <v>2603.759</v>
       </c>
@@ -4291,34 +5191,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M43">
-        <v>753.8093622</v>
+        <v>723.1417722</v>
       </c>
       <c r="N43">
-        <v>-690.6093622</v>
+        <v>-659.9417721999999</v>
       </c>
       <c r="O43">
-        <v>-178.1772154476</v>
+        <v>-170.2649772276</v>
       </c>
       <c r="P43">
-        <v>-512.4321467523999</v>
+        <v>-489.6767949724</v>
       </c>
       <c r="Q43">
-        <v>-330.2321467524</v>
+        <v>-307.4767949724</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
+      <c r="S43">
+        <v>0.1387439664844902</v>
+      </c>
       <c r="T43">
-        <v>2.147326786652842</v>
+        <v>2.146511928048272</v>
       </c>
       <c r="U43">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.02163093325401525</v>
+        <v>0.02254827563119995</v>
       </c>
       <c r="W43">
-        <v>0.2404831166061631</v>
+        <v>0.2304831166061631</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4326,7 +5229,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.0838408265659506</v>
+        <v>0.08739641717519364</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4336,6 +5239,15 @@
       <c r="A44">
         <v>0.42</v>
       </c>
+      <c r="B44">
+        <v>0.178257018034376</v>
+      </c>
+      <c r="C44">
+        <v>72.09646295179209</v>
+      </c>
+      <c r="D44">
+        <v>2951.954462951792</v>
+      </c>
       <c r="E44">
         <v>2678.558</v>
       </c>
@@ -4361,34 +5273,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M44">
-        <v>772.1949563999999</v>
+        <v>740.7793763999999</v>
       </c>
       <c r="N44">
-        <v>-708.9949563999999</v>
+        <v>-677.5793763999999</v>
       </c>
       <c r="O44">
-        <v>-182.9206987512</v>
+        <v>-174.8154791112</v>
       </c>
       <c r="P44">
-        <v>-526.0742576487999</v>
+        <v>-502.7638972887999</v>
       </c>
       <c r="Q44">
-        <v>-343.8742576487999</v>
+        <v>-320.5638972887999</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
+      <c r="S44">
+        <v>0.1403464486652572</v>
+      </c>
       <c r="T44">
-        <v>2.184349662284788</v>
+        <v>2.183520754393931</v>
       </c>
       <c r="U44">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.02111591103368156</v>
+        <v>0.02201141192569519</v>
       </c>
       <c r="W44">
-        <v>0.2406097090679211</v>
+        <v>0.2306097090679211</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4396,7 +5311,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.08184461640961849</v>
+        <v>0.0853155500995938</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4406,6 +5321,15 @@
       <c r="A45">
         <v>0.43</v>
       </c>
+      <c r="B45">
+        <v>0.1801570180343761</v>
+      </c>
+      <c r="C45">
+        <v>-44.4473864179181</v>
+      </c>
+      <c r="D45">
+        <v>2910.209613582082</v>
+      </c>
       <c r="E45">
         <v>2753.357</v>
       </c>
@@ -4431,34 +5355,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M45">
-        <v>790.5805506</v>
+        <v>758.4169806</v>
       </c>
       <c r="N45">
-        <v>-727.3805506</v>
+        <v>-695.2169805999999</v>
       </c>
       <c r="O45">
-        <v>-187.6641820548</v>
+        <v>-179.3659809948</v>
       </c>
       <c r="P45">
-        <v>-539.7163685452</v>
+        <v>-515.8509996051999</v>
       </c>
       <c r="Q45">
-        <v>-357.5163685452</v>
+        <v>-333.6509996052</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
+      <c r="S45">
+        <v>0.1420051582909635</v>
+      </c>
       <c r="T45">
-        <v>2.222671586184521</v>
+        <v>2.221828136049965</v>
       </c>
       <c r="U45">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.02062484333522384</v>
+        <v>0.02149951862509763</v>
       </c>
       <c r="W45">
-        <v>0.240730413508202</v>
+        <v>0.230730413508202</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -4466,7 +5393,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.07994125323730172</v>
+        <v>0.08333146753913812</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -4476,6 +5403,15 @@
       <c r="A46">
         <v>0.44</v>
       </c>
+      <c r="B46">
+        <v>0.1820570180343761</v>
+      </c>
+      <c r="C46">
+        <v>-159.8270357347192</v>
+      </c>
+      <c r="D46">
+        <v>2869.628964265281</v>
+      </c>
       <c r="E46">
         <v>2828.156</v>
       </c>
@@ -4501,34 +5437,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M46">
-        <v>808.9661448000001</v>
+        <v>776.0545848</v>
       </c>
       <c r="N46">
-        <v>-745.7661448</v>
+        <v>-712.8545848</v>
       </c>
       <c r="O46">
-        <v>-192.4076653584</v>
+        <v>-183.9164828784</v>
       </c>
       <c r="P46">
-        <v>-553.3584794416</v>
+        <v>-528.9381019216</v>
       </c>
       <c r="Q46">
-        <v>-371.1584794416</v>
+        <v>-346.7381019216</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
+      <c r="S46">
+        <v>0.1437231075461593</v>
+      </c>
       <c r="T46">
-        <v>2.26236215022353</v>
+        <v>2.261503638479429</v>
       </c>
       <c r="U46">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.02015609689578694</v>
+        <v>0.02101089320179995</v>
       </c>
       <c r="W46">
-        <v>0.2408456313830156</v>
+        <v>0.2308456313830156</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -4536,7 +5475,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.07812440657281761</v>
+        <v>0.0814375705496122</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -4546,6 +5485,15 @@
       <c r="A47">
         <v>0.45</v>
       </c>
+      <c r="B47">
+        <v>0.1839570180343761</v>
+      </c>
+      <c r="C47">
+        <v>-274.0905168713002</v>
+      </c>
+      <c r="D47">
+        <v>2830.1644831287</v>
+      </c>
       <c r="E47">
         <v>2902.955</v>
       </c>
@@ -4571,34 +5519,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M47">
-        <v>827.3517390000001</v>
+        <v>793.692189</v>
       </c>
       <c r="N47">
-        <v>-764.151739</v>
+        <v>-730.4921889999999</v>
       </c>
       <c r="O47">
-        <v>-197.151148662</v>
+        <v>-188.466984762</v>
       </c>
       <c r="P47">
-        <v>-567.0005903380001</v>
+        <v>-542.025204238</v>
       </c>
       <c r="Q47">
-        <v>-384.8005903380001</v>
+        <v>-359.825204238</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
+      <c r="S47">
+        <v>0.1455035276833622</v>
+      </c>
       <c r="T47">
-        <v>2.303496007500322</v>
+        <v>2.302621886451782</v>
       </c>
       <c r="U47">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.01970818363143611</v>
+        <v>0.02054398446398218</v>
       </c>
       <c r="W47">
-        <v>0.240955728463393</v>
+        <v>0.230955728463393</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -4606,7 +5557,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.07638830864897717</v>
+        <v>0.07962784675962087</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -4616,6 +5567,15 @@
       <c r="A48">
         <v>0.46</v>
       </c>
+      <c r="B48">
+        <v>0.1858570180343761</v>
+      </c>
+      <c r="C48">
+        <v>-387.2832553173439</v>
+      </c>
+      <c r="D48">
+        <v>2791.770744682656</v>
+      </c>
       <c r="E48">
         <v>2977.754</v>
       </c>
@@ -4641,34 +5601,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M48">
-        <v>845.7373332000001</v>
+        <v>811.3297932</v>
       </c>
       <c r="N48">
-        <v>-782.5373332</v>
+        <v>-748.1297932</v>
       </c>
       <c r="O48">
-        <v>-201.8946319656</v>
+        <v>-193.0174866456</v>
       </c>
       <c r="P48">
-        <v>-580.6427012344</v>
+        <v>-555.1123065544</v>
       </c>
       <c r="Q48">
-        <v>-398.4427012344</v>
+        <v>-372.9123065544</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
+      <c r="S48">
+        <v>0.1473498893071281</v>
+      </c>
       <c r="T48">
-        <v>2.34615334097255</v>
+        <v>2.345263032497186</v>
       </c>
       <c r="U48">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.01927974485683968</v>
+        <v>0.02009737610606952</v>
       </c>
       <c r="W48">
-        <v>0.2410610387141888</v>
+        <v>0.2310610387141888</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -4676,7 +5639,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.07472769324356465</v>
+        <v>0.07789680661267262</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -4686,6 +5649,15 @@
       <c r="A49">
         <v>0.47</v>
       </c>
+      <c r="B49">
+        <v>0.1877570180343761</v>
+      </c>
+      <c r="C49">
+        <v>-499.4482446030052</v>
+      </c>
+      <c r="D49">
+        <v>2754.404755396995</v>
+      </c>
       <c r="E49">
         <v>3052.553</v>
       </c>
@@ -4711,34 +5683,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M49">
-        <v>864.1229274</v>
+        <v>828.9673974</v>
       </c>
       <c r="N49">
-        <v>-800.9229273999999</v>
+        <v>-765.7673973999999</v>
       </c>
       <c r="O49">
-        <v>-206.6381152692</v>
+        <v>-197.5679885292</v>
       </c>
       <c r="P49">
-        <v>-594.2848121308</v>
+        <v>-568.1994088708</v>
       </c>
       <c r="Q49">
-        <v>-412.0848121308</v>
+        <v>-385.9994088708</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
+      <c r="S49">
+        <v>0.1492659249544324</v>
+      </c>
       <c r="T49">
-        <v>2.390420385141844</v>
+        <v>2.389513278393359</v>
       </c>
       <c r="U49">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.01886953751946011</v>
+        <v>0.01966977235913187</v>
       </c>
       <c r="W49">
-        <v>0.2411618676777167</v>
+        <v>0.2311618676777167</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -4746,7 +5721,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.0731377423234888</v>
+        <v>0.07623942774857317</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -4756,6 +5731,15 @@
       <c r="A50">
         <v>0.48</v>
       </c>
+      <c r="B50">
+        <v>0.189657018034376</v>
+      </c>
+      <c r="C50">
+        <v>-610.6262069001641</v>
+      </c>
+      <c r="D50">
+        <v>2718.025793099836</v>
+      </c>
       <c r="E50">
         <v>3127.352</v>
       </c>
@@ -4781,34 +5765,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M50">
-        <v>882.5085216</v>
+        <v>846.6050016</v>
       </c>
       <c r="N50">
-        <v>-819.3085215999999</v>
+        <v>-783.4050016</v>
       </c>
       <c r="O50">
-        <v>-211.3815985728</v>
+        <v>-202.1184904128</v>
       </c>
       <c r="P50">
-        <v>-607.9269230272</v>
+        <v>-581.2865111871999</v>
       </c>
       <c r="Q50">
-        <v>-425.7269230272</v>
+        <v>-399.0865111872</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
+      <c r="S50">
+        <v>0.1512556542804792</v>
+      </c>
       <c r="T50">
-        <v>2.436390007933032</v>
+        <v>2.435465456824</v>
       </c>
       <c r="U50">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.01847642215447136</v>
+        <v>0.01925998543498329</v>
       </c>
       <c r="W50">
-        <v>0.241258495434431</v>
+        <v>0.2312584954344309</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -4816,7 +5803,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.07161403935841615</v>
+        <v>0.07465110633714456</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -4826,6 +5813,15 @@
       <c r="A51">
         <v>0.49</v>
       </c>
+      <c r="B51">
+        <v>0.191557018034376</v>
+      </c>
+      <c r="C51">
+        <v>-720.855741062654</v>
+      </c>
+      <c r="D51">
+        <v>2682.595258937346</v>
+      </c>
       <c r="E51">
         <v>3202.151</v>
       </c>
@@ -4851,34 +5847,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M51">
-        <v>900.8941158</v>
+        <v>864.2426058</v>
       </c>
       <c r="N51">
-        <v>-837.6941158</v>
+        <v>-801.0426057999999</v>
       </c>
       <c r="O51">
-        <v>-216.1250818764</v>
+        <v>-206.6689922964</v>
       </c>
       <c r="P51">
-        <v>-621.5690339235999</v>
+        <v>-594.3736135035999</v>
       </c>
       <c r="Q51">
-        <v>-439.3690339235999</v>
+        <v>-412.1736135035999</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
+      <c r="S51">
+        <v>0.1533234122075474</v>
+      </c>
       <c r="T51">
-        <v>2.484162361029759</v>
+        <v>2.483219681467608</v>
       </c>
       <c r="U51">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.01809935231458419</v>
+        <v>0.01886692450773873</v>
       </c>
       <c r="W51">
-        <v>0.2413511792010752</v>
+        <v>0.2313511792010752</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -4886,7 +5885,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.07015252835110153</v>
+        <v>0.0731276143710804</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -4896,6 +5895,15 @@
       <c r="A52">
         <v>0.5</v>
       </c>
+      <c r="B52">
+        <v>0.193457018034376</v>
+      </c>
+      <c r="C52">
+        <v>-830.1734592369189</v>
+      </c>
+      <c r="D52">
+        <v>2648.076540763081</v>
+      </c>
       <c r="E52">
         <v>3276.95</v>
       </c>
@@ -4921,34 +5929,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M52">
-        <v>919.27971</v>
+        <v>881.88021</v>
       </c>
       <c r="N52">
-        <v>-856.07971</v>
+        <v>-818.68021</v>
       </c>
       <c r="O52">
-        <v>-220.86856518</v>
+        <v>-211.21949418</v>
       </c>
       <c r="P52">
-        <v>-635.21114482</v>
+        <v>-607.46071582</v>
       </c>
       <c r="Q52">
-        <v>-453.01114482</v>
+        <v>-425.26071582</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
+      <c r="S52">
+        <v>0.1554738804516984</v>
+      </c>
       <c r="T52">
-        <v>2.533845608250354</v>
+        <v>2.532884075096961</v>
       </c>
       <c r="U52">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.0177373652682925</v>
+        <v>0.01848958601758396</v>
       </c>
       <c r="W52">
-        <v>0.2414401556170537</v>
+        <v>0.2314401556170537</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -4956,7 +5967,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.06874947778407947</v>
+        <v>0.07166506208365875</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -4966,6 +5977,15 @@
       <c r="A53">
         <v>0.51</v>
       </c>
+      <c r="B53">
+        <v>0.1953570180343761</v>
+      </c>
+      <c r="C53">
+        <v>-938.6141130594992</v>
+      </c>
+      <c r="D53">
+        <v>2614.434886940501</v>
+      </c>
       <c r="E53">
         <v>3351.749</v>
       </c>
@@ -4991,34 +6011,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M53">
-        <v>937.6653042</v>
+        <v>899.5178142</v>
       </c>
       <c r="N53">
-        <v>-874.4653042</v>
+        <v>-836.3178141999999</v>
       </c>
       <c r="O53">
-        <v>-225.6120484836</v>
+        <v>-215.7699960636</v>
       </c>
       <c r="P53">
-        <v>-648.8532557164</v>
+        <v>-620.5478181363999</v>
       </c>
       <c r="Q53">
-        <v>-466.6532557164</v>
+        <v>-438.3478181363999</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
+      <c r="S53">
+        <v>0.1577121229098963</v>
+      </c>
       <c r="T53">
-        <v>2.585556743112606</v>
+        <v>2.584575586833633</v>
       </c>
       <c r="U53">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.01738957379244363</v>
+        <v>0.01812704511527839</v>
       </c>
       <c r="W53">
-        <v>0.2415256427618174</v>
+        <v>0.2315256427618174</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5026,7 +6049,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.06740144880792109</v>
+        <v>0.07025986478790081</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5036,6 +6059,15 @@
       <c r="A54">
         <v>0.52</v>
       </c>
+      <c r="B54">
+        <v>0.1972570180343761</v>
+      </c>
+      <c r="C54">
+        <v>-1046.210710355781</v>
+      </c>
+      <c r="D54">
+        <v>2581.637289644219</v>
+      </c>
       <c r="E54">
         <v>3426.548</v>
       </c>
@@ -5061,34 +6093,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M54">
-        <v>956.0508984000001</v>
+        <v>917.1554184</v>
       </c>
       <c r="N54">
-        <v>-892.8508984</v>
+        <v>-853.9554184</v>
       </c>
       <c r="O54">
-        <v>-230.3555317872</v>
+        <v>-220.3204979472</v>
       </c>
       <c r="P54">
-        <v>-662.4953666128</v>
+        <v>-633.6349204528</v>
       </c>
       <c r="Q54">
-        <v>-480.2953666128</v>
+        <v>-451.4349204528</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
+      <c r="S54">
+        <v>0.1600436254705192</v>
+      </c>
       <c r="T54">
-        <v>2.639422508594119</v>
+        <v>2.638420911559334</v>
       </c>
       <c r="U54">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.01705515891181971</v>
+        <v>0.01777844809383073</v>
       </c>
       <c r="W54">
-        <v>0.2416078419394747</v>
+        <v>0.2316078419394747</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5096,7 +6131,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.06610526710007647</v>
+        <v>0.06890871354197958</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5106,6 +6141,15 @@
       <c r="A55">
         <v>0.53</v>
       </c>
+      <c r="B55">
+        <v>0.1991570180343761</v>
+      </c>
+      <c r="C55">
+        <v>-1152.994623163778</v>
+      </c>
+      <c r="D55">
+        <v>2549.652376836223</v>
+      </c>
       <c r="E55">
         <v>3501.347</v>
       </c>
@@ -5131,34 +6175,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M55">
-        <v>974.4364926000002</v>
+        <v>934.7930226000001</v>
       </c>
       <c r="N55">
-        <v>-911.2364926000001</v>
+        <v>-871.5930226</v>
       </c>
       <c r="O55">
-        <v>-235.0990150908</v>
+        <v>-224.8709998308</v>
       </c>
       <c r="P55">
-        <v>-676.1374775092002</v>
+        <v>-646.7220227692001</v>
       </c>
       <c r="Q55">
-        <v>-493.9374775092002</v>
+        <v>-464.5220227692001</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
+      <c r="S55">
+        <v>0.1624743409060621</v>
+      </c>
       <c r="T55">
-        <v>2.695580434308888</v>
+        <v>2.694557526698894</v>
       </c>
       <c r="U55">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.0167333634606533</v>
+        <v>0.017443005676966</v>
       </c>
       <c r="W55">
-        <v>0.2416869392613714</v>
+        <v>0.2316869392613714</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5166,7 +6213,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.06485799790950897</v>
+        <v>0.06760854913552716</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5176,6 +6223,15 @@
       <c r="A56">
         <v>0.54</v>
       </c>
+      <c r="B56">
+        <v>0.201057018034376</v>
+      </c>
+      <c r="C56">
+        <v>-1258.995687826105</v>
+      </c>
+      <c r="D56">
+        <v>2518.450312173895</v>
+      </c>
       <c r="E56">
         <v>3576.146</v>
       </c>
@@ -5201,34 +6257,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M56">
-        <v>992.8220868000001</v>
+        <v>952.4306268</v>
       </c>
       <c r="N56">
-        <v>-929.6220868</v>
+        <v>-889.2306268</v>
       </c>
       <c r="O56">
-        <v>-239.8424983944</v>
+        <v>-229.4215017144</v>
       </c>
       <c r="P56">
-        <v>-689.7795884056</v>
+        <v>-659.8091250856</v>
       </c>
       <c r="Q56">
-        <v>-507.5795884056</v>
+        <v>-477.6091250856001</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
+      <c r="S56">
+        <v>0.1650107396214113</v>
+      </c>
       <c r="T56">
-        <v>2.754180008967776</v>
+        <v>2.753134864235827</v>
       </c>
       <c r="U56">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.01642348635953009</v>
+        <v>0.01711998705331848</v>
       </c>
       <c r="W56">
-        <v>0.2417631070528275</v>
+        <v>0.2317631070528275</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5236,7 +6295,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.06365692387414768</v>
+        <v>0.06635653896635074</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5246,6 +6305,15 @@
       <c r="A57">
         <v>0.55</v>
       </c>
+      <c r="B57">
+        <v>0.202957018034376</v>
+      </c>
+      <c r="C57">
+        <v>-1364.242297821375</v>
+      </c>
+      <c r="D57">
+        <v>2488.002702178625</v>
+      </c>
       <c r="E57">
         <v>3650.945</v>
       </c>
@@ -5271,34 +6339,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M57">
-        <v>1011.207681</v>
+        <v>970.068231</v>
       </c>
       <c r="N57">
-        <v>-948.0076809999999</v>
+        <v>-906.8682309999999</v>
       </c>
       <c r="O57">
-        <v>-244.585981698</v>
+        <v>-233.972003598</v>
       </c>
       <c r="P57">
-        <v>-703.421699302</v>
+        <v>-672.8962274019999</v>
       </c>
       <c r="Q57">
-        <v>-521.2216993019999</v>
+        <v>-490.6962274019999</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
+      <c r="S57">
+        <v>0.1676598671685538</v>
+      </c>
       <c r="T57">
-        <v>2.81538400916706</v>
+        <v>2.814315638996623</v>
       </c>
       <c r="U57">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.01612487751662955</v>
+        <v>0.01680871456143996</v>
       </c>
       <c r="W57">
-        <v>0.2418365051064125</v>
+        <v>0.2318365051064125</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5306,7 +6377,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.06249952525825409</v>
+        <v>0.06515005643968985</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5316,6 +6387,15 @@
       <c r="A58">
         <v>0.5600000000000001</v>
       </c>
+      <c r="B58">
+        <v>0.2048570180343761</v>
+      </c>
+      <c r="C58">
+        <v>-1468.761489942153</v>
+      </c>
+      <c r="D58">
+        <v>2458.282510057848</v>
+      </c>
       <c r="E58">
         <v>3725.744000000001</v>
       </c>
@@ -5341,34 +6421,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M58">
-        <v>1029.5932752</v>
+        <v>987.7058352000001</v>
       </c>
       <c r="N58">
-        <v>-966.3932752000003</v>
+        <v>-924.5058352000001</v>
       </c>
       <c r="O58">
-        <v>-249.3294650016001</v>
+        <v>-238.5225054816</v>
       </c>
       <c r="P58">
-        <v>-717.0638101984002</v>
+        <v>-685.9833297184</v>
       </c>
       <c r="Q58">
-        <v>-534.8638101984002</v>
+        <v>-503.7833297184</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
+      <c r="S58">
+        <v>0.1704294096042027</v>
+      </c>
       <c r="T58">
-        <v>2.879370009375402</v>
+        <v>2.878277358064728</v>
       </c>
       <c r="U58">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.01583693327526116</v>
+        <v>0.01650855894427139</v>
       </c>
       <c r="W58">
-        <v>0.2419072818009408</v>
+        <v>0.2319072818009408</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -5376,7 +6459,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.06138346230721381</v>
+        <v>0.06398666257469532</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -5386,6 +6469,15 @@
       <c r="A59">
         <v>0.5700000000000001</v>
       </c>
+      <c r="B59">
+        <v>0.206757018034376</v>
+      </c>
+      <c r="C59">
+        <v>-1572.579024369228</v>
+      </c>
+      <c r="D59">
+        <v>2429.263975630773</v>
+      </c>
       <c r="E59">
         <v>3800.543000000001</v>
       </c>
@@ -5411,34 +6503,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M59">
-        <v>1047.9788694</v>
+        <v>1005.3434394</v>
       </c>
       <c r="N59">
-        <v>-984.7788694000001</v>
+        <v>-942.1434394000001</v>
       </c>
       <c r="O59">
-        <v>-254.0729483052</v>
+        <v>-243.0730073652001</v>
       </c>
       <c r="P59">
-        <v>-730.7059210948</v>
+        <v>-699.0704320348001</v>
       </c>
       <c r="Q59">
-        <v>-548.5059210948</v>
+        <v>-516.8704320348002</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
+      <c r="S59">
+        <v>0.1733277679670912</v>
+      </c>
       <c r="T59">
-        <v>2.946332102616691</v>
+        <v>2.94521404081042</v>
       </c>
       <c r="U59">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.01555909234060746</v>
+        <v>0.01621893510314382</v>
       </c>
       <c r="W59">
-        <v>0.2419755751026787</v>
+        <v>0.2319755751026787</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -5446,7 +6541,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.06030655945971886</v>
+        <v>0.06286408954706912</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -5456,6 +6551,15 @@
       <c r="A60">
         <v>0.58</v>
       </c>
+      <c r="B60">
+        <v>0.208657018034376</v>
+      </c>
+      <c r="C60">
+        <v>-1675.719459140703</v>
+      </c>
+      <c r="D60">
+        <v>2400.922540859297</v>
+      </c>
       <c r="E60">
         <v>3875.342</v>
       </c>
@@ -5481,34 +6585,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M60">
-        <v>1066.3644636</v>
+        <v>1022.9810436</v>
       </c>
       <c r="N60">
-        <v>-1003.1644636</v>
+        <v>-959.7810435999999</v>
       </c>
       <c r="O60">
-        <v>-258.8164316088</v>
+        <v>-247.6235092488</v>
       </c>
       <c r="P60">
-        <v>-744.3480319911998</v>
+        <v>-712.1575343512</v>
       </c>
       <c r="Q60">
-        <v>-562.1480319911998</v>
+        <v>-529.9575343511999</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
+      <c r="S60">
+        <v>0.176364143394879</v>
+      </c>
       <c r="T60">
-        <v>3.016482866964707</v>
+        <v>3.015338184639238</v>
       </c>
       <c r="U60">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.01529083212783837</v>
+        <v>0.01593929829102065</v>
       </c>
       <c r="W60">
-        <v>0.2420415134629774</v>
+        <v>0.2320415134629773</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -5516,7 +6623,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.05926679119317202</v>
+        <v>0.06178022593418864</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -5526,6 +6633,15 @@
       <c r="A61">
         <v>0.59</v>
       </c>
+      <c r="B61">
+        <v>0.210557018034376</v>
+      </c>
+      <c r="C61">
+        <v>-1778.206219468345</v>
+      </c>
+      <c r="D61">
+        <v>2373.234780531655</v>
+      </c>
       <c r="E61">
         <v>3950.141</v>
       </c>
@@ -5551,34 +6667,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M61">
-        <v>1084.7500578</v>
+        <v>1040.6186478</v>
       </c>
       <c r="N61">
-        <v>-1021.5500578</v>
+        <v>-977.4186477999999</v>
       </c>
       <c r="O61">
-        <v>-263.5599149124</v>
+        <v>-252.1740111324</v>
       </c>
       <c r="P61">
-        <v>-757.9901428875999</v>
+        <v>-725.2446366675999</v>
       </c>
       <c r="Q61">
-        <v>-575.7901428875998</v>
+        <v>-543.0446366675999</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
+      <c r="S61">
+        <v>0.1795486346971931</v>
+      </c>
       <c r="T61">
-        <v>3.090055619817504</v>
+        <v>3.088883018410927</v>
       </c>
       <c r="U61">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.01503166548160382</v>
+        <v>0.01566914069286776</v>
       </c>
       <c r="W61">
-        <v>0.2421052166246218</v>
+        <v>0.2321052166246218</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -5586,7 +6705,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.05826226930854195</v>
+        <v>0.0607331034607278</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -5596,6 +6715,15 @@
       <c r="A62">
         <v>0.6</v>
       </c>
+      <c r="B62">
+        <v>0.2124570180343761</v>
+      </c>
+      <c r="C62">
+        <v>-1880.061662312415</v>
+      </c>
+      <c r="D62">
+        <v>2346.178337687585</v>
+      </c>
       <c r="E62">
         <v>4024.94</v>
       </c>
@@ -5621,34 +6749,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M62">
-        <v>1103.135652</v>
+        <v>1058.256252</v>
       </c>
       <c r="N62">
-        <v>-1039.935652</v>
+        <v>-995.0562519999999</v>
       </c>
       <c r="O62">
-        <v>-268.303398216</v>
+        <v>-256.7245130159999</v>
       </c>
       <c r="P62">
-        <v>-771.6322537839999</v>
+        <v>-738.3317389839999</v>
       </c>
       <c r="Q62">
-        <v>-589.4322537839998</v>
+        <v>-556.1317389839999</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
+      <c r="S62">
+        <v>0.182892350564623</v>
+      </c>
       <c r="T62">
-        <v>3.167307010312942</v>
+        <v>3.166105093871201</v>
       </c>
       <c r="U62">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.01478113772357709</v>
+        <v>0.01540798834798663</v>
       </c>
       <c r="W62">
-        <v>0.2421667963475448</v>
+        <v>0.2321667963475448</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -5656,7 +6787,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.05729123148673287</v>
+        <v>0.05972088506971562</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -5666,6 +6797,15 @@
       <c r="A63">
         <v>0.61</v>
       </c>
+      <c r="B63">
+        <v>0.2143570180343761</v>
+      </c>
+      <c r="C63">
+        <v>-1981.307136589132</v>
+      </c>
+      <c r="D63">
+        <v>2319.731863410867</v>
+      </c>
       <c r="E63">
         <v>4099.739</v>
       </c>
@@ -5691,34 +6831,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M63">
-        <v>1121.5212462</v>
+        <v>1075.8938562</v>
       </c>
       <c r="N63">
-        <v>-1058.3212462</v>
+        <v>-1012.6938562</v>
       </c>
       <c r="O63">
-        <v>-273.0468815196</v>
+        <v>-261.2750148996</v>
       </c>
       <c r="P63">
-        <v>-785.2743646803999</v>
+        <v>-751.4188413003999</v>
       </c>
       <c r="Q63">
-        <v>-603.0743646803999</v>
+        <v>-569.2188413003998</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
+      <c r="S63">
+        <v>0.186407539040639</v>
+      </c>
       <c r="T63">
-        <v>3.248520010577377</v>
+        <v>3.247287275765334</v>
       </c>
       <c r="U63">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.01453882399040369</v>
+        <v>0.01515539837506882</v>
       </c>
       <c r="W63">
-        <v>0.2422263570631588</v>
+        <v>0.2322263570631588</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -5726,7 +6869,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.05635203097055697</v>
+        <v>0.05874185416693345</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -5736,6 +6879,15 @@
       <c r="A64">
         <v>0.62</v>
       </c>
+      <c r="B64">
+        <v>0.2162570180343761</v>
+      </c>
+      <c r="C64">
+        <v>-2081.963039351516</v>
+      </c>
+      <c r="D64">
+        <v>2293.874960648484</v>
+      </c>
       <c r="E64">
         <v>4174.538</v>
       </c>
@@ -5761,34 +6913,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M64">
-        <v>1139.9068404</v>
+        <v>1093.5314604</v>
       </c>
       <c r="N64">
-        <v>-1076.7068404</v>
+        <v>-1030.3314604</v>
       </c>
       <c r="O64">
-        <v>-277.7903648232</v>
+        <v>-265.8255167832</v>
       </c>
       <c r="P64">
-        <v>-798.9164755767999</v>
+        <v>-764.5059436168</v>
       </c>
       <c r="Q64">
-        <v>-616.7164755767999</v>
+        <v>-582.3059436168001</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
+      <c r="S64">
+        <v>0.1901077374364453</v>
+      </c>
       <c r="T64">
-        <v>3.334007379276781</v>
+        <v>3.332742204074948</v>
       </c>
       <c r="U64">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.01430432682926815</v>
+        <v>0.01491095646579351</v>
       </c>
       <c r="W64">
-        <v>0.2422839964653659</v>
+        <v>0.2322839964653659</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -5796,7 +6951,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.05544312724522538</v>
+        <v>0.05779440490617649</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -5806,6 +6961,15 @@
       <c r="A65">
         <v>0.63</v>
       </c>
+      <c r="B65">
+        <v>0.2181570180343761</v>
+      </c>
+      <c r="C65">
+        <v>-2182.048868254316</v>
+      </c>
+      <c r="D65">
+        <v>2268.588131745684</v>
+      </c>
       <c r="E65">
         <v>4249.337</v>
       </c>
@@ -5831,34 +6995,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M65">
-        <v>1158.2924346</v>
+        <v>1111.1690646</v>
       </c>
       <c r="N65">
-        <v>-1095.0924346</v>
+        <v>-1047.9690646</v>
       </c>
       <c r="O65">
-        <v>-282.5338481268</v>
+        <v>-270.3760186668</v>
       </c>
       <c r="P65">
-        <v>-812.5585864732</v>
+        <v>-777.5930459331998</v>
       </c>
       <c r="Q65">
-        <v>-630.3585864731999</v>
+        <v>-595.3930459331998</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
+      <c r="S65">
+        <v>0.1940079465563492</v>
+      </c>
       <c r="T65">
-        <v>3.424115686824802</v>
+        <v>3.422816317698596</v>
       </c>
       <c r="U65">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.01407727402245437</v>
+        <v>0.01467427461713013</v>
       </c>
       <c r="W65">
-        <v>0.2423398060452807</v>
+        <v>0.2323398060452807</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -5866,7 +7033,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.05456307760641232</v>
+        <v>0.05687703339972916</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -5876,6 +7043,15 @@
       <c r="A66">
         <v>0.64</v>
       </c>
+      <c r="B66">
+        <v>0.2200570180343761</v>
+      </c>
+      <c r="C66">
+        <v>-2281.583270586671</v>
+      </c>
+      <c r="D66">
+        <v>2243.852729413329</v>
+      </c>
       <c r="E66">
         <v>4324.136</v>
       </c>
@@ -5901,34 +7077,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M66">
-        <v>1176.6780288</v>
+        <v>1128.8066688</v>
       </c>
       <c r="N66">
-        <v>-1113.4780288</v>
+        <v>-1065.6066688</v>
       </c>
       <c r="O66">
-        <v>-287.2773314304</v>
+        <v>-274.9265205504</v>
       </c>
       <c r="P66">
-        <v>-826.2006973696</v>
+        <v>-790.6801482495998</v>
       </c>
       <c r="Q66">
-        <v>-644.0006973695999</v>
+        <v>-608.4801482495998</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
+      <c r="S66">
+        <v>0.1981248339606922</v>
+      </c>
       <c r="T66">
-        <v>3.519230011458824</v>
+        <v>3.517894548745779</v>
       </c>
       <c r="U66">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.01385731661585352</v>
+        <v>0.01444498907623747</v>
       </c>
       <c r="W66">
-        <v>0.2423938715758232</v>
+        <v>0.2323938715758232</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -5936,7 +7115,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.05371052951881206</v>
+        <v>0.05598832975285839</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -5946,6 +7125,15 @@
       <c r="A67">
         <v>0.65</v>
       </c>
+      <c r="B67">
+        <v>0.2219570180343761</v>
+      </c>
+      <c r="C67">
+        <v>-2380.584089131609</v>
+      </c>
+      <c r="D67">
+        <v>2219.65091086839</v>
+      </c>
       <c r="E67">
         <v>4398.934999999999</v>
       </c>
@@ -5971,34 +7159,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M67">
-        <v>1195.063623</v>
+        <v>1146.444273</v>
       </c>
       <c r="N67">
-        <v>-1131.863623</v>
+        <v>-1083.244273</v>
       </c>
       <c r="O67">
-        <v>-292.020814734</v>
+        <v>-279.4770224339999</v>
       </c>
       <c r="P67">
-        <v>-839.842808266</v>
+        <v>-803.7672505659998</v>
       </c>
       <c r="Q67">
-        <v>-657.642808266</v>
+        <v>-621.5672505659998</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
+      <c r="S67">
+        <v>0.2024769720738549</v>
+      </c>
       <c r="T67">
-        <v>3.619779440357649</v>
+        <v>3.618405821567087</v>
       </c>
       <c r="U67">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.01364412712945577</v>
+        <v>0.01422275847506459</v>
       </c>
       <c r="W67">
-        <v>0.2424462735515798</v>
+        <v>0.2324462735515798</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6006,7 +7197,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.05288421368006113</v>
+        <v>0.05512697083358364</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6016,6 +7207,15 @@
       <c r="A68">
         <v>0.66</v>
       </c>
+      <c r="B68">
+        <v>0.2238570180343761</v>
+      </c>
+      <c r="C68">
+        <v>-2479.068405089422</v>
+      </c>
+      <c r="D68">
+        <v>2195.965594910579</v>
+      </c>
       <c r="E68">
         <v>4473.734</v>
       </c>
@@ -6041,34 +7241,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M68">
-        <v>1213.4492172</v>
+        <v>1164.0818772</v>
       </c>
       <c r="N68">
-        <v>-1150.2492172</v>
+        <v>-1100.8818772</v>
       </c>
       <c r="O68">
-        <v>-296.7642980376</v>
+        <v>-284.0275243176001</v>
       </c>
       <c r="P68">
-        <v>-853.4849191624002</v>
+        <v>-816.8543528824001</v>
       </c>
       <c r="Q68">
-        <v>-671.2849191624002</v>
+        <v>-634.6543528824002</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
+      <c r="S68">
+        <v>0.2070851183113212</v>
+      </c>
       <c r="T68">
-        <v>3.726243541544638</v>
+        <v>3.724829522201413</v>
       </c>
       <c r="U68">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.01343739793052462</v>
+        <v>0.0140072621345333</v>
       </c>
       <c r="W68">
-        <v>0.2424970875886771</v>
+        <v>0.2324970875886771</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6076,7 +7279,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.05208293771521177</v>
+        <v>0.05429171369974151</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6086,6 +7289,15 @@
       <c r="A69">
         <v>0.67</v>
       </c>
+      <c r="B69">
+        <v>0.225757018034376</v>
+      </c>
+      <c r="C69">
+        <v>-2577.052578281905</v>
+      </c>
+      <c r="D69">
+        <v>2172.780421718095</v>
+      </c>
       <c r="E69">
         <v>4548.533</v>
       </c>
@@ -6111,34 +7323,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M69">
-        <v>1231.8348114</v>
+        <v>1181.7194814</v>
       </c>
       <c r="N69">
-        <v>-1168.6348114</v>
+        <v>-1118.5194814</v>
       </c>
       <c r="O69">
-        <v>-301.5077813412001</v>
+        <v>-288.5780262012</v>
       </c>
       <c r="P69">
-        <v>-867.1270300588001</v>
+        <v>-829.9414551988001</v>
       </c>
       <c r="Q69">
-        <v>-684.9270300588</v>
+        <v>-647.7414551988002</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
+      <c r="S69">
+        <v>0.211972546138937</v>
+      </c>
       <c r="T69">
-        <v>3.839160012500536</v>
+        <v>3.837703144086305</v>
       </c>
       <c r="U69">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.01323683975245709</v>
+        <v>0.01379819852058504</v>
       </c>
       <c r="W69">
-        <v>0.2425463847888461</v>
+        <v>0.232546384788846</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6146,7 +7361,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.05130558043588018</v>
+        <v>0.05348138961467075</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6156,6 +7371,15 @@
       <c r="A70">
         <v>0.68</v>
       </c>
+      <c r="B70">
+        <v>0.227657018034376</v>
+      </c>
+      <c r="C70">
+        <v>-2674.552284836349</v>
+      </c>
+      <c r="D70">
+        <v>2150.079715163652</v>
+      </c>
       <c r="E70">
         <v>4623.332</v>
       </c>
@@ -6181,34 +7405,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M70">
-        <v>1250.2204056</v>
+        <v>1199.3570856</v>
       </c>
       <c r="N70">
-        <v>-1187.0204056</v>
+        <v>-1136.1570856</v>
       </c>
       <c r="O70">
-        <v>-306.2512646448001</v>
+        <v>-293.1285280848001</v>
       </c>
       <c r="P70">
-        <v>-880.7691409552001</v>
+        <v>-843.0285575152</v>
       </c>
       <c r="Q70">
-        <v>-698.5691409552001</v>
+        <v>-660.8285575151999</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
+      <c r="S70">
+        <v>0.2171654382057788</v>
+      </c>
       <c r="T70">
-        <v>3.959133762891178</v>
+        <v>3.957631367339002</v>
       </c>
       <c r="U70">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.01304218034433272</v>
+        <v>0.01359528383645879</v>
       </c>
       <c r="W70">
-        <v>0.242594232071363</v>
+        <v>0.232594232071363</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -6216,7 +7443,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.05055108660594076</v>
+        <v>0.05269489859092558</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -6226,6 +7453,15 @@
       <c r="A71">
         <v>0.6900000000000001</v>
       </c>
+      <c r="B71">
+        <v>0.2295570180343761</v>
+      </c>
+      <c r="C71">
+        <v>-2771.582552531642</v>
+      </c>
+      <c r="D71">
+        <v>2127.848447468359</v>
+      </c>
       <c r="E71">
         <v>4698.131</v>
       </c>
@@ -6251,34 +7487,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M71">
-        <v>1268.6059998</v>
+        <v>1216.9946898</v>
       </c>
       <c r="N71">
-        <v>-1205.4059998</v>
+        <v>-1153.7946898</v>
       </c>
       <c r="O71">
-        <v>-310.9947479484</v>
+        <v>-297.6790299684</v>
       </c>
       <c r="P71">
-        <v>-894.4112518516</v>
+        <v>-856.1156598315999</v>
       </c>
       <c r="Q71">
-        <v>-712.2112518516001</v>
+        <v>-673.9156598315999</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
+      <c r="S71">
+        <v>0.2226933555672555</v>
+      </c>
       <c r="T71">
-        <v>4.086847755242506</v>
+        <v>4.085296895317679</v>
       </c>
       <c r="U71">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.01285316323789312</v>
+        <v>0.01339825073737968</v>
       </c>
       <c r="W71">
-        <v>0.2426406924761259</v>
+        <v>0.2326406924761259</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -6286,7 +7525,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.0498184621623764</v>
+        <v>0.05193120440844834</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -6296,6 +7535,15 @@
       <c r="A72">
         <v>0.7000000000000001</v>
       </c>
+      <c r="B72">
+        <v>0.2314570180343761</v>
+      </c>
+      <c r="C72">
+        <v>-2868.157793974027</v>
+      </c>
+      <c r="D72">
+        <v>2106.072206025973</v>
+      </c>
       <c r="E72">
         <v>4772.93</v>
       </c>
@@ -6321,34 +7569,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M72">
-        <v>1286.991594</v>
+        <v>1234.632294</v>
       </c>
       <c r="N72">
-        <v>-1223.791594</v>
+        <v>-1171.432294</v>
       </c>
       <c r="O72">
-        <v>-315.738231252</v>
+        <v>-302.229531852</v>
       </c>
       <c r="P72">
-        <v>-908.053362748</v>
+        <v>-869.2027621480001</v>
       </c>
       <c r="Q72">
-        <v>-725.8533627480001</v>
+        <v>-687.0027621480001</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
+      <c r="S72">
+        <v>0.2285898007528307</v>
+      </c>
       <c r="T72">
-        <v>4.22307601375059</v>
+        <v>4.221473458494936</v>
       </c>
       <c r="U72">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.01266954662020893</v>
+        <v>0.01320684715541711</v>
       </c>
       <c r="W72">
-        <v>0.2426858254407527</v>
+        <v>0.2326858254407527</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -6356,7 +7607,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.04910676984577111</v>
+        <v>0.05118933005975623</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -6366,6 +7617,15 @@
       <c r="A73">
         <v>0.71</v>
       </c>
+      <c r="B73">
+        <v>0.233357018034376</v>
+      </c>
+      <c r="C73">
+        <v>-2964.29183775637</v>
+      </c>
+      <c r="D73">
+        <v>2084.73716224363</v>
+      </c>
       <c r="E73">
         <v>4847.728999999999</v>
       </c>
@@ -6391,34 +7651,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M73">
-        <v>1305.3771882</v>
+        <v>1252.2698982</v>
       </c>
       <c r="N73">
-        <v>-1242.1771882</v>
+        <v>-1189.0698982</v>
       </c>
       <c r="O73">
-        <v>-320.4817145556</v>
+        <v>-306.7800337356</v>
       </c>
       <c r="P73">
-        <v>-921.6954736443998</v>
+        <v>-882.2898644643999</v>
       </c>
       <c r="Q73">
-        <v>-739.4954736443999</v>
+        <v>-700.0898644643999</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
+      <c r="S73">
+        <v>0.2348928973305145</v>
+      </c>
       <c r="T73">
-        <v>4.368699324569575</v>
+        <v>4.367041508787863</v>
       </c>
       <c r="U73">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.01249110230161444</v>
+        <v>0.01302083522365068</v>
       </c>
       <c r="W73">
-        <v>0.2427296870542632</v>
+        <v>0.2327296870542632</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -6426,7 +7689,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.04841512520005598</v>
+        <v>0.05046835358004143</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -6436,6 +7699,15 @@
       <c r="A74">
         <v>0.72</v>
       </c>
+      <c r="B74">
+        <v>0.235257018034376</v>
+      </c>
+      <c r="C74">
+        <v>-3059.99795774252</v>
+      </c>
+      <c r="D74">
+        <v>2063.830042257479</v>
+      </c>
       <c r="E74">
         <v>4922.527999999999</v>
       </c>
@@ -6461,34 +7733,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M74">
-        <v>1323.7627824</v>
+        <v>1269.9075024</v>
       </c>
       <c r="N74">
-        <v>-1260.5627824</v>
+        <v>-1206.7075024</v>
       </c>
       <c r="O74">
-        <v>-325.2251978592</v>
+        <v>-311.3305356192</v>
       </c>
       <c r="P74">
-        <v>-935.3375845407999</v>
+        <v>-895.3769667807999</v>
       </c>
       <c r="Q74">
-        <v>-753.1375845407999</v>
+        <v>-713.1769667807998</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
+      <c r="S74">
+        <v>0.2416462150923186</v>
+      </c>
       <c r="T74">
-        <v>4.52472430044706</v>
+        <v>4.523007276958858</v>
       </c>
       <c r="U74">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.01231761476964757</v>
+        <v>0.01283999028998886</v>
       </c>
       <c r="W74">
-        <v>0.2427723302896206</v>
+        <v>0.2327723302896206</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -6496,7 +7771,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.04774269290561073</v>
+        <v>0.049767404224763</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -6506,6 +7781,15 @@
       <c r="A75">
         <v>0.73</v>
       </c>
+      <c r="B75">
+        <v>0.2371570180343761</v>
+      </c>
+      <c r="C75">
+        <v>-3155.28890060706</v>
+      </c>
+      <c r="D75">
+        <v>2043.338099392939</v>
+      </c>
       <c r="E75">
         <v>4997.326999999999</v>
       </c>
@@ -6531,34 +7815,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M75">
-        <v>1342.1483766</v>
+        <v>1287.5451066</v>
       </c>
       <c r="N75">
-        <v>-1278.9483766</v>
+        <v>-1224.3451066</v>
       </c>
       <c r="O75">
-        <v>-329.9686811628</v>
+        <v>-315.8810375027999</v>
       </c>
       <c r="P75">
-        <v>-948.9796954371999</v>
+        <v>-908.4640690971999</v>
       </c>
       <c r="Q75">
-        <v>-766.7796954372</v>
+        <v>-726.2640690971998</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
+      <c r="S75">
+        <v>0.2488997786142563</v>
+      </c>
       <c r="T75">
-        <v>4.692306681945099</v>
+        <v>4.690526064994371</v>
       </c>
       <c r="U75">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.01214888032074829</v>
+        <v>0.01266410001204381</v>
       </c>
       <c r="W75">
-        <v>0.2428138052171601</v>
+        <v>0.2328138052171601</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -6566,7 +7853,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.04708868341375305</v>
+        <v>0.04908565896141015</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -6576,6 +7863,15 @@
       <c r="A76">
         <v>0.74</v>
       </c>
+      <c r="B76">
+        <v>0.2390570180343761</v>
+      </c>
+      <c r="C76">
+        <v>-3250.176911750531</v>
+      </c>
+      <c r="D76">
+        <v>2023.249088249468</v>
+      </c>
       <c r="E76">
         <v>5072.125999999999</v>
       </c>
@@ -6601,34 +7897,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M76">
-        <v>1360.5339708</v>
+        <v>1305.1827108</v>
       </c>
       <c r="N76">
-        <v>-1297.3339708</v>
+        <v>-1241.9827108</v>
       </c>
       <c r="O76">
-        <v>-334.7121644664</v>
+        <v>-320.4315393864</v>
       </c>
       <c r="P76">
-        <v>-962.6218063335998</v>
+        <v>-921.5511714135999</v>
       </c>
       <c r="Q76">
-        <v>-780.4218063335998</v>
+        <v>-739.3511714136</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
+      <c r="S76">
+        <v>0.2567113085609584</v>
+      </c>
       <c r="T76">
-        <v>4.872780015866065</v>
+        <v>4.870930913648</v>
       </c>
       <c r="U76">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.0119847062623598</v>
+        <v>0.01249296352539457</v>
       </c>
       <c r="W76">
-        <v>0.242854159200712</v>
+        <v>0.232854159200712</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -6636,7 +7935,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.04645234985410773</v>
+        <v>0.04842233924571537</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -6646,6 +7945,15 @@
       <c r="A77">
         <v>0.75</v>
       </c>
+      <c r="B77">
+        <v>0.2409570180343761</v>
+      </c>
+      <c r="C77">
+        <v>-3344.673759700826</v>
+      </c>
+      <c r="D77">
+        <v>2003.551240299173</v>
+      </c>
       <c r="E77">
         <v>5146.924999999999</v>
       </c>
@@ -6671,34 +7979,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M77">
-        <v>1378.919565</v>
+        <v>1322.820315</v>
       </c>
       <c r="N77">
-        <v>-1315.719565</v>
+        <v>-1259.620315</v>
       </c>
       <c r="O77">
-        <v>-339.45564777</v>
+        <v>-324.98204127</v>
       </c>
       <c r="P77">
-        <v>-976.2639172299998</v>
+        <v>-934.6382737299999</v>
       </c>
       <c r="Q77">
-        <v>-794.0639172299998</v>
+        <v>-752.43827373</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
+      <c r="S77">
+        <v>0.2651477609033968</v>
+      </c>
       <c r="T77">
-        <v>5.067691216500708</v>
+        <v>5.065768150193922</v>
       </c>
       <c r="U77">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.01182491017886167</v>
+        <v>0.01232639067838931</v>
       </c>
       <c r="W77">
-        <v>0.2428934370780358</v>
+        <v>0.2328934370780358</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -6706,7 +8017,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.04583298518938639</v>
+        <v>0.0477767080557725</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -6716,6 +8027,15 @@
       <c r="A78">
         <v>0.76</v>
       </c>
+      <c r="B78">
+        <v>0.2428570180343761</v>
+      </c>
+      <c r="C78">
+        <v>-3438.790759102931</v>
+      </c>
+      <c r="D78">
+        <v>1984.233240897069</v>
+      </c>
       <c r="E78">
         <v>5221.724</v>
       </c>
@@ -6741,34 +8061,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M78">
-        <v>1397.3051592</v>
+        <v>1340.4579192</v>
       </c>
       <c r="N78">
-        <v>-1334.1051592</v>
+        <v>-1277.2579192</v>
       </c>
       <c r="O78">
-        <v>-344.1991310736</v>
+        <v>-329.5325431536</v>
       </c>
       <c r="P78">
-        <v>-989.9060281264001</v>
+        <v>-947.7253760464</v>
       </c>
       <c r="Q78">
-        <v>-807.7060281264</v>
+        <v>-765.5253760464</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
+      <c r="S78">
+        <v>0.2742872509410383</v>
+      </c>
       <c r="T78">
-        <v>5.278845017188237</v>
+        <v>5.276841823118668</v>
       </c>
       <c r="U78">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.01166931925545559</v>
+        <v>0.01216420132735787</v>
       </c>
       <c r="W78">
-        <v>0.242931681327009</v>
+        <v>0.232931681327009</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -6776,7 +8099,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.04522991959478917</v>
+        <v>0.04714806716030184</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -6786,6 +8109,15 @@
       <c r="A79">
         <v>0.77</v>
       </c>
+      <c r="B79">
+        <v>0.2447570180343761</v>
+      </c>
+      <c r="C79">
+        <v>-3532.538792391382</v>
+      </c>
+      <c r="D79">
+        <v>1965.284207608618</v>
+      </c>
       <c r="E79">
         <v>5296.523</v>
       </c>
@@ -6811,34 +8143,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M79">
-        <v>1415.6907534</v>
+        <v>1358.0955234</v>
       </c>
       <c r="N79">
-        <v>-1352.4907534</v>
+        <v>-1294.8955234</v>
       </c>
       <c r="O79">
-        <v>-348.9426143772</v>
+        <v>-334.0830450372</v>
       </c>
       <c r="P79">
-        <v>-1003.5481390228</v>
+        <v>-960.8124783628</v>
       </c>
       <c r="Q79">
-        <v>-821.3481390228001</v>
+        <v>-778.6124783627999</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
+      <c r="S79">
+        <v>0.2842214792428226</v>
+      </c>
       <c r="T79">
-        <v>5.508360017935552</v>
+        <v>5.506269728471654</v>
       </c>
       <c r="U79">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.01151776965473539</v>
+        <v>0.01200622468674283</v>
       </c>
       <c r="W79">
-        <v>0.2429689322188661</v>
+        <v>0.2329689322188661</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -6846,7 +8181,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.04464251804161001</v>
+        <v>0.04653575459977843</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -6856,6 +8191,15 @@
       <c r="A80">
         <v>0.78</v>
       </c>
+      <c r="B80">
+        <v>0.2466570180343761</v>
+      </c>
+      <c r="C80">
+        <v>-3625.928330232671</v>
+      </c>
+      <c r="D80">
+        <v>1946.69366976733</v>
+      </c>
       <c r="E80">
         <v>5371.322</v>
       </c>
@@ -6881,34 +8225,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M80">
-        <v>1434.0763476</v>
+        <v>1375.7331276</v>
       </c>
       <c r="N80">
-        <v>-1370.8763476</v>
+        <v>-1312.5331276</v>
       </c>
       <c r="O80">
-        <v>-353.6860976808001</v>
+        <v>-338.6335469208</v>
       </c>
       <c r="P80">
-        <v>-1017.1902499192</v>
+        <v>-973.8995806792</v>
       </c>
       <c r="Q80">
-        <v>-834.9902499192001</v>
+        <v>-791.6995806791999</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
+      <c r="S80">
+        <v>0.2950588192084055</v>
+      </c>
       <c r="T80">
-        <v>5.758740018750804</v>
+        <v>5.756554716129457</v>
       </c>
       <c r="U80">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.01137010594121314</v>
+        <v>0.01185229872922049</v>
       </c>
       <c r="W80">
-        <v>0.2430052279596498</v>
+        <v>0.2330052279596498</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -6916,7 +8263,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.04407017806671765</v>
+        <v>0.04593914236131968</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -6926,6 +8273,15 @@
       <c r="A81">
         <v>0.79</v>
       </c>
+      <c r="B81">
+        <v>0.2485570180343761</v>
+      </c>
+      <c r="C81">
+        <v>-3718.969450818261</v>
+      </c>
+      <c r="D81">
+        <v>1928.451549181739</v>
+      </c>
       <c r="E81">
         <v>5446.121</v>
       </c>
@@ -6951,34 +8307,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M81">
-        <v>1452.4619418</v>
+        <v>1393.3707318</v>
       </c>
       <c r="N81">
-        <v>-1389.2619418</v>
+        <v>-1330.1707318</v>
       </c>
       <c r="O81">
-        <v>-358.4295809844</v>
+        <v>-343.1840488044</v>
       </c>
       <c r="P81">
-        <v>-1030.8323608156</v>
+        <v>-986.9866829956001</v>
       </c>
       <c r="Q81">
-        <v>-848.6323608156001</v>
+        <v>-804.7866829956001</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
+      <c r="S81">
+        <v>0.3069282867897581</v>
+      </c>
       <c r="T81">
-        <v>6.032965733929415</v>
+        <v>6.030676369278479</v>
       </c>
       <c r="U81">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.01122618054955222</v>
+        <v>0.01170226963138225</v>
       </c>
       <c r="W81">
-        <v>0.2430406048209201</v>
+        <v>0.2330406048209201</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -6986,7 +8345,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.04351232771144276</v>
+        <v>0.04535763423016381</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -6996,6 +8355,15 @@
       <c r="A82">
         <v>0.8</v>
       </c>
+      <c r="B82">
+        <v>0.2504570180343761</v>
+      </c>
+      <c r="C82">
+        <v>-3811.671858082946</v>
+      </c>
+      <c r="D82">
+        <v>1910.548141917055</v>
+      </c>
       <c r="E82">
         <v>5520.92</v>
       </c>
@@ -7021,34 +8389,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M82">
-        <v>1470.847536</v>
+        <v>1411.008336</v>
       </c>
       <c r="N82">
-        <v>-1407.647536</v>
+        <v>-1347.808336</v>
       </c>
       <c r="O82">
-        <v>-363.173064288</v>
+        <v>-347.734550688</v>
       </c>
       <c r="P82">
-        <v>-1044.474471712</v>
+        <v>-1000.073785312</v>
       </c>
       <c r="Q82">
-        <v>-862.2744717120001</v>
+        <v>-817.8737853120001</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
+      <c r="S82">
+        <v>0.319984701129246</v>
+      </c>
       <c r="T82">
-        <v>6.334614020625885</v>
+        <v>6.332210187742403</v>
       </c>
       <c r="U82">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.01108585329268281</v>
+        <v>0.01155599126098997</v>
       </c>
       <c r="W82">
-        <v>0.2430750972606586</v>
+        <v>0.2330750972606586</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -7056,7 +8427,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.04296842361504971</v>
+        <v>0.04479066380228669</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -7066,6 +8437,15 @@
       <c r="A83">
         <v>0.8100000000000001</v>
       </c>
+      <c r="B83">
+        <v>0.252357018034376</v>
+      </c>
+      <c r="C83">
+        <v>-3904.044898917705</v>
+      </c>
+      <c r="D83">
+        <v>1892.974101082295</v>
+      </c>
       <c r="E83">
         <v>5595.719</v>
       </c>
@@ -7091,34 +8471,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M83">
-        <v>1489.2331302</v>
+        <v>1428.6459402</v>
       </c>
       <c r="N83">
-        <v>-1426.0331302</v>
+        <v>-1365.4459402</v>
       </c>
       <c r="O83">
-        <v>-367.9165475916001</v>
+        <v>-352.2850525716</v>
       </c>
       <c r="P83">
-        <v>-1058.1165826084</v>
+        <v>-1013.1608876284</v>
       </c>
       <c r="Q83">
-        <v>-875.9165826084002</v>
+        <v>-830.9608876283999</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
+      <c r="S83">
+        <v>0.3344154748728905</v>
+      </c>
       <c r="T83">
-        <v>6.668014758553564</v>
+        <v>6.665484408149897</v>
       </c>
       <c r="U83">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.0109489909063534</v>
+        <v>0.01141332470221232</v>
       </c>
       <c r="W83">
-        <v>0.2431087380352183</v>
+        <v>0.2331087380352183</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -7126,7 +8509,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.04243794924943178</v>
+        <v>0.04423769264423383</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -7136,6 +8519,15 @@
       <c r="A84">
         <v>0.8200000000000001</v>
       </c>
+      <c r="B84">
+        <v>0.2542570180343761</v>
+      </c>
+      <c r="C84">
+        <v>-3996.097579441252</v>
+      </c>
+      <c r="D84">
+        <v>1875.720420558747</v>
+      </c>
       <c r="E84">
         <v>5670.518</v>
       </c>
@@ -7161,34 +8553,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M84">
-        <v>1507.6187244</v>
+        <v>1446.2835444</v>
       </c>
       <c r="N84">
-        <v>-1444.4187244</v>
+        <v>-1383.0835444</v>
       </c>
       <c r="O84">
-        <v>-372.6600308952</v>
+        <v>-356.8355544552</v>
       </c>
       <c r="P84">
-        <v>-1071.7586935048</v>
+        <v>-1026.2479899448</v>
       </c>
       <c r="Q84">
-        <v>-889.5586935048</v>
+        <v>-844.0479899447998</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
+      <c r="S84">
+        <v>0.3504496679213845</v>
+      </c>
       <c r="T84">
-        <v>7.038460022917651</v>
+        <v>7.03578909749156</v>
       </c>
       <c r="U84">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.01081546662700762</v>
+        <v>0.01127413781559997</v>
       </c>
       <c r="W84">
-        <v>0.2431415583030815</v>
+        <v>0.2331415583030815</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -7196,7 +8591,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.04192041328297536</v>
+        <v>0.04369820858759677</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -7206,6 +8601,15 @@
       <c r="A85">
         <v>0.8300000000000001</v>
       </c>
+      <c r="B85">
+        <v>0.2561570180343761</v>
+      </c>
+      <c r="C85">
+        <v>-4087.838580389751</v>
+      </c>
+      <c r="D85">
+        <v>1858.778419610249</v>
+      </c>
       <c r="E85">
         <v>5745.317</v>
       </c>
@@ -7231,34 +8635,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M85">
-        <v>1526.0043186</v>
+        <v>1463.9211486</v>
       </c>
       <c r="N85">
-        <v>-1462.8043186</v>
+        <v>-1400.7211486</v>
       </c>
       <c r="O85">
-        <v>-377.4035141988</v>
+        <v>-361.3860563388</v>
       </c>
       <c r="P85">
-        <v>-1085.4008044012</v>
+        <v>-1039.3350922612</v>
       </c>
       <c r="Q85">
-        <v>-903.2008044012</v>
+        <v>-857.1350922612</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
+      <c r="S85">
+        <v>0.3683702366226425</v>
+      </c>
       <c r="T85">
-        <v>7.452487083089278</v>
+        <v>7.449659044402829</v>
       </c>
       <c r="U85">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.01068515980017621</v>
+        <v>0.01113830482986985</v>
       </c>
       <c r="W85">
-        <v>0.2431735877211167</v>
+        <v>0.2331735877211167</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -7266,7 +8673,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.04141534806269853</v>
+        <v>0.04317172414678239</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -7276,6 +8683,15 @@
       <c r="A86">
         <v>0.84</v>
       </c>
+      <c r="B86">
+        <v>0.2580570180343761</v>
+      </c>
+      <c r="C86">
+        <v>-4179.276271679983</v>
+      </c>
+      <c r="D86">
+        <v>1842.139728320016</v>
+      </c>
       <c r="E86">
         <v>5820.115999999999</v>
       </c>
@@ -7301,34 +8717,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M86">
-        <v>1544.3899128</v>
+        <v>1481.5587528</v>
       </c>
       <c r="N86">
-        <v>-1481.1899128</v>
+        <v>-1418.3587528</v>
       </c>
       <c r="O86">
-        <v>-382.1469975023999</v>
+        <v>-365.9365582224</v>
       </c>
       <c r="P86">
-        <v>-1099.0429152976</v>
+        <v>-1052.4221945776</v>
       </c>
       <c r="Q86">
-        <v>-916.8429152975998</v>
+        <v>-870.2221945775998</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
+      <c r="S86">
+        <v>0.3885308764115574</v>
+      </c>
       <c r="T86">
-        <v>7.918267525782355</v>
+        <v>7.915262734678</v>
       </c>
       <c r="U86">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.01055795551684078</v>
+        <v>0.01100570596284759</v>
       </c>
       <c r="W86">
-        <v>0.2432048545339605</v>
+        <v>0.2332048545339606</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -7336,7 +8755,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.04092230820480924</v>
+        <v>0.04265777504979695</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -7346,6 +8765,15 @@
       <c r="A87">
         <v>0.85</v>
       </c>
+      <c r="B87">
+        <v>0.259957018034376</v>
+      </c>
+      <c r="C87">
+        <v>-4270.418726197295</v>
+      </c>
+      <c r="D87">
+        <v>1825.796273802705</v>
+      </c>
       <c r="E87">
         <v>5894.915</v>
       </c>
@@ -7371,34 +8799,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M87">
-        <v>1562.775507</v>
+        <v>1499.196357</v>
       </c>
       <c r="N87">
-        <v>-1499.575507</v>
+        <v>-1435.996357</v>
       </c>
       <c r="O87">
-        <v>-386.890480806</v>
+        <v>-370.487060106</v>
       </c>
       <c r="P87">
-        <v>-1112.685026194</v>
+        <v>-1065.509296894</v>
       </c>
       <c r="Q87">
-        <v>-930.4850261939998</v>
+        <v>-883.309296894</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
+      <c r="S87">
+        <v>0.4113796015056613</v>
+      </c>
       <c r="T87">
-        <v>8.446152027501178</v>
+        <v>8.442946916989868</v>
       </c>
       <c r="U87">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.01043374427546618</v>
+        <v>0.01087622706916704</v>
       </c>
       <c r="W87">
-        <v>0.2432353856570904</v>
+        <v>0.2332353856570904</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -7406,7 +8837,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.04044086928475266</v>
+        <v>0.04215591887274051</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -7416,6 +8847,15 @@
       <c r="A88">
         <v>0.86</v>
       </c>
+      <c r="B88">
+        <v>0.2618570180343761</v>
+      </c>
+      <c r="C88">
+        <v>-4361.273732856025</v>
+      </c>
+      <c r="D88">
+        <v>1809.740267143975</v>
+      </c>
       <c r="E88">
         <v>5969.714</v>
       </c>
@@ -7441,34 +8881,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M88">
-        <v>1581.1611012</v>
+        <v>1516.8339612</v>
       </c>
       <c r="N88">
-        <v>-1517.9611012</v>
+        <v>-1453.6339612</v>
       </c>
       <c r="O88">
-        <v>-391.6339641096</v>
+        <v>-375.0375619896</v>
       </c>
       <c r="P88">
-        <v>-1126.3271370904</v>
+        <v>-1078.5963992104</v>
       </c>
       <c r="Q88">
-        <v>-944.1271370903999</v>
+        <v>-896.3963992104</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
+      <c r="S88">
+        <v>0.437492430184637</v>
+      </c>
       <c r="T88">
-        <v>9.04944860089412</v>
+        <v>9.046014553917715</v>
       </c>
       <c r="U88">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.01031242166761192</v>
+        <v>0.01074975931254881</v>
       </c>
       <c r="W88">
-        <v>0.243265206754101</v>
+        <v>0.233265206754101</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -7476,7 +8919,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.03997062661865092</v>
+        <v>0.04166573376956906</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -7486,6 +8929,15 @@
       <c r="A89">
         <v>0.87</v>
       </c>
+      <c r="B89">
+        <v>0.2637570180343761</v>
+      </c>
+      <c r="C89">
+        <v>-4451.848808976829</v>
+      </c>
+      <c r="D89">
+        <v>1793.964191023172</v>
+      </c>
       <c r="E89">
         <v>6044.513</v>
       </c>
@@ -7511,34 +8963,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M89">
-        <v>1599.5466954</v>
+        <v>1534.4715654</v>
       </c>
       <c r="N89">
-        <v>-1536.3466954</v>
+        <v>-1471.2715654</v>
       </c>
       <c r="O89">
-        <v>-396.3774474132</v>
+        <v>-379.5880638732</v>
       </c>
       <c r="P89">
-        <v>-1139.9692479868</v>
+        <v>-1091.6835015268</v>
       </c>
       <c r="Q89">
-        <v>-957.7692479867999</v>
+        <v>-909.4835015268</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
+      <c r="S89">
+        <v>0.4676226171219169</v>
+      </c>
       <c r="T89">
-        <v>9.745560031732129</v>
+        <v>9.741861827296002</v>
       </c>
       <c r="U89">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.01019388808522558</v>
+        <v>0.01062619886068043</v>
       </c>
       <c r="W89">
-        <v>0.2432943423086516</v>
+        <v>0.2332943423086516</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -7546,7 +9001,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.03951119412878135</v>
+        <v>0.04118681728945905</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -7556,6 +9011,15 @@
       <c r="A90">
         <v>0.88</v>
       </c>
+      <c r="B90">
+        <v>0.265657018034376</v>
+      </c>
+      <c r="C90">
+        <v>-4542.151212022216</v>
+      </c>
+      <c r="D90">
+        <v>1778.460787977784</v>
+      </c>
       <c r="E90">
         <v>6119.312</v>
       </c>
@@ -7581,34 +9045,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M90">
-        <v>1617.9322896</v>
+        <v>1552.1091696</v>
       </c>
       <c r="N90">
-        <v>-1554.7322896</v>
+        <v>-1488.9091696</v>
       </c>
       <c r="O90">
-        <v>-401.1209307168</v>
+        <v>-384.1385657568</v>
       </c>
       <c r="P90">
-        <v>-1153.6113588832</v>
+        <v>-1104.7706038432</v>
       </c>
       <c r="Q90">
-        <v>-971.4113588831999</v>
+        <v>-922.5706038431999</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
+      <c r="S90">
+        <v>0.5027745018820766</v>
+      </c>
       <c r="T90">
-        <v>10.55769003437647</v>
+        <v>10.55368364623734</v>
       </c>
       <c r="U90">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.01007804844789347</v>
+        <v>0.01050544660089998</v>
       </c>
       <c r="W90">
-        <v>0.2433228156915078</v>
+        <v>0.2333228156915078</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -7616,7 +9083,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.03906220328640886</v>
+        <v>0.0407187852748061</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -7626,6 +9093,15 @@
       <c r="A91">
         <v>0.89</v>
       </c>
+      <c r="B91">
+        <v>0.267557018034376</v>
+      </c>
+      <c r="C91">
+        <v>-4632.187950728794</v>
+      </c>
+      <c r="D91">
+        <v>1763.223049271206</v>
+      </c>
       <c r="E91">
         <v>6194.111</v>
       </c>
@@ -7651,34 +9127,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M91">
-        <v>1636.3178838</v>
+        <v>1569.7467738</v>
       </c>
       <c r="N91">
-        <v>-1573.1178838</v>
+        <v>-1506.5467738</v>
       </c>
       <c r="O91">
-        <v>-405.8644140204</v>
+        <v>-388.6890676404</v>
       </c>
       <c r="P91">
-        <v>-1167.2534697796</v>
+        <v>-1117.8577061596</v>
       </c>
       <c r="Q91">
-        <v>-985.0534697795999</v>
+        <v>-935.6577061595999</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
+      <c r="S91">
+        <v>0.5443176384168109</v>
+      </c>
       <c r="T91">
-        <v>11.51748003750161</v>
+        <v>11.51310943225891</v>
       </c>
       <c r="U91">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.009964811948478935</v>
+        <v>0.01038740787504717</v>
       </c>
       <c r="W91">
-        <v>0.2433506492230639</v>
+        <v>0.2333506492230639</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -7686,7 +9165,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.03862330212588738</v>
+        <v>0.04026127083351616</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -7696,6 +9175,15 @@
       <c r="A92">
         <v>0.9</v>
       </c>
+      <c r="B92">
+        <v>0.2694570180343761</v>
+      </c>
+      <c r="C92">
+        <v>-4721.965795672082</v>
+      </c>
+      <c r="D92">
+        <v>1748.244204327917</v>
+      </c>
       <c r="E92">
         <v>6268.91</v>
       </c>
@@ -7721,34 +9209,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M92">
-        <v>1654.703478</v>
+        <v>1587.384378</v>
       </c>
       <c r="N92">
-        <v>-1591.503478</v>
+        <v>-1524.184378</v>
       </c>
       <c r="O92">
-        <v>-410.607897324</v>
+        <v>-393.239569524</v>
       </c>
       <c r="P92">
-        <v>-1180.895580676</v>
+        <v>-1130.944808476</v>
       </c>
       <c r="Q92">
-        <v>-998.695580676</v>
+        <v>-948.7448084759999</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
+      <c r="S92">
+        <v>0.594169402258492</v>
+      </c>
       <c r="T92">
-        <v>12.66922804125177</v>
+        <v>12.66442037548481</v>
       </c>
       <c r="U92">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.009854091815718056</v>
+        <v>0.01027199223199109</v>
       </c>
       <c r="W92">
-        <v>0.2433778642316965</v>
+        <v>0.2333778642316965</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -7756,7 +9247,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.03819415432448858</v>
+        <v>0.03981392337981049</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -7766,6 +9257,15 @@
       <c r="A93">
         <v>0.91</v>
       </c>
+      <c r="B93">
+        <v>0.2713570180343761</v>
+      </c>
+      <c r="C93">
+        <v>-4811.491289297374</v>
+      </c>
+      <c r="D93">
+        <v>1733.517710702625</v>
+      </c>
       <c r="E93">
         <v>6343.709</v>
       </c>
@@ -7791,34 +9291,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M93">
-        <v>1673.0890722</v>
+        <v>1605.0219822</v>
       </c>
       <c r="N93">
-        <v>-1609.8890722</v>
+        <v>-1541.8219822</v>
       </c>
       <c r="O93">
-        <v>-415.3513806276001</v>
+        <v>-397.7900714076</v>
       </c>
       <c r="P93">
-        <v>-1194.5376915724</v>
+        <v>-1144.0319107924</v>
       </c>
       <c r="Q93">
-        <v>-1012.3376915724</v>
+        <v>-961.8319107924001</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
+      <c r="S93">
+        <v>0.655099335842769</v>
+      </c>
       <c r="T93">
-        <v>14.0769200458353</v>
+        <v>14.07157819498312</v>
       </c>
       <c r="U93">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.009745805092468408</v>
+        <v>0.0101591131964747</v>
       </c>
       <c r="W93">
-        <v>0.2434044811082713</v>
+        <v>0.2334044811082713</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -7826,7 +9329,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.03777443834290084</v>
+        <v>0.039376407738274</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -7836,6 +9339,15 @@
       <c r="A94">
         <v>0.92</v>
       </c>
+      <c r="B94">
+        <v>0.2732570180343761</v>
+      </c>
+      <c r="C94">
+        <v>-4900.770755447851</v>
+      </c>
+      <c r="D94">
+        <v>1719.037244552149</v>
+      </c>
       <c r="E94">
         <v>6418.508</v>
       </c>
@@ -7861,34 +9373,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M94">
-        <v>1691.4746664</v>
+        <v>1622.6595864</v>
       </c>
       <c r="N94">
-        <v>-1628.2746664</v>
+        <v>-1559.4595864</v>
       </c>
       <c r="O94">
-        <v>-420.0948639312001</v>
+        <v>-402.3405732912</v>
       </c>
       <c r="P94">
-        <v>-1208.1798024688</v>
+        <v>-1157.1190131088</v>
       </c>
       <c r="Q94">
-        <v>-1025.9798024688</v>
+        <v>-974.9190131088001</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
+      <c r="S94">
+        <v>0.7312617528231153</v>
+      </c>
       <c r="T94">
-        <v>15.83653505156472</v>
+        <v>15.83052546935601</v>
       </c>
       <c r="U94">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.009639872428419839</v>
+        <v>0.01004868805303476</v>
       </c>
       <c r="W94">
-        <v>0.2434305193570944</v>
+        <v>0.2334305193570944</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -7896,7 +9411,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.03736384662178238</v>
+        <v>0.03894840330633631</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -7906,6 +9421,15 @@
       <c r="A95">
         <v>0.93</v>
       </c>
+      <c r="B95">
+        <v>0.2751570180343761</v>
+      </c>
+      <c r="C95">
+        <v>-4989.810308419112</v>
+      </c>
+      <c r="D95">
+        <v>1704.796691580888</v>
+      </c>
       <c r="E95">
         <v>6493.307</v>
       </c>
@@ -7931,34 +9455,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M95">
-        <v>1709.8602606</v>
+        <v>1640.2971906</v>
       </c>
       <c r="N95">
-        <v>-1646.6602606</v>
+        <v>-1577.0971906</v>
       </c>
       <c r="O95">
-        <v>-424.8383472348</v>
+        <v>-406.8910751748</v>
       </c>
       <c r="P95">
-        <v>-1221.8219133652</v>
+        <v>-1170.2061154252</v>
       </c>
       <c r="Q95">
-        <v>-1039.6219133652</v>
+        <v>-988.0061154252001</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
+      <c r="S95">
+        <v>0.8291848603692747</v>
+      </c>
       <c r="T95">
-        <v>18.09889720178825</v>
+        <v>18.09202910783545</v>
       </c>
       <c r="U95">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.009536217886178764</v>
+        <v>0.009940637643862342</v>
       </c>
       <c r="W95">
-        <v>0.2434559976435773</v>
+        <v>0.2334559976435773</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -7966,7 +9493,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.03696208483015029</v>
+        <v>0.03852960327078425</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -7976,6 +9503,15 @@
       <c r="A96">
         <v>0.9400000000000001</v>
       </c>
+      <c r="B96">
+        <v>0.277057018034376</v>
+      </c>
+      <c r="C96">
+        <v>-5078.615861567359</v>
+      </c>
+      <c r="D96">
+        <v>1690.790138432641</v>
+      </c>
       <c r="E96">
         <v>6568.106</v>
       </c>
@@ -8001,34 +9537,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M96">
-        <v>1728.2458548</v>
+        <v>1657.9347948</v>
       </c>
       <c r="N96">
-        <v>-1665.0458548</v>
+        <v>-1594.7347948</v>
       </c>
       <c r="O96">
-        <v>-429.5818305384</v>
+        <v>-411.4415770584</v>
       </c>
       <c r="P96">
-        <v>-1235.4640242616</v>
+        <v>-1183.2932177416</v>
       </c>
       <c r="Q96">
-        <v>-1053.2640242616</v>
+        <v>-1001.0932177416</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
+      <c r="S96">
+        <v>0.9597490037641541</v>
+      </c>
       <c r="T96">
-        <v>21.11538006875297</v>
+        <v>21.10736729247469</v>
       </c>
       <c r="U96">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.009434768759730055</v>
+        <v>0.009834886179565936</v>
       </c>
       <c r="W96">
-        <v>0.2434809338388584</v>
+        <v>0.2334809338388583</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -8036,7 +9575,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.03656887116174445</v>
+        <v>0.03811971387428659</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -8046,6 +9585,15 @@
       <c r="A97">
         <v>0.9500000000000001</v>
       </c>
+      <c r="B97">
+        <v>0.2789570180343761</v>
+      </c>
+      <c r="C97">
+        <v>-5167.193135496684</v>
+      </c>
+      <c r="D97">
+        <v>1677.011864503316</v>
+      </c>
       <c r="E97">
         <v>6642.905</v>
       </c>
@@ -8071,34 +9619,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M97">
-        <v>1746.631449</v>
+        <v>1675.572399</v>
       </c>
       <c r="N97">
-        <v>-1683.431449</v>
+        <v>-1612.372399</v>
       </c>
       <c r="O97">
-        <v>-434.325313842</v>
+        <v>-415.992078942</v>
       </c>
       <c r="P97">
-        <v>-1249.106135158</v>
+        <v>-1196.380320058</v>
       </c>
       <c r="Q97">
-        <v>-1066.906135158</v>
+        <v>-1014.180320058</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
+      <c r="S97">
+        <v>1.142538804516986</v>
+      </c>
       <c r="T97">
-        <v>25.33845608250358</v>
+        <v>25.32884075096964</v>
       </c>
       <c r="U97">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.009335455404364475</v>
+        <v>0.009731361061886296</v>
       </c>
       <c r="W97">
-        <v>0.2435053450616072</v>
+        <v>0.2335053450616072</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -8106,7 +9657,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.03618393567583134</v>
+        <v>0.03771845372824145</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -8116,6 +9667,15 @@
       <c r="A98">
         <v>0.96</v>
       </c>
+      <c r="B98">
+        <v>0.280857018034376</v>
+      </c>
+      <c r="C98">
+        <v>-5255.547665849282</v>
+      </c>
+      <c r="D98">
+        <v>1663.456334150718</v>
+      </c>
       <c r="E98">
         <v>6717.704</v>
       </c>
@@ -8141,34 +9701,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M98">
-        <v>1765.0170432</v>
+        <v>1693.2100032</v>
       </c>
       <c r="N98">
-        <v>-1701.8170432</v>
+        <v>-1630.0100032</v>
       </c>
       <c r="O98">
-        <v>-439.0687971456</v>
+        <v>-420.5425808256</v>
       </c>
       <c r="P98">
-        <v>-1262.7482460544</v>
+        <v>-1209.4674223744</v>
       </c>
       <c r="Q98">
-        <v>-1080.5482460544</v>
+        <v>-1027.2674223744</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
+      <c r="S98">
+        <v>1.416723505646229</v>
+      </c>
       <c r="T98">
-        <v>31.67307010312939</v>
+        <v>31.66105093871198</v>
       </c>
       <c r="U98">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.009238211077235679</v>
+        <v>0.009629992717491645</v>
       </c>
       <c r="W98">
-        <v>0.2435292477172155</v>
+        <v>0.2335292477172155</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -8176,7 +9739,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.03580701967920807</v>
+        <v>0.03732555316857233</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -8186,6 +9749,15 @@
       <c r="A99">
         <v>0.97</v>
       </c>
+      <c r="B99">
+        <v>0.2827570180343761</v>
+      </c>
+      <c r="C99">
+        <v>-5343.684810720888</v>
+      </c>
+      <c r="D99">
+        <v>1650.118189279111</v>
+      </c>
       <c r="E99">
         <v>6792.503</v>
       </c>
@@ -8211,34 +9783,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M99">
-        <v>1783.4026374</v>
+        <v>1710.8476074</v>
       </c>
       <c r="N99">
-        <v>-1720.2026374</v>
+        <v>-1647.6476074</v>
       </c>
       <c r="O99">
-        <v>-443.8122804492</v>
+        <v>-425.0930827092</v>
       </c>
       <c r="P99">
-        <v>-1276.3903569508</v>
+        <v>-1222.5545246908</v>
       </c>
       <c r="Q99">
-        <v>-1094.1903569508</v>
+        <v>-1040.3545246908</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
+      <c r="S99">
+        <v>1.873698007528305</v>
+      </c>
       <c r="T99">
-        <v>42.23076013750586</v>
+        <v>42.21473458494931</v>
       </c>
       <c r="U99">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.00914297178777964</v>
+        <v>0.009530714442053587</v>
       </c>
       <c r="W99">
-        <v>0.2435526575345638</v>
+        <v>0.2335526575345638</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -8246,7 +9821,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.03543787514643271</v>
+        <v>0.03694075365137051</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -8256,6 +9831,15 @@
       <c r="A100">
         <v>0.98</v>
       </c>
+      <c r="B100">
+        <v>0.284657018034376</v>
+      </c>
+      <c r="C100">
+        <v>-5431.609757722283</v>
+      </c>
+      <c r="D100">
+        <v>1636.992242277717</v>
+      </c>
       <c r="E100">
         <v>6867.302</v>
       </c>
@@ -8281,34 +9865,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M100">
-        <v>1801.7882316</v>
+        <v>1728.4852116</v>
       </c>
       <c r="N100">
-        <v>-1738.5882316</v>
+        <v>-1665.2852116</v>
       </c>
       <c r="O100">
-        <v>-448.5557637528</v>
+        <v>-429.6435845928</v>
       </c>
       <c r="P100">
-        <v>-1290.0324678472</v>
+        <v>-1235.6416270072</v>
       </c>
       <c r="Q100">
-        <v>-1107.8324678472</v>
+        <v>-1053.4416270072</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
+      <c r="S100">
+        <v>2.787647011292457</v>
+      </c>
       <c r="T100">
-        <v>63.34614020625879</v>
+        <v>63.32210187742396</v>
       </c>
       <c r="U100">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.009049676157292094</v>
+        <v>0.009433462253869367</v>
       </c>
       <c r="W100">
-        <v>0.2435755896005376</v>
+        <v>0.2335755896005376</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -8316,7 +9903,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.03507626417555076</v>
+        <v>0.0365638071855402</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -8326,6 +9913,15 @@
       <c r="A101">
         <v>0.99</v>
       </c>
+      <c r="B101">
+        <v>0.2865570180343761</v>
+      </c>
+      <c r="C101">
+        <v>-5519.327530706435</v>
+      </c>
+      <c r="D101">
+        <v>1624.073469293565</v>
+      </c>
       <c r="E101">
         <v>6942.101</v>
       </c>
@@ -8351,34 +9947,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M101">
-        <v>1820.1738258</v>
+        <v>1746.1228158</v>
       </c>
       <c r="N101">
-        <v>-1756.9738258</v>
+        <v>-1682.9228158</v>
       </c>
       <c r="O101">
-        <v>-453.2992470564</v>
+        <v>-434.1940864763999</v>
       </c>
       <c r="P101">
-        <v>-1303.6745787436</v>
+        <v>-1248.7287293236</v>
       </c>
       <c r="Q101">
-        <v>-1121.4745787436</v>
+        <v>-1066.5287293236</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
+      <c r="S101">
+        <v>5.529494022584915</v>
+      </c>
       <c r="T101">
-        <v>126.6922804125176</v>
+        <v>126.6442037548479</v>
       </c>
       <c r="U101">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V101">
-        <v>0.008958265287016416</v>
+        <v>0.009338174756355535</v>
       </c>
       <c r="W101">
-        <v>0.2435980583924514</v>
+        <v>0.2335980583924514</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -8386,7 +9985,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.03472195847680781</v>
+        <v>0.03619447579982771</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/netherlands/netherlands_software_system_application.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_software_system_application.xlsx
@@ -1656,7 +1656,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1793,22 +1793,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1011486268241594</v>
+        <v>0.1009210533669531</v>
       </c>
       <c r="C2">
-        <v>7326.14058274612</v>
+        <v>7280.507918809068</v>
       </c>
       <c r="D2">
-        <v>7064.440582746121</v>
+        <v>7093.606918809068</v>
       </c>
       <c r="E2">
-        <v>-463</v>
+        <v>-388.201</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>74.79899999999999</v>
       </c>
       <c r="G2">
         <v>261.7</v>
@@ -1829,28 +1829,28 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.7623897</v>
       </c>
       <c r="N2">
-        <v>63.20000000000002</v>
+        <v>59.43761030000002</v>
       </c>
       <c r="O2">
-        <v>16.30560000000001</v>
+        <v>15.3349034574</v>
       </c>
       <c r="P2">
-        <v>46.89440000000001</v>
+        <v>44.10270684260001</v>
       </c>
       <c r="Q2">
-        <v>229.0944</v>
+        <v>226.3027068426</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1011486268241594</v>
+        <v>0.1015634619868213</v>
       </c>
       <c r="T2">
-        <v>1.278259280003682</v>
+        <v>1.28783976874876</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>16.79783463153751</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1875,22 +1875,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1009210533669531</v>
+        <v>0.1007157399097468</v>
       </c>
       <c r="C3">
-        <v>7280.507918809068</v>
+        <v>7232.229784465382</v>
       </c>
       <c r="D3">
-        <v>7093.606918809068</v>
+        <v>7120.127784465382</v>
       </c>
       <c r="E3">
-        <v>-388.201</v>
+        <v>-313.402</v>
       </c>
       <c r="F3">
-        <v>74.79899999999999</v>
+        <v>149.598</v>
       </c>
       <c r="G3">
         <v>261.7</v>
@@ -1911,45 +1911,45 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M3">
-        <v>3.7623897</v>
+        <v>7.749176399999999</v>
       </c>
       <c r="N3">
-        <v>59.43761030000002</v>
+        <v>55.45082360000002</v>
       </c>
       <c r="O3">
-        <v>15.3349034574</v>
+        <v>14.30631248880001</v>
       </c>
       <c r="P3">
-        <v>44.10270684260001</v>
+        <v>41.14451111120002</v>
       </c>
       <c r="Q3">
-        <v>226.3027068426</v>
+        <v>223.3445111112</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1015634619868213</v>
+        <v>0.101986763173211</v>
       </c>
       <c r="T3">
-        <v>1.28783976874876</v>
+        <v>1.297615777672309</v>
       </c>
       <c r="U3">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V3">
         <v>0.258</v>
       </c>
       <c r="W3">
-        <v>0.0373226</v>
+        <v>0.0384356</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y3">
-        <v>16.79783463153751</v>
+        <v>8.155705424385491</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1957,22 +1957,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1007157399097468</v>
+        <v>0.1005549464525404</v>
       </c>
       <c r="C4">
-        <v>7232.229784465382</v>
+        <v>7178.339762309191</v>
       </c>
       <c r="D4">
-        <v>7120.127784465382</v>
+        <v>7141.036762309191</v>
       </c>
       <c r="E4">
-        <v>-313.402</v>
+        <v>-238.603</v>
       </c>
       <c r="F4">
-        <v>149.598</v>
+        <v>224.397</v>
       </c>
       <c r="G4">
         <v>261.7</v>
@@ -1993,45 +1993,45 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M4">
-        <v>7.749176399999999</v>
+        <v>12.1847571</v>
       </c>
       <c r="N4">
-        <v>55.45082360000002</v>
+        <v>51.01524290000002</v>
       </c>
       <c r="O4">
-        <v>14.30631248880001</v>
+        <v>13.16193266820001</v>
       </c>
       <c r="P4">
-        <v>41.14451111120002</v>
+        <v>37.85331023180001</v>
       </c>
       <c r="Q4">
-        <v>223.3445111112</v>
+        <v>220.0533102318</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.101986763173211</v>
+        <v>0.1024187922191138</v>
       </c>
       <c r="T4">
-        <v>1.297615777672309</v>
+        <v>1.307593353790158</v>
       </c>
       <c r="U4">
-        <v>0.0518</v>
+        <v>0.0543</v>
       </c>
       <c r="V4">
         <v>0.258</v>
       </c>
       <c r="W4">
-        <v>0.0384356</v>
+        <v>0.0402906</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y4">
-        <v>8.155705424385491</v>
+        <v>5.186808360750993</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2039,22 +2039,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1005549464525404</v>
+        <v>0.1003867329953341</v>
       </c>
       <c r="C5">
-        <v>7178.339762309191</v>
+        <v>7125.546447865207</v>
       </c>
       <c r="D5">
-        <v>7141.036762309191</v>
+        <v>7163.042447865208</v>
       </c>
       <c r="E5">
-        <v>-238.603</v>
+        <v>-163.804</v>
       </c>
       <c r="F5">
-        <v>224.397</v>
+        <v>299.196</v>
       </c>
       <c r="G5">
         <v>261.7</v>
@@ -2075,45 +2075,45 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M5">
-        <v>12.1847571</v>
+        <v>16.5455388</v>
       </c>
       <c r="N5">
-        <v>51.01524290000002</v>
+        <v>46.65446120000001</v>
       </c>
       <c r="O5">
-        <v>13.16193266820001</v>
+        <v>12.0368509896</v>
       </c>
       <c r="P5">
-        <v>37.85331023180001</v>
+        <v>34.61761021040001</v>
       </c>
       <c r="Q5">
-        <v>220.0533102318</v>
+        <v>216.8176102104</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1024187922191138</v>
+        <v>0.1028598218701397</v>
       </c>
       <c r="T5">
-        <v>1.307593353790158</v>
+        <v>1.317778796077129</v>
       </c>
       <c r="U5">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V5">
         <v>0.258</v>
       </c>
       <c r="W5">
-        <v>0.0402906</v>
+        <v>0.0410326</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y5">
-        <v>5.186808360750993</v>
+        <v>3.819760768383077</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -2121,22 +2121,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1003867329953341</v>
+        <v>0.1001962595381277</v>
       </c>
       <c r="C6">
-        <v>7125.546447865207</v>
+        <v>7075.829493409246</v>
       </c>
       <c r="D6">
-        <v>7163.042447865208</v>
+        <v>7188.124493409246</v>
       </c>
       <c r="E6">
-        <v>-163.804</v>
+        <v>-89.005</v>
       </c>
       <c r="F6">
-        <v>299.196</v>
+        <v>373.995</v>
       </c>
       <c r="G6">
         <v>261.7</v>
@@ -2157,28 +2157,28 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M6">
-        <v>16.5455388</v>
+        <v>20.6819235</v>
       </c>
       <c r="N6">
-        <v>46.65446120000001</v>
+        <v>42.51807650000002</v>
       </c>
       <c r="O6">
-        <v>12.0368509896</v>
+        <v>10.96966373700001</v>
       </c>
       <c r="P6">
-        <v>34.61761021040001</v>
+        <v>31.54841276300002</v>
       </c>
       <c r="Q6">
-        <v>216.8176102104</v>
+        <v>213.748412763</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1028598218701397</v>
+        <v>0.103310136355924</v>
       </c>
       <c r="T6">
-        <v>1.317778796077129</v>
+        <v>1.328178668728036</v>
       </c>
       <c r="U6">
         <v>0.0553</v>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>3.819760768383077</v>
+        <v>3.055808614706462</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2203,22 +2203,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1001962595381277</v>
+        <v>0.1002729060809214</v>
       </c>
       <c r="C7">
-        <v>7075.829493409246</v>
+        <v>6990.916384740764</v>
       </c>
       <c r="D7">
-        <v>7188.124493409246</v>
+        <v>7178.010384740764</v>
       </c>
       <c r="E7">
-        <v>-89.005</v>
+        <v>-14.20599999999996</v>
       </c>
       <c r="F7">
-        <v>373.995</v>
+        <v>448.794</v>
       </c>
       <c r="G7">
         <v>261.7</v>
@@ -2239,45 +2239,45 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M7">
-        <v>20.6819235</v>
+        <v>27.5110722</v>
       </c>
       <c r="N7">
-        <v>42.51807650000002</v>
+        <v>35.68892780000002</v>
       </c>
       <c r="O7">
-        <v>10.96966373700001</v>
+        <v>9.207743372400005</v>
       </c>
       <c r="P7">
-        <v>31.54841276300002</v>
+        <v>26.48118442760001</v>
       </c>
       <c r="Q7">
-        <v>213.748412763</v>
+        <v>208.6811844276</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.103310136355924</v>
+        <v>0.1037700320009803</v>
       </c>
       <c r="T7">
-        <v>1.328178668728036</v>
+        <v>1.338799815265133</v>
       </c>
       <c r="U7">
-        <v>0.0553</v>
+        <v>0.0613</v>
       </c>
       <c r="V7">
         <v>0.258</v>
       </c>
       <c r="W7">
-        <v>0.0410326</v>
+        <v>0.0454846</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y7">
-        <v>3.055808614706462</v>
+        <v>2.297256884084657</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2285,22 +2285,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1002729060809214</v>
+        <v>0.1008800826237151</v>
       </c>
       <c r="C8">
-        <v>6990.916384740764</v>
+        <v>6836.990424105679</v>
       </c>
       <c r="D8">
-        <v>7178.010384740764</v>
+        <v>7098.883424105679</v>
       </c>
       <c r="E8">
-        <v>-14.20600000000002</v>
+        <v>60.59299999999996</v>
       </c>
       <c r="F8">
-        <v>448.794</v>
+        <v>523.593</v>
       </c>
       <c r="G8">
         <v>261.7</v>
@@ -2321,45 +2321,45 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M8">
-        <v>27.5110722</v>
+        <v>39.6883494</v>
       </c>
       <c r="N8">
-        <v>35.68892780000002</v>
+        <v>23.51165060000002</v>
       </c>
       <c r="O8">
-        <v>9.207743372400005</v>
+        <v>6.066005854800005</v>
       </c>
       <c r="P8">
-        <v>26.48118442760001</v>
+        <v>17.44564474520001</v>
       </c>
       <c r="Q8">
-        <v>208.6811844276</v>
+        <v>199.6456447452</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1037700320009803</v>
+        <v>0.1042398178749625</v>
       </c>
       <c r="T8">
-        <v>1.338799815265133</v>
+        <v>1.349649373555715</v>
       </c>
       <c r="U8">
-        <v>0.0613</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V8">
         <v>0.258</v>
       </c>
       <c r="W8">
-        <v>0.0454846</v>
+        <v>0.0562436</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y8">
-        <v>2.297256884084657</v>
+        <v>1.592406863864185</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1008800826237151</v>
+        <v>0.1037753715814084</v>
       </c>
       <c r="C9">
-        <v>6836.99042410568</v>
+        <v>6407.67332048465</v>
       </c>
       <c r="D9">
-        <v>7098.88342410568</v>
+        <v>6744.36532048465</v>
       </c>
       <c r="E9">
-        <v>60.59300000000007</v>
+        <v>135.3919999999999</v>
       </c>
       <c r="F9">
-        <v>523.5930000000001</v>
+        <v>598.3919999999999</v>
       </c>
       <c r="G9">
         <v>261.7</v>
@@ -2403,45 +2403,45 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M9">
-        <v>39.68834940000001</v>
+        <v>70.9692912</v>
       </c>
       <c r="N9">
-        <v>23.51165060000001</v>
+        <v>-7.769291199999984</v>
       </c>
       <c r="O9">
-        <v>6.066005854800003</v>
+        <v>-2.004477129599996</v>
       </c>
       <c r="P9">
-        <v>17.44564474520001</v>
+        <v>-5.764814070399988</v>
       </c>
       <c r="Q9">
-        <v>199.6456447452</v>
+        <v>176.4351859296</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1042398178749625</v>
+        <v>0.1048557541009582</v>
       </c>
       <c r="T9">
-        <v>1.349649373555715</v>
+        <v>1.363874228659544</v>
       </c>
       <c r="U9">
-        <v>0.07580000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V9">
-        <v>0.258</v>
+        <v>0.2297557115802223</v>
       </c>
       <c r="W9">
-        <v>0.0562436</v>
+        <v>0.09135097260658565</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y9">
-        <v>1.592406863864185</v>
+        <v>0.8905260138768304</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2449,22 +2449,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1037753715814084</v>
+        <v>0.1123178296332762</v>
       </c>
       <c r="C10">
-        <v>6407.67332048465</v>
+        <v>5466.738757217717</v>
       </c>
       <c r="D10">
-        <v>6744.36532048465</v>
+        <v>5878.229757217717</v>
       </c>
       <c r="E10">
-        <v>135.3919999999999</v>
+        <v>210.1909999999999</v>
       </c>
       <c r="F10">
-        <v>598.3919999999999</v>
+        <v>673.1909999999999</v>
       </c>
       <c r="G10">
         <v>261.7</v>
@@ -2485,45 +2485,45 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M10">
-        <v>70.9692912</v>
+        <v>135.1767528</v>
       </c>
       <c r="N10">
-        <v>-7.769291199999984</v>
+        <v>-71.97675279999996</v>
       </c>
       <c r="O10">
-        <v>-2.004477129599996</v>
+        <v>-18.57000222239999</v>
       </c>
       <c r="P10">
-        <v>-5.764814070399988</v>
+        <v>-53.40675057759996</v>
       </c>
       <c r="Q10">
-        <v>176.4351859296</v>
+        <v>128.7932494224</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1048557541009582</v>
+        <v>0.1059623646425817</v>
       </c>
       <c r="T10">
-        <v>1.363874228659544</v>
+        <v>1.389431054101193</v>
       </c>
       <c r="U10">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V10">
-        <v>0.2297557115802223</v>
+        <v>0.1206242912501743</v>
       </c>
       <c r="W10">
-        <v>0.09135097260658565</v>
+        <v>0.176578642316965</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y10">
-        <v>0.8905260138768304</v>
+        <v>0.4675360125975746</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2531,22 +2531,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1123178296332762</v>
+        <v>0.1138678296332762</v>
       </c>
       <c r="C11">
-        <v>5466.738757217717</v>
+        <v>5258.084216754984</v>
       </c>
       <c r="D11">
-        <v>5878.229757217717</v>
+        <v>5744.374216754984</v>
       </c>
       <c r="E11">
-        <v>210.1909999999999</v>
+        <v>284.9899999999999</v>
       </c>
       <c r="F11">
-        <v>673.1909999999999</v>
+        <v>747.9899999999999</v>
       </c>
       <c r="G11">
         <v>261.7</v>
@@ -2567,37 +2567,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M11">
-        <v>135.1767528</v>
+        <v>150.196392</v>
       </c>
       <c r="N11">
-        <v>-71.97675279999996</v>
+        <v>-86.99639199999996</v>
       </c>
       <c r="O11">
-        <v>-18.57000222239999</v>
+        <v>-22.44506913599999</v>
       </c>
       <c r="P11">
-        <v>-53.40675057759996</v>
+        <v>-64.55132286399997</v>
       </c>
       <c r="Q11">
-        <v>128.7932494224</v>
+        <v>117.648677136</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1059623646425817</v>
+        <v>0.1066308353608326</v>
       </c>
       <c r="T11">
-        <v>1.389431054101193</v>
+        <v>1.40486917692454</v>
       </c>
       <c r="U11">
         <v>0.2008</v>
       </c>
       <c r="V11">
-        <v>0.1206242912501743</v>
+        <v>0.1085618621251568</v>
       </c>
       <c r="W11">
-        <v>0.176578642316965</v>
+        <v>0.1790007780852685</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>0.4675360125975746</v>
+        <v>0.4207824113378171</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2613,22 +2613,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1138678296332762</v>
+        <v>0.1154178296332762</v>
       </c>
       <c r="C12">
-        <v>5258.084216754983</v>
+        <v>5055.390105935349</v>
       </c>
       <c r="D12">
-        <v>5744.374216754983</v>
+        <v>5616.479105935349</v>
       </c>
       <c r="E12">
-        <v>284.99</v>
+        <v>359.789</v>
       </c>
       <c r="F12">
-        <v>747.99</v>
+        <v>822.789</v>
       </c>
       <c r="G12">
         <v>261.7</v>
@@ -2649,37 +2649,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M12">
-        <v>150.196392</v>
+        <v>165.2160312</v>
       </c>
       <c r="N12">
-        <v>-86.99639199999999</v>
+        <v>-102.0160312</v>
       </c>
       <c r="O12">
-        <v>-22.445069136</v>
+        <v>-26.3201360496</v>
       </c>
       <c r="P12">
-        <v>-64.55132286399999</v>
+        <v>-75.69589515039999</v>
       </c>
       <c r="Q12">
-        <v>117.648677136</v>
+        <v>106.5041048496</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1066308353608326</v>
+        <v>0.1073143278929767</v>
       </c>
       <c r="T12">
-        <v>1.40486917692454</v>
+        <v>1.420654223856276</v>
       </c>
       <c r="U12">
         <v>0.2008</v>
       </c>
       <c r="V12">
-        <v>0.1085618621251568</v>
+        <v>0.09869260193196072</v>
       </c>
       <c r="W12">
-        <v>0.1790007780852685</v>
+        <v>0.1809825255320623</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>0.420782411337817</v>
+        <v>0.382529464852561</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2695,22 +2695,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1154178296332762</v>
+        <v>0.1169678296332762</v>
       </c>
       <c r="C13">
-        <v>5055.390105935349</v>
+        <v>4858.266979162636</v>
       </c>
       <c r="D13">
-        <v>5616.479105935349</v>
+        <v>5494.154979162636</v>
       </c>
       <c r="E13">
-        <v>359.789</v>
+        <v>434.588</v>
       </c>
       <c r="F13">
-        <v>822.789</v>
+        <v>897.588</v>
       </c>
       <c r="G13">
         <v>261.7</v>
@@ -2731,37 +2731,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M13">
-        <v>165.2160312</v>
+        <v>180.2356704</v>
       </c>
       <c r="N13">
-        <v>-102.0160312</v>
+        <v>-117.0356704</v>
       </c>
       <c r="O13">
-        <v>-26.3201360496</v>
+        <v>-30.1952029632</v>
       </c>
       <c r="P13">
-        <v>-75.69589515039999</v>
+        <v>-86.8404674368</v>
       </c>
       <c r="Q13">
-        <v>106.5041048496</v>
+        <v>95.35953256319999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1073143278929767</v>
+        <v>0.108013354346306</v>
       </c>
       <c r="T13">
-        <v>1.420654223856276</v>
+        <v>1.436798021854643</v>
       </c>
       <c r="U13">
         <v>0.2008</v>
       </c>
       <c r="V13">
-        <v>0.09869260193196072</v>
+        <v>0.09046821843763067</v>
       </c>
       <c r="W13">
-        <v>0.1809825255320623</v>
+        <v>0.1826339817377238</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>0.382529464852561</v>
+        <v>0.3506520094481809</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2777,22 +2777,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1169678296332762</v>
+        <v>0.1185178296332761</v>
       </c>
       <c r="C14">
-        <v>4858.266979162636</v>
+        <v>4666.358595389099</v>
       </c>
       <c r="D14">
-        <v>5494.154979162636</v>
+        <v>5377.045595389099</v>
       </c>
       <c r="E14">
-        <v>434.588</v>
+        <v>509.3869999999999</v>
       </c>
       <c r="F14">
-        <v>897.588</v>
+        <v>972.3869999999999</v>
       </c>
       <c r="G14">
         <v>261.7</v>
@@ -2813,37 +2813,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M14">
-        <v>180.2356704</v>
+        <v>195.2553096</v>
       </c>
       <c r="N14">
-        <v>-117.0356704</v>
+        <v>-132.0553096</v>
       </c>
       <c r="O14">
-        <v>-30.1952029632</v>
+        <v>-34.0702698768</v>
       </c>
       <c r="P14">
-        <v>-86.8404674368</v>
+        <v>-97.98503972319999</v>
       </c>
       <c r="Q14">
-        <v>95.35953256319999</v>
+        <v>84.2149602768</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.108013354346306</v>
+        <v>0.1087284503732751</v>
       </c>
       <c r="T14">
-        <v>1.436798021854643</v>
+        <v>1.453312941646075</v>
       </c>
       <c r="U14">
         <v>0.2008</v>
       </c>
       <c r="V14">
-        <v>0.09046821843763067</v>
+        <v>0.08350912471165908</v>
       </c>
       <c r="W14">
-        <v>0.1826339817377238</v>
+        <v>0.1840313677578989</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>0.3506520094481809</v>
+        <v>0.3236787779521669</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2859,22 +2859,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1185178296332761</v>
+        <v>0.1200678296332762</v>
       </c>
       <c r="C15">
-        <v>4666.358595389099</v>
+        <v>4479.338453152852</v>
       </c>
       <c r="D15">
-        <v>5377.045595389099</v>
+        <v>5264.824453152852</v>
       </c>
       <c r="E15">
-        <v>509.3869999999999</v>
+        <v>584.1860000000001</v>
       </c>
       <c r="F15">
-        <v>972.3869999999999</v>
+        <v>1047.186</v>
       </c>
       <c r="G15">
         <v>261.7</v>
@@ -2895,37 +2895,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M15">
-        <v>195.2553096</v>
+        <v>210.2749488</v>
       </c>
       <c r="N15">
-        <v>-132.0553096</v>
+        <v>-147.0749488</v>
       </c>
       <c r="O15">
-        <v>-34.0702698768</v>
+        <v>-37.94533679040001</v>
       </c>
       <c r="P15">
-        <v>-97.98503972319999</v>
+        <v>-109.1296120096</v>
       </c>
       <c r="Q15">
-        <v>84.2149602768</v>
+        <v>73.07038799039998</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1087284503732751</v>
+        <v>0.1094601765404062</v>
       </c>
       <c r="T15">
-        <v>1.453312941646075</v>
+        <v>1.470211929339635</v>
       </c>
       <c r="U15">
         <v>0.2008</v>
       </c>
       <c r="V15">
-        <v>0.08350912471165908</v>
+        <v>0.07754418723225485</v>
       </c>
       <c r="W15">
-        <v>0.1840313677578989</v>
+        <v>0.1852291272037632</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.3236787779521669</v>
+        <v>0.3005588652412978</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2941,22 +2941,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1200678296332762</v>
+        <v>0.1216178296332762</v>
       </c>
       <c r="C16">
-        <v>4479.338453152852</v>
+        <v>4296.906750636064</v>
       </c>
       <c r="D16">
-        <v>5264.824453152852</v>
+        <v>5157.191750636064</v>
       </c>
       <c r="E16">
-        <v>584.1860000000001</v>
+        <v>658.9850000000001</v>
       </c>
       <c r="F16">
-        <v>1047.186</v>
+        <v>1121.985</v>
       </c>
       <c r="G16">
         <v>261.7</v>
@@ -2977,37 +2977,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M16">
-        <v>210.2749488</v>
+        <v>225.294588</v>
       </c>
       <c r="N16">
-        <v>-147.0749488</v>
+        <v>-162.094588</v>
       </c>
       <c r="O16">
-        <v>-37.94533679040001</v>
+        <v>-41.82040370400001</v>
       </c>
       <c r="P16">
-        <v>-109.1296120096</v>
+        <v>-120.274184296</v>
       </c>
       <c r="Q16">
-        <v>73.07038799039998</v>
+        <v>61.92581570399997</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1094601765404062</v>
+        <v>0.1102091197938227</v>
       </c>
       <c r="T16">
-        <v>1.470211929339635</v>
+        <v>1.487508540273042</v>
       </c>
       <c r="U16">
         <v>0.2008</v>
       </c>
       <c r="V16">
-        <v>0.07754418723225485</v>
+        <v>0.07237457475010453</v>
       </c>
       <c r="W16">
-        <v>0.1852291272037632</v>
+        <v>0.186267185390179</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.3005588652412978</v>
+        <v>0.2805216075585447</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -3023,22 +3023,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1216178296332762</v>
+        <v>0.1231678296332762</v>
       </c>
       <c r="C17">
-        <v>4296.906750636064</v>
+        <v>4118.787711139341</v>
       </c>
       <c r="D17">
-        <v>5157.191750636064</v>
+        <v>5053.871711139341</v>
       </c>
       <c r="E17">
-        <v>658.9849999999999</v>
+        <v>733.7839999999999</v>
       </c>
       <c r="F17">
-        <v>1121.985</v>
+        <v>1196.784</v>
       </c>
       <c r="G17">
         <v>261.7</v>
@@ -3059,37 +3059,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M17">
-        <v>225.294588</v>
+        <v>240.3142272</v>
       </c>
       <c r="N17">
-        <v>-162.094588</v>
+        <v>-177.1142272</v>
       </c>
       <c r="O17">
-        <v>-41.82040370399999</v>
+        <v>-45.69547061759999</v>
       </c>
       <c r="P17">
-        <v>-120.274184296</v>
+        <v>-131.4187565824</v>
       </c>
       <c r="Q17">
-        <v>61.92581570400003</v>
+        <v>50.78124341760002</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1102091197938227</v>
+        <v>0.1109758950294635</v>
       </c>
       <c r="T17">
-        <v>1.487508540273042</v>
+        <v>1.505216975276293</v>
       </c>
       <c r="U17">
         <v>0.2008</v>
       </c>
       <c r="V17">
-        <v>0.07237457475010454</v>
+        <v>0.06785116382822301</v>
       </c>
       <c r="W17">
-        <v>0.186267185390179</v>
+        <v>0.1871754863032928</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.2805216075585447</v>
+        <v>0.2629890070861357</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -3105,22 +3105,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1231678296332762</v>
+        <v>0.1247178296332762</v>
       </c>
       <c r="C18">
-        <v>4118.787711139341</v>
+        <v>3944.727223733167</v>
       </c>
       <c r="D18">
-        <v>5053.871711139341</v>
+        <v>4954.610223733167</v>
       </c>
       <c r="E18">
-        <v>733.7839999999999</v>
+        <v>808.5830000000001</v>
       </c>
       <c r="F18">
-        <v>1196.784</v>
+        <v>1271.583</v>
       </c>
       <c r="G18">
         <v>261.7</v>
@@ -3141,37 +3141,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M18">
-        <v>240.3142272</v>
+        <v>255.3338664</v>
       </c>
       <c r="N18">
-        <v>-177.1142272</v>
+        <v>-192.1338664</v>
       </c>
       <c r="O18">
-        <v>-45.69547061759999</v>
+        <v>-49.5705375312</v>
       </c>
       <c r="P18">
-        <v>-131.4187565824</v>
+        <v>-142.5633288688</v>
       </c>
       <c r="Q18">
-        <v>50.78124341760002</v>
+        <v>39.63667113119999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1109758950294635</v>
+        <v>0.1117611467768064</v>
       </c>
       <c r="T18">
-        <v>1.505216975276293</v>
+        <v>1.52335211955673</v>
       </c>
       <c r="U18">
         <v>0.2008</v>
       </c>
       <c r="V18">
-        <v>0.06785116382822301</v>
+        <v>0.06385991889715105</v>
       </c>
       <c r="W18">
-        <v>0.1871754863032928</v>
+        <v>0.1879769282854521</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.2629890070861357</v>
+        <v>0.2475190654928335</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3187,22 +3187,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1247178296332762</v>
+        <v>0.1262678296332762</v>
       </c>
       <c r="C19">
-        <v>3944.727223733167</v>
+        <v>3774.490756589023</v>
       </c>
       <c r="D19">
-        <v>4954.610223733167</v>
+        <v>4859.172756589023</v>
       </c>
       <c r="E19">
-        <v>808.5830000000001</v>
+        <v>883.3820000000001</v>
       </c>
       <c r="F19">
-        <v>1271.583</v>
+        <v>1346.382</v>
       </c>
       <c r="G19">
         <v>261.7</v>
@@ -3223,37 +3223,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M19">
-        <v>255.3338664</v>
+        <v>270.3535056</v>
       </c>
       <c r="N19">
-        <v>-192.1338664</v>
+        <v>-207.1535056</v>
       </c>
       <c r="O19">
-        <v>-49.5705375312</v>
+        <v>-53.4456044448</v>
       </c>
       <c r="P19">
-        <v>-142.5633288688</v>
+        <v>-153.7079011552</v>
       </c>
       <c r="Q19">
-        <v>39.63667113119999</v>
+        <v>28.49209884480001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1117611467768064</v>
+        <v>0.1125655510057918</v>
       </c>
       <c r="T19">
-        <v>1.52335211955673</v>
+        <v>1.541929584429373</v>
       </c>
       <c r="U19">
         <v>0.2008</v>
       </c>
       <c r="V19">
-        <v>0.06385991889715105</v>
+        <v>0.06031214562508711</v>
       </c>
       <c r="W19">
-        <v>0.1879769282854521</v>
+        <v>0.1886893211584825</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.2475190654928335</v>
+        <v>0.2337680062987872</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3269,22 +3269,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1262678296332762</v>
+        <v>0.1278178296332762</v>
       </c>
       <c r="C20">
-        <v>3774.490756589023</v>
+        <v>3607.86150691783</v>
       </c>
       <c r="D20">
-        <v>4859.172756589023</v>
+        <v>4767.34250691783</v>
       </c>
       <c r="E20">
-        <v>883.3819999999998</v>
+        <v>958.181</v>
       </c>
       <c r="F20">
-        <v>1346.382</v>
+        <v>1421.181</v>
       </c>
       <c r="G20">
         <v>261.7</v>
@@ -3305,37 +3305,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M20">
-        <v>270.3535055999999</v>
+        <v>285.3731448</v>
       </c>
       <c r="N20">
-        <v>-207.1535055999999</v>
+        <v>-222.1731448</v>
       </c>
       <c r="O20">
-        <v>-53.44560444479998</v>
+        <v>-57.32067135840001</v>
       </c>
       <c r="P20">
-        <v>-153.7079011551999</v>
+        <v>-164.8524734416</v>
       </c>
       <c r="Q20">
-        <v>28.49209884480004</v>
+        <v>17.34752655839998</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1125655510057918</v>
+        <v>0.1133898170675917</v>
       </c>
       <c r="T20">
-        <v>1.541929584429373</v>
+        <v>1.560965752138377</v>
       </c>
       <c r="U20">
         <v>0.2008</v>
       </c>
       <c r="V20">
-        <v>0.06031214562508713</v>
+        <v>0.05713782217113515</v>
       </c>
       <c r="W20">
-        <v>0.1886893211584825</v>
+        <v>0.1893267253080361</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.2337680062987874</v>
+        <v>0.2214644270199037</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3351,22 +3351,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1278178296332762</v>
+        <v>0.1293678296332761</v>
       </c>
       <c r="C21">
-        <v>3607.86150691783</v>
+        <v>3444.638756795928</v>
       </c>
       <c r="D21">
-        <v>4767.34250691783</v>
+        <v>4678.918756795928</v>
       </c>
       <c r="E21">
-        <v>958.181</v>
+        <v>1032.98</v>
       </c>
       <c r="F21">
-        <v>1421.181</v>
+        <v>1495.98</v>
       </c>
       <c r="G21">
         <v>261.7</v>
@@ -3387,37 +3387,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M21">
-        <v>285.3731448</v>
+        <v>300.392784</v>
       </c>
       <c r="N21">
-        <v>-222.1731448</v>
+        <v>-237.192784</v>
       </c>
       <c r="O21">
-        <v>-57.32067135840001</v>
+        <v>-61.195738272</v>
       </c>
       <c r="P21">
-        <v>-164.8524734416</v>
+        <v>-175.997045728</v>
       </c>
       <c r="Q21">
-        <v>17.34752655839998</v>
+        <v>6.202954271999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1133898170675917</v>
+        <v>0.1142346897809366</v>
       </c>
       <c r="T21">
-        <v>1.560965752138377</v>
+        <v>1.580477824040107</v>
       </c>
       <c r="U21">
         <v>0.2008</v>
       </c>
       <c r="V21">
-        <v>0.05713782217113515</v>
+        <v>0.05428093106257841</v>
       </c>
       <c r="W21">
-        <v>0.1893267253080361</v>
+        <v>0.1899003890426343</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.2214644270199037</v>
+        <v>0.2103912056689086</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1293678296332761</v>
+        <v>0.1309178296332762</v>
       </c>
       <c r="C22">
-        <v>3444.638756795928</v>
+        <v>3284.636408633974</v>
       </c>
       <c r="D22">
-        <v>4678.918756795928</v>
+        <v>4593.715408633974</v>
       </c>
       <c r="E22">
-        <v>1032.98</v>
+        <v>1107.779</v>
       </c>
       <c r="F22">
-        <v>1495.98</v>
+        <v>1570.779</v>
       </c>
       <c r="G22">
         <v>261.7</v>
@@ -3469,37 +3469,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M22">
-        <v>300.392784</v>
+        <v>315.4124232</v>
       </c>
       <c r="N22">
-        <v>-237.192784</v>
+        <v>-252.2124232</v>
       </c>
       <c r="O22">
-        <v>-61.195738272</v>
+        <v>-65.07080518560001</v>
       </c>
       <c r="P22">
-        <v>-175.997045728</v>
+        <v>-187.1416180144</v>
       </c>
       <c r="Q22">
-        <v>6.202954271999999</v>
+        <v>-4.941618014400035</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1142346897809366</v>
+        <v>0.1151009516768979</v>
       </c>
       <c r="T22">
-        <v>1.580477824040107</v>
+        <v>1.600483872445678</v>
       </c>
       <c r="U22">
         <v>0.2008</v>
       </c>
       <c r="V22">
-        <v>0.05428093106257841</v>
+        <v>0.05169612482150324</v>
       </c>
       <c r="W22">
-        <v>0.1899003890426343</v>
+        <v>0.1904194181358422</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.2103912056689086</v>
+        <v>0.200372576827532</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3515,22 +3515,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1309178296332761</v>
+        <v>0.140257018034376</v>
       </c>
       <c r="C23">
-        <v>3284.636408633977</v>
+        <v>2755.645919689714</v>
       </c>
       <c r="D23">
-        <v>4593.715408633977</v>
+        <v>4139.523919689715</v>
       </c>
       <c r="E23">
-        <v>1107.779</v>
+        <v>1182.578</v>
       </c>
       <c r="F23">
-        <v>1570.779</v>
+        <v>1645.578</v>
       </c>
       <c r="G23">
         <v>261.7</v>
@@ -3551,45 +3551,45 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M23">
-        <v>315.4124232</v>
+        <v>388.0272924</v>
       </c>
       <c r="N23">
-        <v>-252.2124232</v>
+        <v>-324.8272924</v>
       </c>
       <c r="O23">
-        <v>-65.07080518559999</v>
+        <v>-83.80544143920001</v>
       </c>
       <c r="P23">
-        <v>-187.1416180144</v>
+        <v>-241.0218509608</v>
       </c>
       <c r="Q23">
-        <v>-4.941618014399978</v>
+        <v>-58.82185096080002</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1151009516768979</v>
+        <v>0.1161037695203195</v>
       </c>
       <c r="T23">
-        <v>1.600483872445678</v>
+        <v>1.623643637882667</v>
       </c>
       <c r="U23">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.05169612482150324</v>
+        <v>0.04202178640359991</v>
       </c>
       <c r="W23">
-        <v>0.1904194181358422</v>
+        <v>0.2258912627660312</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y23">
-        <v>0.200372576827532</v>
+        <v>0.1628751410992244</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3597,22 +3597,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.140257018034376</v>
+        <v>0.1421570180343761</v>
       </c>
       <c r="C24">
-        <v>2755.645919689714</v>
+        <v>2599.222398634024</v>
       </c>
       <c r="D24">
-        <v>4139.523919689715</v>
+        <v>4057.899398634023</v>
       </c>
       <c r="E24">
-        <v>1182.578</v>
+        <v>1257.377</v>
       </c>
       <c r="F24">
-        <v>1645.578</v>
+        <v>1720.377</v>
       </c>
       <c r="G24">
         <v>261.7</v>
@@ -3633,37 +3633,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M24">
-        <v>388.0272924</v>
+        <v>405.6648966</v>
       </c>
       <c r="N24">
-        <v>-324.8272924</v>
+        <v>-342.4648966</v>
       </c>
       <c r="O24">
-        <v>-83.80544143920001</v>
+        <v>-88.3559433228</v>
       </c>
       <c r="P24">
-        <v>-241.0218509608</v>
+        <v>-254.1089532772</v>
       </c>
       <c r="Q24">
-        <v>-58.82185096080002</v>
+        <v>-71.9089532772</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1161037695203195</v>
+        <v>0.1170168054881158</v>
       </c>
       <c r="T24">
-        <v>1.623643637882667</v>
+        <v>1.64472991889413</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.04202178640359991</v>
+        <v>0.04019475221213904</v>
       </c>
       <c r="W24">
-        <v>0.2258912627660312</v>
+        <v>0.2263220774283776</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.1628751410992244</v>
+        <v>0.1557936132253451</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3679,22 +3679,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1421570180343761</v>
+        <v>0.1440570180343761</v>
       </c>
       <c r="C25">
-        <v>2599.222398634024</v>
+        <v>2445.955631021666</v>
       </c>
       <c r="D25">
-        <v>4057.899398634023</v>
+        <v>3979.431631021666</v>
       </c>
       <c r="E25">
-        <v>1257.377</v>
+        <v>1332.176</v>
       </c>
       <c r="F25">
-        <v>1720.377</v>
+        <v>1795.176</v>
       </c>
       <c r="G25">
         <v>261.7</v>
@@ -3715,37 +3715,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M25">
-        <v>405.6648966</v>
+        <v>423.3025008000001</v>
       </c>
       <c r="N25">
-        <v>-342.4648966</v>
+        <v>-360.1025008</v>
       </c>
       <c r="O25">
-        <v>-88.3559433228</v>
+        <v>-92.90644520640001</v>
       </c>
       <c r="P25">
-        <v>-254.1089532772</v>
+        <v>-267.1960555936</v>
       </c>
       <c r="Q25">
-        <v>-71.9089532772</v>
+        <v>-84.99605559360003</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1170168054881158</v>
+        <v>0.1179538687182226</v>
       </c>
       <c r="T25">
-        <v>1.64472991889413</v>
+        <v>1.666371102037474</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.04019475221213904</v>
+        <v>0.03851997086996657</v>
       </c>
       <c r="W25">
-        <v>0.2263220774283776</v>
+        <v>0.2267169908688619</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.1557936132253451</v>
+        <v>0.1493022126742891</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3761,22 +3761,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.144057018034376</v>
+        <v>0.1459570180343761</v>
       </c>
       <c r="C26">
-        <v>2445.955631021667</v>
+        <v>2295.665963993759</v>
       </c>
       <c r="D26">
-        <v>3979.431631021667</v>
+        <v>3903.940963993759</v>
       </c>
       <c r="E26">
-        <v>1332.176</v>
+        <v>1406.975</v>
       </c>
       <c r="F26">
-        <v>1795.176</v>
+        <v>1869.975</v>
       </c>
       <c r="G26">
         <v>261.7</v>
@@ -3797,37 +3797,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M26">
-        <v>423.3025008</v>
+        <v>440.940105</v>
       </c>
       <c r="N26">
-        <v>-360.1025008</v>
+        <v>-377.740105</v>
       </c>
       <c r="O26">
-        <v>-92.90644520640001</v>
+        <v>-97.45694709</v>
       </c>
       <c r="P26">
-        <v>-267.1960555936</v>
+        <v>-280.28315791</v>
       </c>
       <c r="Q26">
-        <v>-84.99605559360003</v>
+        <v>-98.08315791000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1179538687182226</v>
+        <v>0.1189159203011323</v>
       </c>
       <c r="T26">
-        <v>1.666371102037474</v>
+        <v>1.688589383397974</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.03851997086996658</v>
+        <v>0.03697917203516791</v>
       </c>
       <c r="W26">
-        <v>0.2267169908688619</v>
+        <v>0.2270803112341074</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.149302212674289</v>
+        <v>0.1433301241673176</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3843,22 +3843,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1459570180343761</v>
+        <v>0.1478570180343761</v>
       </c>
       <c r="C27">
-        <v>2295.665963993759</v>
+        <v>2148.187123112167</v>
       </c>
       <c r="D27">
-        <v>3903.940963993759</v>
+        <v>3831.261123112167</v>
       </c>
       <c r="E27">
-        <v>1406.975</v>
+        <v>1481.774</v>
       </c>
       <c r="F27">
-        <v>1869.975</v>
+        <v>1944.774</v>
       </c>
       <c r="G27">
         <v>261.7</v>
@@ -3879,37 +3879,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M27">
-        <v>440.940105</v>
+        <v>458.5777092</v>
       </c>
       <c r="N27">
-        <v>-377.740105</v>
+        <v>-395.3777092</v>
       </c>
       <c r="O27">
-        <v>-97.45694709</v>
+        <v>-102.0074489736</v>
       </c>
       <c r="P27">
-        <v>-280.28315791</v>
+        <v>-293.3702602264</v>
       </c>
       <c r="Q27">
-        <v>-98.08315791000001</v>
+        <v>-111.1702602264</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1189159203011323</v>
+        <v>0.1199039732781746</v>
       </c>
       <c r="T27">
-        <v>1.688589383397974</v>
+        <v>1.711408158849298</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.03697917203516791</v>
+        <v>0.03555689618766146</v>
       </c>
       <c r="W27">
-        <v>0.2270803112341074</v>
+        <v>0.2274156838789494</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.1433301241673176</v>
+        <v>0.1378174270839591</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3925,22 +3925,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1478570180343761</v>
+        <v>0.149757018034376</v>
       </c>
       <c r="C28">
-        <v>2148.187123112167</v>
+        <v>2003.364989786951</v>
       </c>
       <c r="D28">
-        <v>3831.261123112167</v>
+        <v>3761.237989786951</v>
       </c>
       <c r="E28">
-        <v>1481.774</v>
+        <v>1556.573</v>
       </c>
       <c r="F28">
-        <v>1944.774</v>
+        <v>2019.573</v>
       </c>
       <c r="G28">
         <v>261.7</v>
@@ -3961,37 +3961,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M28">
-        <v>458.5777092</v>
+        <v>476.2153134</v>
       </c>
       <c r="N28">
-        <v>-395.3777092</v>
+        <v>-413.0153134</v>
       </c>
       <c r="O28">
-        <v>-102.0074489736</v>
+        <v>-106.5579508572</v>
       </c>
       <c r="P28">
-        <v>-293.3702602264</v>
+        <v>-306.4573625428</v>
       </c>
       <c r="Q28">
-        <v>-111.1702602264</v>
+        <v>-124.2573625428</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1199039732781746</v>
+        <v>0.1209190961997934</v>
       </c>
       <c r="T28">
-        <v>1.711408158849298</v>
+        <v>1.734852106230795</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.03555689618766146</v>
+        <v>0.03423997410663696</v>
       </c>
       <c r="W28">
-        <v>0.2274156838789494</v>
+        <v>0.227726214105655</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.1378174270839591</v>
+        <v>0.1327130779327015</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -4007,22 +4007,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.149757018034376</v>
+        <v>0.1516570180343761</v>
       </c>
       <c r="C29">
-        <v>2003.364989786951</v>
+        <v>1861.056510365618</v>
       </c>
       <c r="D29">
-        <v>3761.237989786951</v>
+        <v>3693.728510365618</v>
       </c>
       <c r="E29">
-        <v>1556.573</v>
+        <v>1631.372</v>
       </c>
       <c r="F29">
-        <v>2019.573</v>
+        <v>2094.372</v>
       </c>
       <c r="G29">
         <v>261.7</v>
@@ -4043,37 +4043,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M29">
-        <v>476.2153134</v>
+        <v>493.8529176000001</v>
       </c>
       <c r="N29">
-        <v>-413.0153134</v>
+        <v>-430.6529176</v>
       </c>
       <c r="O29">
-        <v>-106.5579508572</v>
+        <v>-111.1084527408</v>
       </c>
       <c r="P29">
-        <v>-306.4573625428</v>
+        <v>-319.5444648592</v>
       </c>
       <c r="Q29">
-        <v>-124.2573625428</v>
+        <v>-137.3444648592001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1209190961997934</v>
+        <v>0.1219624169803461</v>
       </c>
       <c r="T29">
-        <v>1.734852106230795</v>
+        <v>1.75894727437289</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.03423997410663696</v>
+        <v>0.03301711788854278</v>
       </c>
       <c r="W29">
-        <v>0.227726214105655</v>
+        <v>0.2280145636018816</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.1327130779327015</v>
+        <v>0.1279733251493906</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -4089,22 +4089,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1516570180343761</v>
+        <v>0.153557018034376</v>
       </c>
       <c r="C30">
-        <v>1861.056510365618</v>
+        <v>1721.128720633745</v>
       </c>
       <c r="D30">
-        <v>3693.728510365618</v>
+        <v>3628.599720633745</v>
       </c>
       <c r="E30">
-        <v>1631.372</v>
+        <v>1706.171</v>
       </c>
       <c r="F30">
-        <v>2094.372</v>
+        <v>2169.171</v>
       </c>
       <c r="G30">
         <v>261.7</v>
@@ -4125,37 +4125,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M30">
-        <v>493.8529176000001</v>
+        <v>511.4905218000001</v>
       </c>
       <c r="N30">
-        <v>-430.6529176</v>
+        <v>-448.2905218000001</v>
       </c>
       <c r="O30">
-        <v>-111.1084527408</v>
+        <v>-115.6589546244</v>
       </c>
       <c r="P30">
-        <v>-319.5444648592</v>
+        <v>-332.6315671756</v>
       </c>
       <c r="Q30">
-        <v>-137.3444648592001</v>
+        <v>-150.4315671756</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1219624169803461</v>
+        <v>0.1230351270786608</v>
       </c>
       <c r="T30">
-        <v>1.75894727437289</v>
+        <v>1.783721179645747</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.03301711788854278</v>
+        <v>0.0318785965820413</v>
       </c>
       <c r="W30">
-        <v>0.2280145636018816</v>
+        <v>0.2282830269259547</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.1279733251493906</v>
+        <v>0.1235604518683771</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4171,22 +4171,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.153557018034376</v>
+        <v>0.1554570180343761</v>
       </c>
       <c r="C31">
-        <v>1721.128720633745</v>
+        <v>1583.457871728982</v>
       </c>
       <c r="D31">
-        <v>3628.599720633745</v>
+        <v>3565.727871728982</v>
       </c>
       <c r="E31">
-        <v>1706.171</v>
+        <v>1780.97</v>
       </c>
       <c r="F31">
-        <v>2169.171</v>
+        <v>2243.97</v>
       </c>
       <c r="G31">
         <v>261.7</v>
@@ -4207,37 +4207,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M31">
-        <v>511.4905218</v>
+        <v>529.128126</v>
       </c>
       <c r="N31">
-        <v>-448.2905218</v>
+        <v>-465.9281259999999</v>
       </c>
       <c r="O31">
-        <v>-115.6589546244</v>
+        <v>-120.209456508</v>
       </c>
       <c r="P31">
-        <v>-332.6315671756</v>
+        <v>-345.7186694919999</v>
       </c>
       <c r="Q31">
-        <v>-150.4315671756</v>
+        <v>-163.518669492</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1230351270786608</v>
+        <v>0.1241384860369274</v>
       </c>
       <c r="T31">
-        <v>1.783721179645747</v>
+        <v>1.809202910783543</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.03187859658204131</v>
+        <v>0.03081597669597327</v>
       </c>
       <c r="W31">
-        <v>0.2282830269259547</v>
+        <v>0.2285335926950895</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.1235604518683772</v>
+        <v>0.1194417701394314</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4253,22 +4253,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1554570180343761</v>
+        <v>0.157357018034376</v>
       </c>
       <c r="C32">
-        <v>1583.457871728982</v>
+        <v>1447.92864537785</v>
       </c>
       <c r="D32">
-        <v>3565.727871728982</v>
+        <v>3504.997645377849</v>
       </c>
       <c r="E32">
-        <v>1780.97</v>
+        <v>1855.769</v>
       </c>
       <c r="F32">
-        <v>2243.97</v>
+        <v>2318.769</v>
       </c>
       <c r="G32">
         <v>261.7</v>
@@ -4289,37 +4289,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M32">
-        <v>529.128126</v>
+        <v>546.7657302</v>
       </c>
       <c r="N32">
-        <v>-465.9281259999999</v>
+        <v>-483.5657302</v>
       </c>
       <c r="O32">
-        <v>-120.209456508</v>
+        <v>-124.7599583916</v>
       </c>
       <c r="P32">
-        <v>-345.7186694919999</v>
+        <v>-358.8057718084</v>
       </c>
       <c r="Q32">
-        <v>-163.518669492</v>
+        <v>-176.6057718084</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1241384860369274</v>
+        <v>0.1252738264142742</v>
       </c>
       <c r="T32">
-        <v>1.809202910783543</v>
+        <v>1.835423242823885</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.03081597669597327</v>
+        <v>0.02982191293158703</v>
       </c>
       <c r="W32">
-        <v>0.2285335926950895</v>
+        <v>0.2287679929307318</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.1194417701394314</v>
+        <v>0.1155888098123529</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4335,22 +4335,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.157357018034376</v>
+        <v>0.159257018034376</v>
       </c>
       <c r="C33">
-        <v>1447.92864537785</v>
+        <v>1314.433447984401</v>
       </c>
       <c r="D33">
-        <v>3504.997645377849</v>
+        <v>3446.301447984401</v>
       </c>
       <c r="E33">
-        <v>1855.769</v>
+        <v>1930.568</v>
       </c>
       <c r="F33">
-        <v>2318.769</v>
+        <v>2393.568</v>
       </c>
       <c r="G33">
         <v>261.7</v>
@@ -4371,37 +4371,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M33">
-        <v>546.7657302</v>
+        <v>564.4033343999999</v>
       </c>
       <c r="N33">
-        <v>-483.5657302</v>
+        <v>-501.2033343999999</v>
       </c>
       <c r="O33">
-        <v>-124.7599583916</v>
+        <v>-129.3104602752</v>
       </c>
       <c r="P33">
-        <v>-358.8057718084</v>
+        <v>-371.8928741248</v>
       </c>
       <c r="Q33">
-        <v>-176.6057718084</v>
+        <v>-189.6928741248</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1252738264142742</v>
+        <v>0.1264425591556606</v>
       </c>
       <c r="T33">
-        <v>1.835423242823885</v>
+        <v>1.862414761100706</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.02982191293158703</v>
+        <v>0.02888997815247494</v>
       </c>
       <c r="W33">
-        <v>0.2287679929307318</v>
+        <v>0.2289877431516464</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.1155888098123529</v>
+        <v>0.1119766595057169</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4417,22 +4417,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.159257018034376</v>
+        <v>0.161157018034376</v>
       </c>
       <c r="C34">
-        <v>1314.433447984401</v>
+        <v>1182.871774479619</v>
       </c>
       <c r="D34">
-        <v>3446.301447984401</v>
+        <v>3389.53877447962</v>
       </c>
       <c r="E34">
-        <v>1930.568</v>
+        <v>2005.367</v>
       </c>
       <c r="F34">
-        <v>2393.568</v>
+        <v>2468.367</v>
       </c>
       <c r="G34">
         <v>261.7</v>
@@ -4453,37 +4453,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M34">
-        <v>564.4033343999999</v>
+        <v>582.0409386000001</v>
       </c>
       <c r="N34">
-        <v>-501.2033343999999</v>
+        <v>-518.8409386000001</v>
       </c>
       <c r="O34">
-        <v>-129.3104602752</v>
+        <v>-133.8609621588</v>
       </c>
       <c r="P34">
-        <v>-371.8928741248</v>
+        <v>-384.9799764412001</v>
       </c>
       <c r="Q34">
-        <v>-189.6928741248</v>
+        <v>-202.7799764412001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1264425591556606</v>
+        <v>0.127646179441566</v>
       </c>
       <c r="T34">
-        <v>1.862414761100706</v>
+        <v>1.890211996341016</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.02888997815247494</v>
+        <v>0.0280145242690666</v>
       </c>
       <c r="W34">
-        <v>0.2289877431516464</v>
+        <v>0.2291941751773541</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.1119766595057169</v>
+        <v>0.108583427399483</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.161157018034376</v>
+        <v>0.1630570180343761</v>
       </c>
       <c r="C35">
-        <v>1182.871774479619</v>
+        <v>1053.149634018864</v>
       </c>
       <c r="D35">
-        <v>3389.53877447962</v>
+        <v>3334.615634018865</v>
       </c>
       <c r="E35">
-        <v>2005.367</v>
+        <v>2080.166</v>
       </c>
       <c r="F35">
-        <v>2468.367</v>
+        <v>2543.166</v>
       </c>
       <c r="G35">
         <v>261.7</v>
@@ -4535,37 +4535,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M35">
-        <v>582.0409386000001</v>
+        <v>599.6785428000001</v>
       </c>
       <c r="N35">
-        <v>-518.8409386000001</v>
+        <v>-536.4785428</v>
       </c>
       <c r="O35">
-        <v>-133.8609621588</v>
+        <v>-138.4114640424</v>
       </c>
       <c r="P35">
-        <v>-384.9799764412001</v>
+        <v>-398.0670787576</v>
       </c>
       <c r="Q35">
-        <v>-202.7799764412001</v>
+        <v>-215.8670787576</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.127646179441566</v>
+        <v>0.1288862730694685</v>
       </c>
       <c r="T35">
-        <v>1.890211996341016</v>
+        <v>1.918851572043152</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.0280145242690666</v>
+        <v>0.02719056767291759</v>
       </c>
       <c r="W35">
-        <v>0.2291941751773541</v>
+        <v>0.229388464142726</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.108583427399483</v>
+        <v>0.1053897971818512</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4581,22 +4581,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1630570180343761</v>
+        <v>0.1649570180343761</v>
       </c>
       <c r="C36">
-        <v>1053.149634018864</v>
+        <v>925.1790306240218</v>
       </c>
       <c r="D36">
-        <v>3334.615634018865</v>
+        <v>3281.444030624022</v>
       </c>
       <c r="E36">
-        <v>2080.166</v>
+        <v>2154.965</v>
       </c>
       <c r="F36">
-        <v>2543.166</v>
+        <v>2617.965</v>
       </c>
       <c r="G36">
         <v>261.7</v>
@@ -4617,37 +4617,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M36">
-        <v>599.6785428000001</v>
+        <v>617.3161470000001</v>
       </c>
       <c r="N36">
-        <v>-536.4785428</v>
+        <v>-554.1161470000001</v>
       </c>
       <c r="O36">
-        <v>-138.4114640424</v>
+        <v>-142.961965926</v>
       </c>
       <c r="P36">
-        <v>-398.0670787576</v>
+        <v>-411.154181074</v>
       </c>
       <c r="Q36">
-        <v>-215.8670787576</v>
+        <v>-228.954181074</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1288862730694685</v>
+        <v>0.1301645234243834</v>
       </c>
       <c r="T36">
-        <v>1.918851572043152</v>
+        <v>1.948372365459201</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.02719056767291759</v>
+        <v>0.02641369431083422</v>
       </c>
       <c r="W36">
-        <v>0.229388464142726</v>
+        <v>0.2295716508815053</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.1053897971818512</v>
+        <v>0.1023786601195126</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4663,22 +4663,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1649570180343761</v>
+        <v>0.1668570180343761</v>
       </c>
       <c r="C37">
-        <v>925.1790306240218</v>
+        <v>798.8774927338595</v>
       </c>
       <c r="D37">
-        <v>3281.444030624022</v>
+        <v>3229.94149273386</v>
       </c>
       <c r="E37">
-        <v>2154.965</v>
+        <v>2229.764</v>
       </c>
       <c r="F37">
-        <v>2617.965</v>
+        <v>2692.764</v>
       </c>
       <c r="G37">
         <v>261.7</v>
@@ -4699,37 +4699,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M37">
-        <v>617.3161470000001</v>
+        <v>634.9537512000001</v>
       </c>
       <c r="N37">
-        <v>-554.1161470000001</v>
+        <v>-571.7537512</v>
       </c>
       <c r="O37">
-        <v>-142.961965926</v>
+        <v>-147.5124678096</v>
       </c>
       <c r="P37">
-        <v>-411.154181074</v>
+        <v>-424.2412833904</v>
       </c>
       <c r="Q37">
-        <v>-228.954181074</v>
+        <v>-242.0412833904</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1301645234243834</v>
+        <v>0.1314827191028894</v>
       </c>
       <c r="T37">
-        <v>1.948372365459201</v>
+        <v>1.978815683669501</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.02641369431083422</v>
+        <v>0.02567998057997772</v>
       </c>
       <c r="W37">
-        <v>0.2295716508815053</v>
+        <v>0.2297446605792413</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.1023786601195126</v>
+        <v>0.09953480844952611</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4745,22 +4745,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1668570180343761</v>
+        <v>0.168757018034376</v>
       </c>
       <c r="C38">
-        <v>798.87749273386</v>
+        <v>674.1676463722597</v>
       </c>
       <c r="D38">
-        <v>3229.94149273386</v>
+        <v>3180.03064637226</v>
       </c>
       <c r="E38">
-        <v>2229.764</v>
+        <v>2304.563</v>
       </c>
       <c r="F38">
-        <v>2692.764</v>
+        <v>2767.563</v>
       </c>
       <c r="G38">
         <v>261.7</v>
@@ -4781,37 +4781,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M38">
-        <v>634.9537511999999</v>
+        <v>652.5913554</v>
       </c>
       <c r="N38">
-        <v>-571.7537511999999</v>
+        <v>-589.3913554</v>
       </c>
       <c r="O38">
-        <v>-147.5124678096</v>
+        <v>-152.0629696932</v>
       </c>
       <c r="P38">
-        <v>-424.2412833903999</v>
+        <v>-437.3283857068</v>
       </c>
       <c r="Q38">
-        <v>-242.0412833903999</v>
+        <v>-255.1283857068</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1314827191028894</v>
+        <v>0.1328427622632527</v>
       </c>
       <c r="T38">
-        <v>1.978815683669501</v>
+        <v>2.010225456426159</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.02567998057997772</v>
+        <v>0.02498592705078913</v>
       </c>
       <c r="W38">
-        <v>0.2297446605792413</v>
+        <v>0.2299083184014239</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.09953480844952611</v>
+        <v>0.09684467849143075</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4827,22 +4827,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.168757018034376</v>
+        <v>0.1706570180343761</v>
       </c>
       <c r="C39">
-        <v>674.1676463722597</v>
+        <v>550.9768272880979</v>
       </c>
       <c r="D39">
-        <v>3180.03064637226</v>
+        <v>3131.638827288098</v>
       </c>
       <c r="E39">
-        <v>2304.563</v>
+        <v>2379.362</v>
       </c>
       <c r="F39">
-        <v>2767.563</v>
+        <v>2842.362</v>
       </c>
       <c r="G39">
         <v>261.7</v>
@@ -4863,37 +4863,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M39">
-        <v>652.5913554</v>
+        <v>670.2289596000001</v>
       </c>
       <c r="N39">
-        <v>-589.3913554</v>
+        <v>-607.0289596</v>
       </c>
       <c r="O39">
-        <v>-152.0629696932</v>
+        <v>-156.6134715768</v>
       </c>
       <c r="P39">
-        <v>-437.3283857068</v>
+        <v>-450.4154880232</v>
       </c>
       <c r="Q39">
-        <v>-255.1283857068</v>
+        <v>-268.2154880232</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1328427622632527</v>
+        <v>0.1342466777836277</v>
       </c>
       <c r="T39">
-        <v>2.010225456426159</v>
+        <v>2.042648447658839</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.02498592705078913</v>
+        <v>0.02432840265471574</v>
       </c>
       <c r="W39">
-        <v>0.2299083184014239</v>
+        <v>0.2300633626540181</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.09684467849143075</v>
+        <v>0.09429613432060369</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4909,22 +4909,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1706570180343761</v>
+        <v>0.1725570180343761</v>
       </c>
       <c r="C40">
-        <v>550.9768272880979</v>
+        <v>429.236727977654</v>
       </c>
       <c r="D40">
-        <v>3131.638827288098</v>
+        <v>3084.697727977654</v>
       </c>
       <c r="E40">
-        <v>2379.362</v>
+        <v>2454.161</v>
       </c>
       <c r="F40">
-        <v>2842.362</v>
+        <v>2917.161</v>
       </c>
       <c r="G40">
         <v>261.7</v>
@@ -4945,37 +4945,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M40">
-        <v>670.2289596000001</v>
+        <v>687.8665638</v>
       </c>
       <c r="N40">
-        <v>-607.0289596</v>
+        <v>-624.6665637999999</v>
       </c>
       <c r="O40">
-        <v>-156.6134715768</v>
+        <v>-161.1639734604</v>
       </c>
       <c r="P40">
-        <v>-450.4154880232</v>
+        <v>-463.5025903395999</v>
       </c>
       <c r="Q40">
-        <v>-268.2154880232</v>
+        <v>-281.3025903395999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1342466777836277</v>
+        <v>0.1356966233210642</v>
       </c>
       <c r="T40">
-        <v>2.042648447658839</v>
+        <v>2.076134487784394</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.02432840265471574</v>
+        <v>0.02370459745844097</v>
       </c>
       <c r="W40">
-        <v>0.2300633626540181</v>
+        <v>0.2302104559192996</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.09429613432060369</v>
+        <v>0.09187828472263948</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4991,22 +4991,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1725570180343761</v>
+        <v>0.1744570180343761</v>
       </c>
       <c r="C41">
-        <v>429.236727977654</v>
+        <v>308.8830759835309</v>
       </c>
       <c r="D41">
-        <v>3084.697727977654</v>
+        <v>3039.143075983531</v>
       </c>
       <c r="E41">
-        <v>2454.161</v>
+        <v>2528.96</v>
       </c>
       <c r="F41">
-        <v>2917.161</v>
+        <v>2991.96</v>
       </c>
       <c r="G41">
         <v>261.7</v>
@@ -5027,37 +5027,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M41">
-        <v>687.8665638</v>
+        <v>705.504168</v>
       </c>
       <c r="N41">
-        <v>-624.6665637999999</v>
+        <v>-642.304168</v>
       </c>
       <c r="O41">
-        <v>-161.1639734604</v>
+        <v>-165.714475344</v>
       </c>
       <c r="P41">
-        <v>-463.5025903395999</v>
+        <v>-476.589692656</v>
       </c>
       <c r="Q41">
-        <v>-281.3025903395999</v>
+        <v>-294.389692656</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1356966233210642</v>
+        <v>0.1371949003764154</v>
       </c>
       <c r="T41">
-        <v>2.076134487784394</v>
+        <v>2.110736729247467</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.02370459745844097</v>
+        <v>0.02311198252197995</v>
       </c>
       <c r="W41">
-        <v>0.2302104559192996</v>
+        <v>0.2303501945213171</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.09187828472263948</v>
+        <v>0.08958132760457349</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -5073,22 +5073,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1744570180343761</v>
+        <v>0.176357018034376</v>
       </c>
       <c r="C42">
-        <v>308.8830759835309</v>
+        <v>189.8553402839443</v>
       </c>
       <c r="D42">
-        <v>3039.143075983531</v>
+        <v>2994.914340283945</v>
       </c>
       <c r="E42">
-        <v>2528.96</v>
+        <v>2603.759</v>
       </c>
       <c r="F42">
-        <v>2991.96</v>
+        <v>3066.759</v>
       </c>
       <c r="G42">
         <v>261.7</v>
@@ -5109,37 +5109,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M42">
-        <v>705.504168</v>
+        <v>723.1417722</v>
       </c>
       <c r="N42">
-        <v>-642.304168</v>
+        <v>-659.9417721999999</v>
       </c>
       <c r="O42">
-        <v>-165.714475344</v>
+        <v>-170.2649772276</v>
       </c>
       <c r="P42">
-        <v>-476.589692656</v>
+        <v>-489.6767949724</v>
       </c>
       <c r="Q42">
-        <v>-294.389692656</v>
+        <v>-307.4767949724</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1371949003764154</v>
+        <v>0.1387439664844902</v>
       </c>
       <c r="T42">
-        <v>2.110736729247467</v>
+        <v>2.146511928048272</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.02311198252197995</v>
+        <v>0.02254827563119995</v>
       </c>
       <c r="W42">
-        <v>0.2303501945213171</v>
+        <v>0.2304831166061631</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.08958132760457349</v>
+        <v>0.08739641717519364</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5155,22 +5155,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.176357018034376</v>
+        <v>0.1782570180343761</v>
       </c>
       <c r="C43">
-        <v>189.8553402839443</v>
+        <v>72.09646295179073</v>
       </c>
       <c r="D43">
-        <v>2994.914340283945</v>
+        <v>2951.954462951791</v>
       </c>
       <c r="E43">
-        <v>2603.759</v>
+        <v>2678.558</v>
       </c>
       <c r="F43">
-        <v>3066.759</v>
+        <v>3141.558</v>
       </c>
       <c r="G43">
         <v>261.7</v>
@@ -5191,37 +5191,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M43">
-        <v>723.1417722</v>
+        <v>740.7793764</v>
       </c>
       <c r="N43">
-        <v>-659.9417721999999</v>
+        <v>-677.5793764</v>
       </c>
       <c r="O43">
-        <v>-170.2649772276</v>
+        <v>-174.8154791112</v>
       </c>
       <c r="P43">
-        <v>-489.6767949724</v>
+        <v>-502.7638972888</v>
       </c>
       <c r="Q43">
-        <v>-307.4767949724</v>
+        <v>-320.5638972888</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1387439664844902</v>
+        <v>0.1403464486652573</v>
       </c>
       <c r="T43">
-        <v>2.146511928048272</v>
+        <v>2.183520754393932</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.02254827563119995</v>
+        <v>0.02201141192569519</v>
       </c>
       <c r="W43">
-        <v>0.2304831166061631</v>
+        <v>0.2306097090679211</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.08739641717519364</v>
+        <v>0.0853155500995938</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5237,22 +5237,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.178257018034376</v>
+        <v>0.1801570180343761</v>
       </c>
       <c r="C44">
-        <v>72.09646295179209</v>
+        <v>-44.4473864179181</v>
       </c>
       <c r="D44">
-        <v>2951.954462951792</v>
+        <v>2910.209613582082</v>
       </c>
       <c r="E44">
-        <v>2678.558</v>
+        <v>2753.357</v>
       </c>
       <c r="F44">
-        <v>3141.558</v>
+        <v>3216.357</v>
       </c>
       <c r="G44">
         <v>261.7</v>
@@ -5273,37 +5273,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M44">
-        <v>740.7793763999999</v>
+        <v>758.4169806</v>
       </c>
       <c r="N44">
-        <v>-677.5793763999999</v>
+        <v>-695.2169805999999</v>
       </c>
       <c r="O44">
-        <v>-174.8154791112</v>
+        <v>-179.3659809948</v>
       </c>
       <c r="P44">
-        <v>-502.7638972887999</v>
+        <v>-515.8509996051999</v>
       </c>
       <c r="Q44">
-        <v>-320.5638972887999</v>
+        <v>-333.6509996052</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1403464486652572</v>
+        <v>0.1420051582909635</v>
       </c>
       <c r="T44">
-        <v>2.183520754393931</v>
+        <v>2.221828136049965</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.02201141192569519</v>
+        <v>0.02149951862509763</v>
       </c>
       <c r="W44">
-        <v>0.2306097090679211</v>
+        <v>0.230730413508202</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.0853155500995938</v>
+        <v>0.08333146753913812</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5319,22 +5319,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1801570180343761</v>
+        <v>0.1820570180343761</v>
       </c>
       <c r="C45">
-        <v>-44.4473864179181</v>
+        <v>-159.8270357347192</v>
       </c>
       <c r="D45">
-        <v>2910.209613582082</v>
+        <v>2869.628964265281</v>
       </c>
       <c r="E45">
-        <v>2753.357</v>
+        <v>2828.156</v>
       </c>
       <c r="F45">
-        <v>3216.357</v>
+        <v>3291.156</v>
       </c>
       <c r="G45">
         <v>261.7</v>
@@ -5355,37 +5355,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M45">
-        <v>758.4169806</v>
+        <v>776.0545848</v>
       </c>
       <c r="N45">
-        <v>-695.2169805999999</v>
+        <v>-712.8545848</v>
       </c>
       <c r="O45">
-        <v>-179.3659809948</v>
+        <v>-183.9164828784</v>
       </c>
       <c r="P45">
-        <v>-515.8509996051999</v>
+        <v>-528.9381019216</v>
       </c>
       <c r="Q45">
-        <v>-333.6509996052</v>
+        <v>-346.7381019216</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1420051582909635</v>
+        <v>0.1437231075461593</v>
       </c>
       <c r="T45">
-        <v>2.221828136049965</v>
+        <v>2.261503638479429</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.02149951862509763</v>
+        <v>0.02101089320179995</v>
       </c>
       <c r="W45">
-        <v>0.230730413508202</v>
+        <v>0.2308456313830156</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.08333146753913812</v>
+        <v>0.0814375705496122</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5401,22 +5401,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1820570180343761</v>
+        <v>0.1839570180343761</v>
       </c>
       <c r="C46">
-        <v>-159.8270357347192</v>
+        <v>-274.0905168713002</v>
       </c>
       <c r="D46">
-        <v>2869.628964265281</v>
+        <v>2830.1644831287</v>
       </c>
       <c r="E46">
-        <v>2828.156</v>
+        <v>2902.955</v>
       </c>
       <c r="F46">
-        <v>3291.156</v>
+        <v>3365.955</v>
       </c>
       <c r="G46">
         <v>261.7</v>
@@ -5437,37 +5437,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M46">
-        <v>776.0545848</v>
+        <v>793.692189</v>
       </c>
       <c r="N46">
-        <v>-712.8545848</v>
+        <v>-730.4921889999999</v>
       </c>
       <c r="O46">
-        <v>-183.9164828784</v>
+        <v>-188.466984762</v>
       </c>
       <c r="P46">
-        <v>-528.9381019216</v>
+        <v>-542.025204238</v>
       </c>
       <c r="Q46">
-        <v>-346.7381019216</v>
+        <v>-359.825204238</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1437231075461593</v>
+        <v>0.1455035276833622</v>
       </c>
       <c r="T46">
-        <v>2.261503638479429</v>
+        <v>2.302621886451782</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.02101089320179995</v>
+        <v>0.02054398446398218</v>
       </c>
       <c r="W46">
-        <v>0.2308456313830156</v>
+        <v>0.230955728463393</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.0814375705496122</v>
+        <v>0.07962784675962087</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5483,22 +5483,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1839570180343761</v>
+        <v>0.1858570180343761</v>
       </c>
       <c r="C47">
-        <v>-274.0905168713002</v>
+        <v>-387.2832553173439</v>
       </c>
       <c r="D47">
-        <v>2830.1644831287</v>
+        <v>2791.770744682656</v>
       </c>
       <c r="E47">
-        <v>2902.955</v>
+        <v>2977.754</v>
       </c>
       <c r="F47">
-        <v>3365.955</v>
+        <v>3440.754</v>
       </c>
       <c r="G47">
         <v>261.7</v>
@@ -5519,37 +5519,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M47">
-        <v>793.692189</v>
+        <v>811.3297932</v>
       </c>
       <c r="N47">
-        <v>-730.4921889999999</v>
+        <v>-748.1297932</v>
       </c>
       <c r="O47">
-        <v>-188.466984762</v>
+        <v>-193.0174866456</v>
       </c>
       <c r="P47">
-        <v>-542.025204238</v>
+        <v>-555.1123065544</v>
       </c>
       <c r="Q47">
-        <v>-359.825204238</v>
+        <v>-372.9123065544</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1455035276833622</v>
+        <v>0.1473498893071281</v>
       </c>
       <c r="T47">
-        <v>2.302621886451782</v>
+        <v>2.345263032497186</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.02054398446398218</v>
+        <v>0.02009737610606952</v>
       </c>
       <c r="W47">
-        <v>0.230955728463393</v>
+        <v>0.2310610387141888</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.07962784675962087</v>
+        <v>0.07789680661267262</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1858570180343761</v>
+        <v>0.1877570180343761</v>
       </c>
       <c r="C48">
-        <v>-387.2832553173439</v>
+        <v>-499.4482446030052</v>
       </c>
       <c r="D48">
-        <v>2791.770744682656</v>
+        <v>2754.404755396995</v>
       </c>
       <c r="E48">
-        <v>2977.754</v>
+        <v>3052.553</v>
       </c>
       <c r="F48">
-        <v>3440.754</v>
+        <v>3515.553</v>
       </c>
       <c r="G48">
         <v>261.7</v>
@@ -5601,37 +5601,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M48">
-        <v>811.3297932</v>
+        <v>828.9673974</v>
       </c>
       <c r="N48">
-        <v>-748.1297932</v>
+        <v>-765.7673973999999</v>
       </c>
       <c r="O48">
-        <v>-193.0174866456</v>
+        <v>-197.5679885292</v>
       </c>
       <c r="P48">
-        <v>-555.1123065544</v>
+        <v>-568.1994088708</v>
       </c>
       <c r="Q48">
-        <v>-372.9123065544</v>
+        <v>-385.9994088708</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1473498893071281</v>
+        <v>0.1492659249544324</v>
       </c>
       <c r="T48">
-        <v>2.345263032497186</v>
+        <v>2.389513278393359</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.02009737610606952</v>
+        <v>0.01966977235913187</v>
       </c>
       <c r="W48">
-        <v>0.2310610387141888</v>
+        <v>0.2311618676777167</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5639,7 +5639,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.07789680661267262</v>
+        <v>0.07623942774857317</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5647,22 +5647,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1877570180343761</v>
+        <v>0.1896570180343761</v>
       </c>
       <c r="C49">
-        <v>-499.4482446030052</v>
+        <v>-610.626206900165</v>
       </c>
       <c r="D49">
-        <v>2754.404755396995</v>
+        <v>2718.025793099835</v>
       </c>
       <c r="E49">
-        <v>3052.553</v>
+        <v>3127.352</v>
       </c>
       <c r="F49">
-        <v>3515.553</v>
+        <v>3590.352</v>
       </c>
       <c r="G49">
         <v>261.7</v>
@@ -5683,37 +5683,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M49">
-        <v>828.9673974</v>
+        <v>846.6050016000002</v>
       </c>
       <c r="N49">
-        <v>-765.7673973999999</v>
+        <v>-783.4050016000001</v>
       </c>
       <c r="O49">
-        <v>-197.5679885292</v>
+        <v>-202.1184904128</v>
       </c>
       <c r="P49">
-        <v>-568.1994088708</v>
+        <v>-581.2865111872001</v>
       </c>
       <c r="Q49">
-        <v>-385.9994088708</v>
+        <v>-399.0865111872001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1492659249544324</v>
+        <v>0.1512556542804792</v>
       </c>
       <c r="T49">
-        <v>2.389513278393359</v>
+        <v>2.435465456824001</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.01966977235913187</v>
+        <v>0.01925998543498329</v>
       </c>
       <c r="W49">
-        <v>0.2311618676777167</v>
+        <v>0.2312584954344309</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.07623942774857317</v>
+        <v>0.07465110633714456</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5729,22 +5729,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.189657018034376</v>
+        <v>0.191557018034376</v>
       </c>
       <c r="C50">
-        <v>-610.6262069001641</v>
+        <v>-720.855741062654</v>
       </c>
       <c r="D50">
-        <v>2718.025793099836</v>
+        <v>2682.595258937346</v>
       </c>
       <c r="E50">
-        <v>3127.352</v>
+        <v>3202.151</v>
       </c>
       <c r="F50">
-        <v>3590.352</v>
+        <v>3665.151</v>
       </c>
       <c r="G50">
         <v>261.7</v>
@@ -5765,37 +5765,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M50">
-        <v>846.6050016</v>
+        <v>864.2426058</v>
       </c>
       <c r="N50">
-        <v>-783.4050016</v>
+        <v>-801.0426057999999</v>
       </c>
       <c r="O50">
-        <v>-202.1184904128</v>
+        <v>-206.6689922964</v>
       </c>
       <c r="P50">
-        <v>-581.2865111871999</v>
+        <v>-594.3736135035999</v>
       </c>
       <c r="Q50">
-        <v>-399.0865111872</v>
+        <v>-412.1736135035999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1512556542804792</v>
+        <v>0.1533234122075474</v>
       </c>
       <c r="T50">
-        <v>2.435465456824</v>
+        <v>2.483219681467608</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.01925998543498329</v>
+        <v>0.01886692450773873</v>
       </c>
       <c r="W50">
-        <v>0.2312584954344309</v>
+        <v>0.2313511792010752</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.07465110633714456</v>
+        <v>0.0731276143710804</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5811,22 +5811,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.191557018034376</v>
+        <v>0.193457018034376</v>
       </c>
       <c r="C51">
-        <v>-720.855741062654</v>
+        <v>-830.1734592369189</v>
       </c>
       <c r="D51">
-        <v>2682.595258937346</v>
+        <v>2648.076540763081</v>
       </c>
       <c r="E51">
-        <v>3202.151</v>
+        <v>3276.95</v>
       </c>
       <c r="F51">
-        <v>3665.151</v>
+        <v>3739.95</v>
       </c>
       <c r="G51">
         <v>261.7</v>
@@ -5847,37 +5847,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M51">
-        <v>864.2426058</v>
+        <v>881.88021</v>
       </c>
       <c r="N51">
-        <v>-801.0426057999999</v>
+        <v>-818.68021</v>
       </c>
       <c r="O51">
-        <v>-206.6689922964</v>
+        <v>-211.21949418</v>
       </c>
       <c r="P51">
-        <v>-594.3736135035999</v>
+        <v>-607.46071582</v>
       </c>
       <c r="Q51">
-        <v>-412.1736135035999</v>
+        <v>-425.26071582</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1533234122075474</v>
+        <v>0.1554738804516984</v>
       </c>
       <c r="T51">
-        <v>2.483219681467608</v>
+        <v>2.532884075096961</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.01886692450773873</v>
+        <v>0.01848958601758396</v>
       </c>
       <c r="W51">
-        <v>0.2313511792010752</v>
+        <v>0.2314401556170537</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.0731276143710804</v>
+        <v>0.07166506208365875</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5893,22 +5893,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.193457018034376</v>
+        <v>0.1953570180343761</v>
       </c>
       <c r="C52">
-        <v>-830.1734592369189</v>
+        <v>-938.6141130594992</v>
       </c>
       <c r="D52">
-        <v>2648.076540763081</v>
+        <v>2614.434886940501</v>
       </c>
       <c r="E52">
-        <v>3276.95</v>
+        <v>3351.749</v>
       </c>
       <c r="F52">
-        <v>3739.95</v>
+        <v>3814.749</v>
       </c>
       <c r="G52">
         <v>261.7</v>
@@ -5929,37 +5929,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M52">
-        <v>881.88021</v>
+        <v>899.5178142</v>
       </c>
       <c r="N52">
-        <v>-818.68021</v>
+        <v>-836.3178141999999</v>
       </c>
       <c r="O52">
-        <v>-211.21949418</v>
+        <v>-215.7699960636</v>
       </c>
       <c r="P52">
-        <v>-607.46071582</v>
+        <v>-620.5478181363999</v>
       </c>
       <c r="Q52">
-        <v>-425.26071582</v>
+        <v>-438.3478181363999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1554738804516984</v>
+        <v>0.1577121229098963</v>
       </c>
       <c r="T52">
-        <v>2.532884075096961</v>
+        <v>2.584575586833633</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.01848958601758396</v>
+        <v>0.01812704511527839</v>
       </c>
       <c r="W52">
-        <v>0.2314401556170537</v>
+        <v>0.2315256427618174</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.07166506208365875</v>
+        <v>0.07025986478790081</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5975,22 +5975,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1953570180343761</v>
+        <v>0.1972570180343761</v>
       </c>
       <c r="C53">
-        <v>-938.6141130594992</v>
+        <v>-1046.210710355781</v>
       </c>
       <c r="D53">
-        <v>2614.434886940501</v>
+        <v>2581.637289644219</v>
       </c>
       <c r="E53">
-        <v>3351.749</v>
+        <v>3426.548</v>
       </c>
       <c r="F53">
-        <v>3814.749</v>
+        <v>3889.548</v>
       </c>
       <c r="G53">
         <v>261.7</v>
@@ -6011,37 +6011,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M53">
-        <v>899.5178142</v>
+        <v>917.1554184</v>
       </c>
       <c r="N53">
-        <v>-836.3178141999999</v>
+        <v>-853.9554184</v>
       </c>
       <c r="O53">
-        <v>-215.7699960636</v>
+        <v>-220.3204979472</v>
       </c>
       <c r="P53">
-        <v>-620.5478181363999</v>
+        <v>-633.6349204528</v>
       </c>
       <c r="Q53">
-        <v>-438.3478181363999</v>
+        <v>-451.4349204528</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1577121229098963</v>
+        <v>0.1600436254705192</v>
       </c>
       <c r="T53">
-        <v>2.584575586833633</v>
+        <v>2.638420911559334</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.01812704511527839</v>
+        <v>0.01777844809383073</v>
       </c>
       <c r="W53">
-        <v>0.2315256427618174</v>
+        <v>0.2316078419394747</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.07025986478790081</v>
+        <v>0.06890871354197958</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -6057,22 +6057,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1972570180343761</v>
+        <v>0.1991570180343761</v>
       </c>
       <c r="C54">
-        <v>-1046.210710355781</v>
+        <v>-1152.994623163778</v>
       </c>
       <c r="D54">
-        <v>2581.637289644219</v>
+        <v>2549.652376836223</v>
       </c>
       <c r="E54">
-        <v>3426.548</v>
+        <v>3501.347</v>
       </c>
       <c r="F54">
-        <v>3889.548</v>
+        <v>3964.347</v>
       </c>
       <c r="G54">
         <v>261.7</v>
@@ -6093,37 +6093,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M54">
-        <v>917.1554184</v>
+        <v>934.7930226000001</v>
       </c>
       <c r="N54">
-        <v>-853.9554184</v>
+        <v>-871.5930226</v>
       </c>
       <c r="O54">
-        <v>-220.3204979472</v>
+        <v>-224.8709998308</v>
       </c>
       <c r="P54">
-        <v>-633.6349204528</v>
+        <v>-646.7220227692001</v>
       </c>
       <c r="Q54">
-        <v>-451.4349204528</v>
+        <v>-464.5220227692001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1600436254705192</v>
+        <v>0.1624743409060621</v>
       </c>
       <c r="T54">
-        <v>2.638420911559334</v>
+        <v>2.694557526698894</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.01777844809383073</v>
+        <v>0.017443005676966</v>
       </c>
       <c r="W54">
-        <v>0.2316078419394747</v>
+        <v>0.2316869392613714</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.06890871354197958</v>
+        <v>0.06760854913552716</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6139,22 +6139,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1991570180343761</v>
+        <v>0.201057018034376</v>
       </c>
       <c r="C55">
-        <v>-1152.994623163778</v>
+        <v>-1258.995687826105</v>
       </c>
       <c r="D55">
-        <v>2549.652376836223</v>
+        <v>2518.450312173895</v>
       </c>
       <c r="E55">
-        <v>3501.347</v>
+        <v>3576.146</v>
       </c>
       <c r="F55">
-        <v>3964.347</v>
+        <v>4039.146</v>
       </c>
       <c r="G55">
         <v>261.7</v>
@@ -6175,37 +6175,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M55">
-        <v>934.7930226000001</v>
+        <v>952.4306268</v>
       </c>
       <c r="N55">
-        <v>-871.5930226</v>
+        <v>-889.2306268</v>
       </c>
       <c r="O55">
-        <v>-224.8709998308</v>
+        <v>-229.4215017144</v>
       </c>
       <c r="P55">
-        <v>-646.7220227692001</v>
+        <v>-659.8091250856</v>
       </c>
       <c r="Q55">
-        <v>-464.5220227692001</v>
+        <v>-477.6091250856001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1624743409060621</v>
+        <v>0.1650107396214113</v>
       </c>
       <c r="T55">
-        <v>2.694557526698894</v>
+        <v>2.753134864235827</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.017443005676966</v>
+        <v>0.01711998705331848</v>
       </c>
       <c r="W55">
-        <v>0.2316869392613714</v>
+        <v>0.2317631070528275</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.06760854913552716</v>
+        <v>0.06635653896635074</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6221,22 +6221,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.201057018034376</v>
+        <v>0.202957018034376</v>
       </c>
       <c r="C56">
-        <v>-1258.995687826105</v>
+        <v>-1364.242297821375</v>
       </c>
       <c r="D56">
-        <v>2518.450312173895</v>
+        <v>2488.002702178625</v>
       </c>
       <c r="E56">
-        <v>3576.146</v>
+        <v>3650.945</v>
       </c>
       <c r="F56">
-        <v>4039.146</v>
+        <v>4113.945</v>
       </c>
       <c r="G56">
         <v>261.7</v>
@@ -6257,37 +6257,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M56">
-        <v>952.4306268</v>
+        <v>970.068231</v>
       </c>
       <c r="N56">
-        <v>-889.2306268</v>
+        <v>-906.8682309999999</v>
       </c>
       <c r="O56">
-        <v>-229.4215017144</v>
+        <v>-233.972003598</v>
       </c>
       <c r="P56">
-        <v>-659.8091250856</v>
+        <v>-672.8962274019999</v>
       </c>
       <c r="Q56">
-        <v>-477.6091250856001</v>
+        <v>-490.6962274019999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1650107396214113</v>
+        <v>0.1676598671685538</v>
       </c>
       <c r="T56">
-        <v>2.753134864235827</v>
+        <v>2.814315638996623</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.01711998705331848</v>
+        <v>0.01680871456143996</v>
       </c>
       <c r="W56">
-        <v>0.2317631070528275</v>
+        <v>0.2318365051064125</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.06635653896635074</v>
+        <v>0.06515005643968985</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6303,22 +6303,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.202957018034376</v>
+        <v>0.2048570180343761</v>
       </c>
       <c r="C57">
-        <v>-1364.242297821375</v>
+        <v>-1468.761489942153</v>
       </c>
       <c r="D57">
-        <v>2488.002702178625</v>
+        <v>2458.282510057848</v>
       </c>
       <c r="E57">
-        <v>3650.945</v>
+        <v>3725.744000000001</v>
       </c>
       <c r="F57">
-        <v>4113.945</v>
+        <v>4188.744000000001</v>
       </c>
       <c r="G57">
         <v>261.7</v>
@@ -6339,37 +6339,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M57">
-        <v>970.068231</v>
+        <v>987.7058352000001</v>
       </c>
       <c r="N57">
-        <v>-906.8682309999999</v>
+        <v>-924.5058352000001</v>
       </c>
       <c r="O57">
-        <v>-233.972003598</v>
+        <v>-238.5225054816</v>
       </c>
       <c r="P57">
-        <v>-672.8962274019999</v>
+        <v>-685.9833297184</v>
       </c>
       <c r="Q57">
-        <v>-490.6962274019999</v>
+        <v>-503.7833297184</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1676598671685538</v>
+        <v>0.1704294096042027</v>
       </c>
       <c r="T57">
-        <v>2.814315638996623</v>
+        <v>2.878277358064728</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.01680871456143996</v>
+        <v>0.01650855894427139</v>
       </c>
       <c r="W57">
-        <v>0.2318365051064125</v>
+        <v>0.2319072818009408</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.06515005643968985</v>
+        <v>0.06398666257469532</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6385,22 +6385,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2048570180343761</v>
+        <v>0.206757018034376</v>
       </c>
       <c r="C58">
-        <v>-1468.761489942153</v>
+        <v>-1572.579024369228</v>
       </c>
       <c r="D58">
-        <v>2458.282510057848</v>
+        <v>2429.263975630773</v>
       </c>
       <c r="E58">
-        <v>3725.744000000001</v>
+        <v>3800.543000000001</v>
       </c>
       <c r="F58">
-        <v>4188.744000000001</v>
+        <v>4263.543000000001</v>
       </c>
       <c r="G58">
         <v>261.7</v>
@@ -6421,37 +6421,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M58">
-        <v>987.7058352000001</v>
+        <v>1005.3434394</v>
       </c>
       <c r="N58">
-        <v>-924.5058352000001</v>
+        <v>-942.1434394000001</v>
       </c>
       <c r="O58">
-        <v>-238.5225054816</v>
+        <v>-243.0730073652001</v>
       </c>
       <c r="P58">
-        <v>-685.9833297184</v>
+        <v>-699.0704320348001</v>
       </c>
       <c r="Q58">
-        <v>-503.7833297184</v>
+        <v>-516.8704320348002</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1704294096042027</v>
+        <v>0.1733277679670912</v>
       </c>
       <c r="T58">
-        <v>2.878277358064728</v>
+        <v>2.94521404081042</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.01650855894427139</v>
+        <v>0.01621893510314382</v>
       </c>
       <c r="W58">
-        <v>0.2319072818009408</v>
+        <v>0.2319755751026787</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.06398666257469532</v>
+        <v>0.06286408954706912</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6467,22 +6467,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.206757018034376</v>
+        <v>0.2086570180343761</v>
       </c>
       <c r="C59">
-        <v>-1572.579024369228</v>
+        <v>-1675.719459140704</v>
       </c>
       <c r="D59">
-        <v>2429.263975630773</v>
+        <v>2400.922540859297</v>
       </c>
       <c r="E59">
-        <v>3800.543000000001</v>
+        <v>3875.342000000001</v>
       </c>
       <c r="F59">
-        <v>4263.543000000001</v>
+        <v>4338.342000000001</v>
       </c>
       <c r="G59">
         <v>261.7</v>
@@ -6503,37 +6503,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M59">
-        <v>1005.3434394</v>
+        <v>1022.9810436</v>
       </c>
       <c r="N59">
-        <v>-942.1434394000001</v>
+        <v>-959.7810436000001</v>
       </c>
       <c r="O59">
-        <v>-243.0730073652001</v>
+        <v>-247.6235092488</v>
       </c>
       <c r="P59">
-        <v>-699.0704320348001</v>
+        <v>-712.1575343512001</v>
       </c>
       <c r="Q59">
-        <v>-516.8704320348002</v>
+        <v>-529.9575343512001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1733277679670912</v>
+        <v>0.1763641433948791</v>
       </c>
       <c r="T59">
-        <v>2.94521404081042</v>
+        <v>3.015338184639239</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.01621893510314382</v>
+        <v>0.01593929829102065</v>
       </c>
       <c r="W59">
-        <v>0.2319755751026787</v>
+        <v>0.2320415134629773</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.06286408954706912</v>
+        <v>0.06178022593418864</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6549,22 +6549,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.208657018034376</v>
+        <v>0.210557018034376</v>
       </c>
       <c r="C60">
-        <v>-1675.719459140703</v>
+        <v>-1778.206219468345</v>
       </c>
       <c r="D60">
-        <v>2400.922540859297</v>
+        <v>2373.234780531655</v>
       </c>
       <c r="E60">
-        <v>3875.342</v>
+        <v>3950.141</v>
       </c>
       <c r="F60">
-        <v>4338.342</v>
+        <v>4413.141</v>
       </c>
       <c r="G60">
         <v>261.7</v>
@@ -6585,37 +6585,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M60">
-        <v>1022.9810436</v>
+        <v>1040.6186478</v>
       </c>
       <c r="N60">
-        <v>-959.7810435999999</v>
+        <v>-977.4186477999999</v>
       </c>
       <c r="O60">
-        <v>-247.6235092488</v>
+        <v>-252.1740111324</v>
       </c>
       <c r="P60">
-        <v>-712.1575343512</v>
+        <v>-725.2446366675999</v>
       </c>
       <c r="Q60">
-        <v>-529.9575343511999</v>
+        <v>-543.0446366675999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.176364143394879</v>
+        <v>0.1795486346971931</v>
       </c>
       <c r="T60">
-        <v>3.015338184639238</v>
+        <v>3.088883018410927</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.01593929829102065</v>
+        <v>0.01566914069286776</v>
       </c>
       <c r="W60">
-        <v>0.2320415134629773</v>
+        <v>0.2321052166246218</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.06178022593418864</v>
+        <v>0.0607331034607278</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.210557018034376</v>
+        <v>0.2124570180343761</v>
       </c>
       <c r="C61">
-        <v>-1778.206219468345</v>
+        <v>-1880.061662312415</v>
       </c>
       <c r="D61">
-        <v>2373.234780531655</v>
+        <v>2346.178337687585</v>
       </c>
       <c r="E61">
-        <v>3950.141</v>
+        <v>4024.94</v>
       </c>
       <c r="F61">
-        <v>4413.141</v>
+        <v>4487.94</v>
       </c>
       <c r="G61">
         <v>261.7</v>
@@ -6667,37 +6667,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M61">
-        <v>1040.6186478</v>
+        <v>1058.256252</v>
       </c>
       <c r="N61">
-        <v>-977.4186477999999</v>
+        <v>-995.0562519999999</v>
       </c>
       <c r="O61">
-        <v>-252.1740111324</v>
+        <v>-256.7245130159999</v>
       </c>
       <c r="P61">
-        <v>-725.2446366675999</v>
+        <v>-738.3317389839999</v>
       </c>
       <c r="Q61">
-        <v>-543.0446366675999</v>
+        <v>-556.1317389839999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1795486346971931</v>
+        <v>0.182892350564623</v>
       </c>
       <c r="T61">
-        <v>3.088883018410927</v>
+        <v>3.166105093871201</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.01566914069286776</v>
+        <v>0.01540798834798663</v>
       </c>
       <c r="W61">
-        <v>0.2321052166246218</v>
+        <v>0.2321667963475448</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.0607331034607278</v>
+        <v>0.05972088506971562</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6713,22 +6713,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2124570180343761</v>
+        <v>0.2143570180343761</v>
       </c>
       <c r="C62">
-        <v>-1880.061662312415</v>
+        <v>-1981.307136589132</v>
       </c>
       <c r="D62">
-        <v>2346.178337687585</v>
+        <v>2319.731863410867</v>
       </c>
       <c r="E62">
-        <v>4024.94</v>
+        <v>4099.739</v>
       </c>
       <c r="F62">
-        <v>4487.94</v>
+        <v>4562.739</v>
       </c>
       <c r="G62">
         <v>261.7</v>
@@ -6749,37 +6749,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M62">
-        <v>1058.256252</v>
+        <v>1075.8938562</v>
       </c>
       <c r="N62">
-        <v>-995.0562519999999</v>
+        <v>-1012.6938562</v>
       </c>
       <c r="O62">
-        <v>-256.7245130159999</v>
+        <v>-261.2750148996</v>
       </c>
       <c r="P62">
-        <v>-738.3317389839999</v>
+        <v>-751.4188413003999</v>
       </c>
       <c r="Q62">
-        <v>-556.1317389839999</v>
+        <v>-569.2188413003998</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.182892350564623</v>
+        <v>0.186407539040639</v>
       </c>
       <c r="T62">
-        <v>3.166105093871201</v>
+        <v>3.247287275765334</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.01540798834798663</v>
+        <v>0.01515539837506882</v>
       </c>
       <c r="W62">
-        <v>0.2321667963475448</v>
+        <v>0.2322263570631588</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.05972088506971562</v>
+        <v>0.05874185416693345</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6795,22 +6795,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2143570180343761</v>
+        <v>0.2162570180343761</v>
       </c>
       <c r="C63">
-        <v>-1981.307136589132</v>
+        <v>-2081.963039351516</v>
       </c>
       <c r="D63">
-        <v>2319.731863410867</v>
+        <v>2293.874960648484</v>
       </c>
       <c r="E63">
-        <v>4099.739</v>
+        <v>4174.538</v>
       </c>
       <c r="F63">
-        <v>4562.739</v>
+        <v>4637.538</v>
       </c>
       <c r="G63">
         <v>261.7</v>
@@ -6831,37 +6831,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M63">
-        <v>1075.8938562</v>
+        <v>1093.5314604</v>
       </c>
       <c r="N63">
-        <v>-1012.6938562</v>
+        <v>-1030.3314604</v>
       </c>
       <c r="O63">
-        <v>-261.2750148996</v>
+        <v>-265.8255167832</v>
       </c>
       <c r="P63">
-        <v>-751.4188413003999</v>
+        <v>-764.5059436168</v>
       </c>
       <c r="Q63">
-        <v>-569.2188413003998</v>
+        <v>-582.3059436168001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.186407539040639</v>
+        <v>0.1901077374364453</v>
       </c>
       <c r="T63">
-        <v>3.247287275765334</v>
+        <v>3.332742204074948</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.01515539837506882</v>
+        <v>0.01491095646579351</v>
       </c>
       <c r="W63">
-        <v>0.2322263570631588</v>
+        <v>0.2322839964653659</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.05874185416693345</v>
+        <v>0.05779440490617649</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6877,22 +6877,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2162570180343761</v>
+        <v>0.2181570180343761</v>
       </c>
       <c r="C64">
-        <v>-2081.963039351516</v>
+        <v>-2182.048868254316</v>
       </c>
       <c r="D64">
-        <v>2293.874960648484</v>
+        <v>2268.588131745684</v>
       </c>
       <c r="E64">
-        <v>4174.538</v>
+        <v>4249.337</v>
       </c>
       <c r="F64">
-        <v>4637.538</v>
+        <v>4712.337</v>
       </c>
       <c r="G64">
         <v>261.7</v>
@@ -6913,37 +6913,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M64">
-        <v>1093.5314604</v>
+        <v>1111.1690646</v>
       </c>
       <c r="N64">
-        <v>-1030.3314604</v>
+        <v>-1047.9690646</v>
       </c>
       <c r="O64">
-        <v>-265.8255167832</v>
+        <v>-270.3760186668</v>
       </c>
       <c r="P64">
-        <v>-764.5059436168</v>
+        <v>-777.5930459331998</v>
       </c>
       <c r="Q64">
-        <v>-582.3059436168001</v>
+        <v>-595.3930459331998</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1901077374364453</v>
+        <v>0.1940079465563492</v>
       </c>
       <c r="T64">
-        <v>3.332742204074948</v>
+        <v>3.422816317698596</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.01491095646579351</v>
+        <v>0.01467427461713013</v>
       </c>
       <c r="W64">
-        <v>0.2322839964653659</v>
+        <v>0.2323398060452807</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.05779440490617649</v>
+        <v>0.05687703339972916</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6959,22 +6959,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2181570180343761</v>
+        <v>0.2200570180343761</v>
       </c>
       <c r="C65">
-        <v>-2182.048868254316</v>
+        <v>-2281.583270586671</v>
       </c>
       <c r="D65">
-        <v>2268.588131745684</v>
+        <v>2243.852729413329</v>
       </c>
       <c r="E65">
-        <v>4249.337</v>
+        <v>4324.136</v>
       </c>
       <c r="F65">
-        <v>4712.337</v>
+        <v>4787.136</v>
       </c>
       <c r="G65">
         <v>261.7</v>
@@ -6995,37 +6995,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M65">
-        <v>1111.1690646</v>
+        <v>1128.8066688</v>
       </c>
       <c r="N65">
-        <v>-1047.9690646</v>
+        <v>-1065.6066688</v>
       </c>
       <c r="O65">
-        <v>-270.3760186668</v>
+        <v>-274.9265205504</v>
       </c>
       <c r="P65">
-        <v>-777.5930459331998</v>
+        <v>-790.6801482495998</v>
       </c>
       <c r="Q65">
-        <v>-595.3930459331998</v>
+        <v>-608.4801482495998</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1940079465563492</v>
+        <v>0.1981248339606922</v>
       </c>
       <c r="T65">
-        <v>3.422816317698596</v>
+        <v>3.517894548745779</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.01467427461713013</v>
+        <v>0.01444498907623747</v>
       </c>
       <c r="W65">
-        <v>0.2323398060452807</v>
+        <v>0.2323938715758232</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -7033,7 +7033,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.05687703339972916</v>
+        <v>0.05598832975285839</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -7041,22 +7041,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2200570180343761</v>
+        <v>0.2219570180343761</v>
       </c>
       <c r="C66">
-        <v>-2281.583270586671</v>
+        <v>-2380.584089131609</v>
       </c>
       <c r="D66">
-        <v>2243.852729413329</v>
+        <v>2219.65091086839</v>
       </c>
       <c r="E66">
-        <v>4324.136</v>
+        <v>4398.934999999999</v>
       </c>
       <c r="F66">
-        <v>4787.136</v>
+        <v>4861.934999999999</v>
       </c>
       <c r="G66">
         <v>261.7</v>
@@ -7077,37 +7077,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M66">
-        <v>1128.8066688</v>
+        <v>1146.444273</v>
       </c>
       <c r="N66">
-        <v>-1065.6066688</v>
+        <v>-1083.244273</v>
       </c>
       <c r="O66">
-        <v>-274.9265205504</v>
+        <v>-279.4770224339999</v>
       </c>
       <c r="P66">
-        <v>-790.6801482495998</v>
+        <v>-803.7672505659998</v>
       </c>
       <c r="Q66">
-        <v>-608.4801482495998</v>
+        <v>-621.5672505659998</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1981248339606922</v>
+        <v>0.2024769720738549</v>
       </c>
       <c r="T66">
-        <v>3.517894548745779</v>
+        <v>3.618405821567087</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.01444498907623747</v>
+        <v>0.01422275847506459</v>
       </c>
       <c r="W66">
-        <v>0.2323938715758232</v>
+        <v>0.2324462735515798</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.05598832975285839</v>
+        <v>0.05512697083358364</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7123,22 +7123,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2219570180343761</v>
+        <v>0.2238570180343761</v>
       </c>
       <c r="C67">
-        <v>-2380.584089131609</v>
+        <v>-2479.068405089422</v>
       </c>
       <c r="D67">
-        <v>2219.65091086839</v>
+        <v>2195.965594910579</v>
       </c>
       <c r="E67">
-        <v>4398.934999999999</v>
+        <v>4473.734</v>
       </c>
       <c r="F67">
-        <v>4861.934999999999</v>
+        <v>4936.734</v>
       </c>
       <c r="G67">
         <v>261.7</v>
@@ -7159,37 +7159,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M67">
-        <v>1146.444273</v>
+        <v>1164.0818772</v>
       </c>
       <c r="N67">
-        <v>-1083.244273</v>
+        <v>-1100.8818772</v>
       </c>
       <c r="O67">
-        <v>-279.4770224339999</v>
+        <v>-284.0275243176001</v>
       </c>
       <c r="P67">
-        <v>-803.7672505659998</v>
+        <v>-816.8543528824001</v>
       </c>
       <c r="Q67">
-        <v>-621.5672505659998</v>
+        <v>-634.6543528824002</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2024769720738549</v>
+        <v>0.2070851183113212</v>
       </c>
       <c r="T67">
-        <v>3.618405821567087</v>
+        <v>3.724829522201413</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.01422275847506459</v>
+        <v>0.0140072621345333</v>
       </c>
       <c r="W67">
-        <v>0.2324462735515798</v>
+        <v>0.2324970875886771</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.05512697083358364</v>
+        <v>0.05429171369974151</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7205,22 +7205,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2238570180343761</v>
+        <v>0.225757018034376</v>
       </c>
       <c r="C68">
-        <v>-2479.068405089422</v>
+        <v>-2577.052578281905</v>
       </c>
       <c r="D68">
-        <v>2195.965594910579</v>
+        <v>2172.780421718095</v>
       </c>
       <c r="E68">
-        <v>4473.734</v>
+        <v>4548.533</v>
       </c>
       <c r="F68">
-        <v>4936.734</v>
+        <v>5011.533</v>
       </c>
       <c r="G68">
         <v>261.7</v>
@@ -7241,37 +7241,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M68">
-        <v>1164.0818772</v>
+        <v>1181.7194814</v>
       </c>
       <c r="N68">
-        <v>-1100.8818772</v>
+        <v>-1118.5194814</v>
       </c>
       <c r="O68">
-        <v>-284.0275243176001</v>
+        <v>-288.5780262012</v>
       </c>
       <c r="P68">
-        <v>-816.8543528824001</v>
+        <v>-829.9414551988001</v>
       </c>
       <c r="Q68">
-        <v>-634.6543528824002</v>
+        <v>-647.7414551988002</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2070851183113212</v>
+        <v>0.211972546138937</v>
       </c>
       <c r="T68">
-        <v>3.724829522201413</v>
+        <v>3.837703144086305</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.0140072621345333</v>
+        <v>0.01379819852058504</v>
       </c>
       <c r="W68">
-        <v>0.2324970875886771</v>
+        <v>0.232546384788846</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.05429171369974151</v>
+        <v>0.05348138961467075</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7287,22 +7287,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.225757018034376</v>
+        <v>0.227657018034376</v>
       </c>
       <c r="C69">
-        <v>-2577.052578281905</v>
+        <v>-2674.552284836349</v>
       </c>
       <c r="D69">
-        <v>2172.780421718095</v>
+        <v>2150.079715163652</v>
       </c>
       <c r="E69">
-        <v>4548.533</v>
+        <v>4623.332</v>
       </c>
       <c r="F69">
-        <v>5011.533</v>
+        <v>5086.332</v>
       </c>
       <c r="G69">
         <v>261.7</v>
@@ -7323,37 +7323,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M69">
-        <v>1181.7194814</v>
+        <v>1199.3570856</v>
       </c>
       <c r="N69">
-        <v>-1118.5194814</v>
+        <v>-1136.1570856</v>
       </c>
       <c r="O69">
-        <v>-288.5780262012</v>
+        <v>-293.1285280848001</v>
       </c>
       <c r="P69">
-        <v>-829.9414551988001</v>
+        <v>-843.0285575152</v>
       </c>
       <c r="Q69">
-        <v>-647.7414551988002</v>
+        <v>-660.8285575151999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.211972546138937</v>
+        <v>0.2171654382057788</v>
       </c>
       <c r="T69">
-        <v>3.837703144086305</v>
+        <v>3.957631367339002</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.01379819852058504</v>
+        <v>0.01359528383645879</v>
       </c>
       <c r="W69">
-        <v>0.232546384788846</v>
+        <v>0.232594232071363</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.05348138961467075</v>
+        <v>0.05269489859092558</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7369,22 +7369,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.227657018034376</v>
+        <v>0.2295570180343761</v>
       </c>
       <c r="C70">
-        <v>-2674.552284836349</v>
+        <v>-2771.582552531642</v>
       </c>
       <c r="D70">
-        <v>2150.079715163652</v>
+        <v>2127.848447468359</v>
       </c>
       <c r="E70">
-        <v>4623.332</v>
+        <v>4698.131</v>
       </c>
       <c r="F70">
-        <v>5086.332</v>
+        <v>5161.131</v>
       </c>
       <c r="G70">
         <v>261.7</v>
@@ -7405,37 +7405,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M70">
-        <v>1199.3570856</v>
+        <v>1216.9946898</v>
       </c>
       <c r="N70">
-        <v>-1136.1570856</v>
+        <v>-1153.7946898</v>
       </c>
       <c r="O70">
-        <v>-293.1285280848001</v>
+        <v>-297.6790299684</v>
       </c>
       <c r="P70">
-        <v>-843.0285575152</v>
+        <v>-856.1156598315999</v>
       </c>
       <c r="Q70">
-        <v>-660.8285575151999</v>
+        <v>-673.9156598315999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2171654382057788</v>
+        <v>0.2226933555672555</v>
       </c>
       <c r="T70">
-        <v>3.957631367339002</v>
+        <v>4.085296895317679</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.01359528383645879</v>
+        <v>0.01339825073737968</v>
       </c>
       <c r="W70">
-        <v>0.232594232071363</v>
+        <v>0.2326406924761259</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.05269489859092558</v>
+        <v>0.05193120440844834</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7451,22 +7451,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2295570180343761</v>
+        <v>0.2314570180343761</v>
       </c>
       <c r="C71">
-        <v>-2771.582552531642</v>
+        <v>-2868.157793974027</v>
       </c>
       <c r="D71">
-        <v>2127.848447468359</v>
+        <v>2106.072206025973</v>
       </c>
       <c r="E71">
-        <v>4698.131</v>
+        <v>4772.93</v>
       </c>
       <c r="F71">
-        <v>5161.131</v>
+        <v>5235.93</v>
       </c>
       <c r="G71">
         <v>261.7</v>
@@ -7487,37 +7487,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M71">
-        <v>1216.9946898</v>
+        <v>1234.632294</v>
       </c>
       <c r="N71">
-        <v>-1153.7946898</v>
+        <v>-1171.432294</v>
       </c>
       <c r="O71">
-        <v>-297.6790299684</v>
+        <v>-302.229531852</v>
       </c>
       <c r="P71">
-        <v>-856.1156598315999</v>
+        <v>-869.2027621480001</v>
       </c>
       <c r="Q71">
-        <v>-673.9156598315999</v>
+        <v>-687.0027621480001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2226933555672555</v>
+        <v>0.2285898007528307</v>
       </c>
       <c r="T71">
-        <v>4.085296895317679</v>
+        <v>4.221473458494936</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.01339825073737968</v>
+        <v>0.01320684715541711</v>
       </c>
       <c r="W71">
-        <v>0.2326406924761259</v>
+        <v>0.2326858254407527</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.05193120440844834</v>
+        <v>0.05118933005975623</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7533,22 +7533,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2314570180343761</v>
+        <v>0.2333570180343761</v>
       </c>
       <c r="C72">
-        <v>-2868.157793974027</v>
+        <v>-2964.291837756371</v>
       </c>
       <c r="D72">
-        <v>2106.072206025973</v>
+        <v>2084.737162243629</v>
       </c>
       <c r="E72">
-        <v>4772.93</v>
+        <v>4847.729</v>
       </c>
       <c r="F72">
-        <v>5235.93</v>
+        <v>5310.729</v>
       </c>
       <c r="G72">
         <v>261.7</v>
@@ -7569,37 +7569,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M72">
-        <v>1234.632294</v>
+        <v>1252.2698982</v>
       </c>
       <c r="N72">
-        <v>-1171.432294</v>
+        <v>-1189.0698982</v>
       </c>
       <c r="O72">
-        <v>-302.229531852</v>
+        <v>-306.7800337356001</v>
       </c>
       <c r="P72">
-        <v>-869.2027621480001</v>
+        <v>-882.2898644644001</v>
       </c>
       <c r="Q72">
-        <v>-687.0027621480001</v>
+        <v>-700.0898644644001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2285898007528307</v>
+        <v>0.2348928973305145</v>
       </c>
       <c r="T72">
-        <v>4.221473458494936</v>
+        <v>4.367041508787865</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.01320684715541711</v>
+        <v>0.01302083522365067</v>
       </c>
       <c r="W72">
-        <v>0.2326858254407527</v>
+        <v>0.2327296870542632</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.05118933005975623</v>
+        <v>0.05046835358004143</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7615,22 +7615,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.233357018034376</v>
+        <v>0.235257018034376</v>
       </c>
       <c r="C73">
-        <v>-2964.29183775637</v>
+        <v>-3059.99795774252</v>
       </c>
       <c r="D73">
-        <v>2084.73716224363</v>
+        <v>2063.830042257479</v>
       </c>
       <c r="E73">
-        <v>4847.728999999999</v>
+        <v>4922.527999999999</v>
       </c>
       <c r="F73">
-        <v>5310.728999999999</v>
+        <v>5385.527999999999</v>
       </c>
       <c r="G73">
         <v>261.7</v>
@@ -7651,37 +7651,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M73">
-        <v>1252.2698982</v>
+        <v>1269.9075024</v>
       </c>
       <c r="N73">
-        <v>-1189.0698982</v>
+        <v>-1206.7075024</v>
       </c>
       <c r="O73">
-        <v>-306.7800337356</v>
+        <v>-311.3305356192</v>
       </c>
       <c r="P73">
-        <v>-882.2898644643999</v>
+        <v>-895.3769667807999</v>
       </c>
       <c r="Q73">
-        <v>-700.0898644643999</v>
+        <v>-713.1769667807998</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2348928973305145</v>
+        <v>0.2416462150923186</v>
       </c>
       <c r="T73">
-        <v>4.367041508787863</v>
+        <v>4.523007276958858</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.01302083522365068</v>
+        <v>0.01283999028998886</v>
       </c>
       <c r="W73">
-        <v>0.2327296870542632</v>
+        <v>0.2327723302896206</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.05046835358004143</v>
+        <v>0.049767404224763</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7697,22 +7697,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.235257018034376</v>
+        <v>0.2371570180343761</v>
       </c>
       <c r="C74">
-        <v>-3059.99795774252</v>
+        <v>-3155.28890060706</v>
       </c>
       <c r="D74">
-        <v>2063.830042257479</v>
+        <v>2043.338099392939</v>
       </c>
       <c r="E74">
-        <v>4922.527999999999</v>
+        <v>4997.326999999999</v>
       </c>
       <c r="F74">
-        <v>5385.527999999999</v>
+        <v>5460.326999999999</v>
       </c>
       <c r="G74">
         <v>261.7</v>
@@ -7733,37 +7733,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M74">
-        <v>1269.9075024</v>
+        <v>1287.5451066</v>
       </c>
       <c r="N74">
-        <v>-1206.7075024</v>
+        <v>-1224.3451066</v>
       </c>
       <c r="O74">
-        <v>-311.3305356192</v>
+        <v>-315.8810375027999</v>
       </c>
       <c r="P74">
-        <v>-895.3769667807999</v>
+        <v>-908.4640690971999</v>
       </c>
       <c r="Q74">
-        <v>-713.1769667807998</v>
+        <v>-726.2640690971998</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2416462150923186</v>
+        <v>0.2488997786142563</v>
       </c>
       <c r="T74">
-        <v>4.523007276958858</v>
+        <v>4.690526064994371</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.01283999028998886</v>
+        <v>0.01266410001204381</v>
       </c>
       <c r="W74">
-        <v>0.2327723302896206</v>
+        <v>0.2328138052171601</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.049767404224763</v>
+        <v>0.04908565896141015</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7779,22 +7779,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2371570180343761</v>
+        <v>0.2390570180343761</v>
       </c>
       <c r="C75">
-        <v>-3155.28890060706</v>
+        <v>-3250.176911750531</v>
       </c>
       <c r="D75">
-        <v>2043.338099392939</v>
+        <v>2023.249088249468</v>
       </c>
       <c r="E75">
-        <v>4997.326999999999</v>
+        <v>5072.125999999999</v>
       </c>
       <c r="F75">
-        <v>5460.326999999999</v>
+        <v>5535.125999999999</v>
       </c>
       <c r="G75">
         <v>261.7</v>
@@ -7815,37 +7815,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M75">
-        <v>1287.5451066</v>
+        <v>1305.1827108</v>
       </c>
       <c r="N75">
-        <v>-1224.3451066</v>
+        <v>-1241.9827108</v>
       </c>
       <c r="O75">
-        <v>-315.8810375027999</v>
+        <v>-320.4315393864</v>
       </c>
       <c r="P75">
-        <v>-908.4640690971999</v>
+        <v>-921.5511714135999</v>
       </c>
       <c r="Q75">
-        <v>-726.2640690971998</v>
+        <v>-739.3511714136</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2488997786142563</v>
+        <v>0.2567113085609584</v>
       </c>
       <c r="T75">
-        <v>4.690526064994371</v>
+        <v>4.870930913648</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.01266410001204381</v>
+        <v>0.01249296352539457</v>
       </c>
       <c r="W75">
-        <v>0.2328138052171601</v>
+        <v>0.232854159200712</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.04908565896141015</v>
+        <v>0.04842233924571537</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7861,22 +7861,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2390570180343761</v>
+        <v>0.2409570180343761</v>
       </c>
       <c r="C76">
-        <v>-3250.176911750531</v>
+        <v>-3344.673759700826</v>
       </c>
       <c r="D76">
-        <v>2023.249088249468</v>
+        <v>2003.551240299173</v>
       </c>
       <c r="E76">
-        <v>5072.125999999999</v>
+        <v>5146.924999999999</v>
       </c>
       <c r="F76">
-        <v>5535.125999999999</v>
+        <v>5609.924999999999</v>
       </c>
       <c r="G76">
         <v>261.7</v>
@@ -7897,37 +7897,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M76">
-        <v>1305.1827108</v>
+        <v>1322.820315</v>
       </c>
       <c r="N76">
-        <v>-1241.9827108</v>
+        <v>-1259.620315</v>
       </c>
       <c r="O76">
-        <v>-320.4315393864</v>
+        <v>-324.98204127</v>
       </c>
       <c r="P76">
-        <v>-921.5511714135999</v>
+        <v>-934.6382737299999</v>
       </c>
       <c r="Q76">
-        <v>-739.3511714136</v>
+        <v>-752.43827373</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2567113085609584</v>
+        <v>0.2651477609033968</v>
       </c>
       <c r="T76">
-        <v>4.870930913648</v>
+        <v>5.065768150193922</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.01249296352539457</v>
+        <v>0.01232639067838931</v>
       </c>
       <c r="W76">
-        <v>0.232854159200712</v>
+        <v>0.2328934370780358</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.04842233924571537</v>
+        <v>0.0477767080557725</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7943,22 +7943,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2409570180343761</v>
+        <v>0.2428570180343761</v>
       </c>
       <c r="C77">
-        <v>-3344.673759700826</v>
+        <v>-3438.790759102931</v>
       </c>
       <c r="D77">
-        <v>2003.551240299173</v>
+        <v>1984.233240897069</v>
       </c>
       <c r="E77">
-        <v>5146.924999999999</v>
+        <v>5221.724</v>
       </c>
       <c r="F77">
-        <v>5609.924999999999</v>
+        <v>5684.724</v>
       </c>
       <c r="G77">
         <v>261.7</v>
@@ -7979,37 +7979,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M77">
-        <v>1322.820315</v>
+        <v>1340.4579192</v>
       </c>
       <c r="N77">
-        <v>-1259.620315</v>
+        <v>-1277.2579192</v>
       </c>
       <c r="O77">
-        <v>-324.98204127</v>
+        <v>-329.5325431536</v>
       </c>
       <c r="P77">
-        <v>-934.6382737299999</v>
+        <v>-947.7253760464</v>
       </c>
       <c r="Q77">
-        <v>-752.43827373</v>
+        <v>-765.5253760464</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2651477609033968</v>
+        <v>0.2742872509410383</v>
       </c>
       <c r="T77">
-        <v>5.065768150193922</v>
+        <v>5.276841823118668</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.01232639067838931</v>
+        <v>0.01216420132735787</v>
       </c>
       <c r="W77">
-        <v>0.2328934370780358</v>
+        <v>0.232931681327009</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.0477767080557725</v>
+        <v>0.04714806716030184</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -8025,22 +8025,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2428570180343761</v>
+        <v>0.2447570180343761</v>
       </c>
       <c r="C78">
-        <v>-3438.790759102931</v>
+        <v>-3532.538792391382</v>
       </c>
       <c r="D78">
-        <v>1984.233240897069</v>
+        <v>1965.284207608618</v>
       </c>
       <c r="E78">
-        <v>5221.724</v>
+        <v>5296.523</v>
       </c>
       <c r="F78">
-        <v>5684.724</v>
+        <v>5759.523</v>
       </c>
       <c r="G78">
         <v>261.7</v>
@@ -8061,37 +8061,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M78">
-        <v>1340.4579192</v>
+        <v>1358.0955234</v>
       </c>
       <c r="N78">
-        <v>-1277.2579192</v>
+        <v>-1294.8955234</v>
       </c>
       <c r="O78">
-        <v>-329.5325431536</v>
+        <v>-334.0830450372</v>
       </c>
       <c r="P78">
-        <v>-947.7253760464</v>
+        <v>-960.8124783628</v>
       </c>
       <c r="Q78">
-        <v>-765.5253760464</v>
+        <v>-778.6124783627999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2742872509410383</v>
+        <v>0.2842214792428226</v>
       </c>
       <c r="T78">
-        <v>5.276841823118668</v>
+        <v>5.506269728471654</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.01216420132735787</v>
+        <v>0.01200622468674283</v>
       </c>
       <c r="W78">
-        <v>0.232931681327009</v>
+        <v>0.2329689322188661</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.04714806716030184</v>
+        <v>0.04653575459977843</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -8107,22 +8107,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2447570180343761</v>
+        <v>0.2466570180343761</v>
       </c>
       <c r="C79">
-        <v>-3532.538792391382</v>
+        <v>-3625.928330232671</v>
       </c>
       <c r="D79">
-        <v>1965.284207608618</v>
+        <v>1946.69366976733</v>
       </c>
       <c r="E79">
-        <v>5296.523</v>
+        <v>5371.322</v>
       </c>
       <c r="F79">
-        <v>5759.523</v>
+        <v>5834.322</v>
       </c>
       <c r="G79">
         <v>261.7</v>
@@ -8143,37 +8143,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M79">
-        <v>1358.0955234</v>
+        <v>1375.7331276</v>
       </c>
       <c r="N79">
-        <v>-1294.8955234</v>
+        <v>-1312.5331276</v>
       </c>
       <c r="O79">
-        <v>-334.0830450372</v>
+        <v>-338.6335469208</v>
       </c>
       <c r="P79">
-        <v>-960.8124783628</v>
+        <v>-973.8995806792</v>
       </c>
       <c r="Q79">
-        <v>-778.6124783627999</v>
+        <v>-791.6995806791999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2842214792428226</v>
+        <v>0.2950588192084055</v>
       </c>
       <c r="T79">
-        <v>5.506269728471654</v>
+        <v>5.756554716129457</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.01200622468674283</v>
+        <v>0.01185229872922049</v>
       </c>
       <c r="W79">
-        <v>0.2329689322188661</v>
+        <v>0.2330052279596498</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.04653575459977843</v>
+        <v>0.04593914236131968</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8189,22 +8189,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2466570180343761</v>
+        <v>0.2485570180343761</v>
       </c>
       <c r="C80">
-        <v>-3625.928330232671</v>
+        <v>-3718.969450818261</v>
       </c>
       <c r="D80">
-        <v>1946.69366976733</v>
+        <v>1928.451549181739</v>
       </c>
       <c r="E80">
-        <v>5371.322</v>
+        <v>5446.121</v>
       </c>
       <c r="F80">
-        <v>5834.322</v>
+        <v>5909.121</v>
       </c>
       <c r="G80">
         <v>261.7</v>
@@ -8225,37 +8225,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M80">
-        <v>1375.7331276</v>
+        <v>1393.3707318</v>
       </c>
       <c r="N80">
-        <v>-1312.5331276</v>
+        <v>-1330.1707318</v>
       </c>
       <c r="O80">
-        <v>-338.6335469208</v>
+        <v>-343.1840488044</v>
       </c>
       <c r="P80">
-        <v>-973.8995806792</v>
+        <v>-986.9866829956001</v>
       </c>
       <c r="Q80">
-        <v>-791.6995806791999</v>
+        <v>-804.7866829956001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2950588192084055</v>
+        <v>0.3069282867897581</v>
       </c>
       <c r="T80">
-        <v>5.756554716129457</v>
+        <v>6.030676369278479</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.01185229872922049</v>
+        <v>0.01170226963138225</v>
       </c>
       <c r="W80">
-        <v>0.2330052279596498</v>
+        <v>0.2330406048209201</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.04593914236131968</v>
+        <v>0.04535763423016381</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8271,22 +8271,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2485570180343761</v>
+        <v>0.2504570180343761</v>
       </c>
       <c r="C81">
-        <v>-3718.969450818261</v>
+        <v>-3811.671858082946</v>
       </c>
       <c r="D81">
-        <v>1928.451549181739</v>
+        <v>1910.548141917055</v>
       </c>
       <c r="E81">
-        <v>5446.121</v>
+        <v>5520.92</v>
       </c>
       <c r="F81">
-        <v>5909.121</v>
+        <v>5983.92</v>
       </c>
       <c r="G81">
         <v>261.7</v>
@@ -8307,37 +8307,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M81">
-        <v>1393.3707318</v>
+        <v>1411.008336</v>
       </c>
       <c r="N81">
-        <v>-1330.1707318</v>
+        <v>-1347.808336</v>
       </c>
       <c r="O81">
-        <v>-343.1840488044</v>
+        <v>-347.734550688</v>
       </c>
       <c r="P81">
-        <v>-986.9866829956001</v>
+        <v>-1000.073785312</v>
       </c>
       <c r="Q81">
-        <v>-804.7866829956001</v>
+        <v>-817.8737853120001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3069282867897581</v>
+        <v>0.319984701129246</v>
       </c>
       <c r="T81">
-        <v>6.030676369278479</v>
+        <v>6.332210187742403</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.01170226963138225</v>
+        <v>0.01155599126098997</v>
       </c>
       <c r="W81">
-        <v>0.2330406048209201</v>
+        <v>0.2330750972606586</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.04535763423016381</v>
+        <v>0.04479066380228669</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8353,22 +8353,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2504570180343761</v>
+        <v>0.252357018034376</v>
       </c>
       <c r="C82">
-        <v>-3811.671858082946</v>
+        <v>-3904.044898917705</v>
       </c>
       <c r="D82">
-        <v>1910.548141917055</v>
+        <v>1892.974101082295</v>
       </c>
       <c r="E82">
-        <v>5520.92</v>
+        <v>5595.719</v>
       </c>
       <c r="F82">
-        <v>5983.92</v>
+        <v>6058.719</v>
       </c>
       <c r="G82">
         <v>261.7</v>
@@ -8389,37 +8389,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M82">
-        <v>1411.008336</v>
+        <v>1428.6459402</v>
       </c>
       <c r="N82">
-        <v>-1347.808336</v>
+        <v>-1365.4459402</v>
       </c>
       <c r="O82">
-        <v>-347.734550688</v>
+        <v>-352.2850525716</v>
       </c>
       <c r="P82">
-        <v>-1000.073785312</v>
+        <v>-1013.1608876284</v>
       </c>
       <c r="Q82">
-        <v>-817.8737853120001</v>
+        <v>-830.9608876283999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.319984701129246</v>
+        <v>0.3344154748728905</v>
       </c>
       <c r="T82">
-        <v>6.332210187742403</v>
+        <v>6.665484408149897</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.01155599126098997</v>
+        <v>0.01141332470221232</v>
       </c>
       <c r="W82">
-        <v>0.2330750972606586</v>
+        <v>0.2331087380352183</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.04479066380228669</v>
+        <v>0.04423769264423383</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8435,22 +8435,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.252357018034376</v>
+        <v>0.2542570180343761</v>
       </c>
       <c r="C83">
-        <v>-3904.044898917705</v>
+        <v>-3996.097579441252</v>
       </c>
       <c r="D83">
-        <v>1892.974101082295</v>
+        <v>1875.720420558747</v>
       </c>
       <c r="E83">
-        <v>5595.719</v>
+        <v>5670.518</v>
       </c>
       <c r="F83">
-        <v>6058.719</v>
+        <v>6133.518</v>
       </c>
       <c r="G83">
         <v>261.7</v>
@@ -8471,37 +8471,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M83">
-        <v>1428.6459402</v>
+        <v>1446.2835444</v>
       </c>
       <c r="N83">
-        <v>-1365.4459402</v>
+        <v>-1383.0835444</v>
       </c>
       <c r="O83">
-        <v>-352.2850525716</v>
+        <v>-356.8355544552</v>
       </c>
       <c r="P83">
-        <v>-1013.1608876284</v>
+        <v>-1026.2479899448</v>
       </c>
       <c r="Q83">
-        <v>-830.9608876283999</v>
+        <v>-844.0479899447998</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3344154748728905</v>
+        <v>0.3504496679213845</v>
       </c>
       <c r="T83">
-        <v>6.665484408149897</v>
+        <v>7.03578909749156</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.01141332470221232</v>
+        <v>0.01127413781559997</v>
       </c>
       <c r="W83">
-        <v>0.2331087380352183</v>
+        <v>0.2331415583030815</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.04423769264423383</v>
+        <v>0.04369820858759677</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8517,22 +8517,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2542570180343761</v>
+        <v>0.2561570180343761</v>
       </c>
       <c r="C84">
-        <v>-3996.097579441252</v>
+        <v>-4087.838580389751</v>
       </c>
       <c r="D84">
-        <v>1875.720420558747</v>
+        <v>1858.778419610249</v>
       </c>
       <c r="E84">
-        <v>5670.518</v>
+        <v>5745.317</v>
       </c>
       <c r="F84">
-        <v>6133.518</v>
+        <v>6208.317</v>
       </c>
       <c r="G84">
         <v>261.7</v>
@@ -8553,37 +8553,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M84">
-        <v>1446.2835444</v>
+        <v>1463.9211486</v>
       </c>
       <c r="N84">
-        <v>-1383.0835444</v>
+        <v>-1400.7211486</v>
       </c>
       <c r="O84">
-        <v>-356.8355544552</v>
+        <v>-361.3860563388</v>
       </c>
       <c r="P84">
-        <v>-1026.2479899448</v>
+        <v>-1039.3350922612</v>
       </c>
       <c r="Q84">
-        <v>-844.0479899447998</v>
+        <v>-857.1350922612</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3504496679213845</v>
+        <v>0.3683702366226425</v>
       </c>
       <c r="T84">
-        <v>7.03578909749156</v>
+        <v>7.449659044402829</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.01127413781559997</v>
+        <v>0.01113830482986985</v>
       </c>
       <c r="W84">
-        <v>0.2331415583030815</v>
+        <v>0.2331735877211167</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.04369820858759677</v>
+        <v>0.04317172414678239</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8599,22 +8599,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2561570180343761</v>
+        <v>0.2580570180343761</v>
       </c>
       <c r="C85">
-        <v>-4087.838580389751</v>
+        <v>-4179.276271679984</v>
       </c>
       <c r="D85">
-        <v>1858.778419610249</v>
+        <v>1842.139728320016</v>
       </c>
       <c r="E85">
-        <v>5745.317</v>
+        <v>5820.116</v>
       </c>
       <c r="F85">
-        <v>6208.317</v>
+        <v>6283.116</v>
       </c>
       <c r="G85">
         <v>261.7</v>
@@ -8635,37 +8635,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M85">
-        <v>1463.9211486</v>
+        <v>1481.5587528</v>
       </c>
       <c r="N85">
-        <v>-1400.7211486</v>
+        <v>-1418.3587528</v>
       </c>
       <c r="O85">
-        <v>-361.3860563388</v>
+        <v>-365.9365582224</v>
       </c>
       <c r="P85">
-        <v>-1039.3350922612</v>
+        <v>-1052.4221945776</v>
       </c>
       <c r="Q85">
-        <v>-857.1350922612</v>
+        <v>-870.2221945776</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3683702366226425</v>
+        <v>0.3885308764115577</v>
       </c>
       <c r="T85">
-        <v>7.449659044402829</v>
+        <v>7.915262734678007</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.01113830482986985</v>
+        <v>0.01100570596284759</v>
       </c>
       <c r="W85">
-        <v>0.2331735877211167</v>
+        <v>0.2332048545339606</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.04317172414678239</v>
+        <v>0.04265777504979684</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8681,22 +8681,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2580570180343761</v>
+        <v>0.259957018034376</v>
       </c>
       <c r="C86">
-        <v>-4179.276271679983</v>
+        <v>-4270.418726197295</v>
       </c>
       <c r="D86">
-        <v>1842.139728320016</v>
+        <v>1825.796273802705</v>
       </c>
       <c r="E86">
-        <v>5820.115999999999</v>
+        <v>5894.915</v>
       </c>
       <c r="F86">
-        <v>6283.115999999999</v>
+        <v>6357.915</v>
       </c>
       <c r="G86">
         <v>261.7</v>
@@ -8717,37 +8717,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M86">
-        <v>1481.5587528</v>
+        <v>1499.196357</v>
       </c>
       <c r="N86">
-        <v>-1418.3587528</v>
+        <v>-1435.996357</v>
       </c>
       <c r="O86">
-        <v>-365.9365582224</v>
+        <v>-370.487060106</v>
       </c>
       <c r="P86">
-        <v>-1052.4221945776</v>
+        <v>-1065.509296894</v>
       </c>
       <c r="Q86">
-        <v>-870.2221945775998</v>
+        <v>-883.309296894</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3885308764115574</v>
+        <v>0.4113796015056613</v>
       </c>
       <c r="T86">
-        <v>7.915262734678</v>
+        <v>8.442946916989868</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.01100570596284759</v>
+        <v>0.01087622706916704</v>
       </c>
       <c r="W86">
-        <v>0.2332048545339606</v>
+        <v>0.2332353856570904</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8755,7 +8755,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.04265777504979695</v>
+        <v>0.04215591887274051</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8763,22 +8763,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.259957018034376</v>
+        <v>0.2618570180343761</v>
       </c>
       <c r="C87">
-        <v>-4270.418726197295</v>
+        <v>-4361.273732856025</v>
       </c>
       <c r="D87">
-        <v>1825.796273802705</v>
+        <v>1809.740267143975</v>
       </c>
       <c r="E87">
-        <v>5894.915</v>
+        <v>5969.714</v>
       </c>
       <c r="F87">
-        <v>6357.915</v>
+        <v>6432.714</v>
       </c>
       <c r="G87">
         <v>261.7</v>
@@ -8799,37 +8799,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M87">
-        <v>1499.196357</v>
+        <v>1516.8339612</v>
       </c>
       <c r="N87">
-        <v>-1435.996357</v>
+        <v>-1453.6339612</v>
       </c>
       <c r="O87">
-        <v>-370.487060106</v>
+        <v>-375.0375619896</v>
       </c>
       <c r="P87">
-        <v>-1065.509296894</v>
+        <v>-1078.5963992104</v>
       </c>
       <c r="Q87">
-        <v>-883.309296894</v>
+        <v>-896.3963992104</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4113796015056613</v>
+        <v>0.437492430184637</v>
       </c>
       <c r="T87">
-        <v>8.442946916989868</v>
+        <v>9.046014553917715</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.01087622706916704</v>
+        <v>0.01074975931254881</v>
       </c>
       <c r="W87">
-        <v>0.2332353856570904</v>
+        <v>0.233265206754101</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.04215591887274051</v>
+        <v>0.04166573376956906</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8845,22 +8845,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2618570180343761</v>
+        <v>0.2637570180343761</v>
       </c>
       <c r="C88">
-        <v>-4361.273732856025</v>
+        <v>-4451.848808976829</v>
       </c>
       <c r="D88">
-        <v>1809.740267143975</v>
+        <v>1793.964191023172</v>
       </c>
       <c r="E88">
-        <v>5969.714</v>
+        <v>6044.513</v>
       </c>
       <c r="F88">
-        <v>6432.714</v>
+        <v>6507.513</v>
       </c>
       <c r="G88">
         <v>261.7</v>
@@ -8881,37 +8881,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M88">
-        <v>1516.8339612</v>
+        <v>1534.4715654</v>
       </c>
       <c r="N88">
-        <v>-1453.6339612</v>
+        <v>-1471.2715654</v>
       </c>
       <c r="O88">
-        <v>-375.0375619896</v>
+        <v>-379.5880638732</v>
       </c>
       <c r="P88">
-        <v>-1078.5963992104</v>
+        <v>-1091.6835015268</v>
       </c>
       <c r="Q88">
-        <v>-896.3963992104</v>
+        <v>-909.4835015268</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.437492430184637</v>
+        <v>0.4676226171219169</v>
       </c>
       <c r="T88">
-        <v>9.046014553917715</v>
+        <v>9.741861827296002</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.01074975931254881</v>
+        <v>0.01062619886068043</v>
       </c>
       <c r="W88">
-        <v>0.233265206754101</v>
+        <v>0.2332943423086516</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8919,7 +8919,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.04166573376956906</v>
+        <v>0.04118681728945905</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8927,22 +8927,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2637570180343761</v>
+        <v>0.265657018034376</v>
       </c>
       <c r="C89">
-        <v>-4451.848808976829</v>
+        <v>-4542.151212022216</v>
       </c>
       <c r="D89">
-        <v>1793.964191023172</v>
+        <v>1778.460787977784</v>
       </c>
       <c r="E89">
-        <v>6044.513</v>
+        <v>6119.312</v>
       </c>
       <c r="F89">
-        <v>6507.513</v>
+        <v>6582.312</v>
       </c>
       <c r="G89">
         <v>261.7</v>
@@ -8963,37 +8963,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M89">
-        <v>1534.4715654</v>
+        <v>1552.1091696</v>
       </c>
       <c r="N89">
-        <v>-1471.2715654</v>
+        <v>-1488.9091696</v>
       </c>
       <c r="O89">
-        <v>-379.5880638732</v>
+        <v>-384.1385657568</v>
       </c>
       <c r="P89">
-        <v>-1091.6835015268</v>
+        <v>-1104.7706038432</v>
       </c>
       <c r="Q89">
-        <v>-909.4835015268</v>
+        <v>-922.5706038431999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4676226171219169</v>
+        <v>0.5027745018820766</v>
       </c>
       <c r="T89">
-        <v>9.741861827296002</v>
+        <v>10.55368364623734</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.01062619886068043</v>
+        <v>0.01050544660089998</v>
       </c>
       <c r="W89">
-        <v>0.2332943423086516</v>
+        <v>0.2333228156915078</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.04118681728945905</v>
+        <v>0.0407187852748061</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -9009,22 +9009,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.265657018034376</v>
+        <v>0.267557018034376</v>
       </c>
       <c r="C90">
-        <v>-4542.151212022216</v>
+        <v>-4632.187950728794</v>
       </c>
       <c r="D90">
-        <v>1778.460787977784</v>
+        <v>1763.223049271206</v>
       </c>
       <c r="E90">
-        <v>6119.312</v>
+        <v>6194.111</v>
       </c>
       <c r="F90">
-        <v>6582.312</v>
+        <v>6657.111</v>
       </c>
       <c r="G90">
         <v>261.7</v>
@@ -9045,37 +9045,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M90">
-        <v>1552.1091696</v>
+        <v>1569.7467738</v>
       </c>
       <c r="N90">
-        <v>-1488.9091696</v>
+        <v>-1506.5467738</v>
       </c>
       <c r="O90">
-        <v>-384.1385657568</v>
+        <v>-388.6890676404</v>
       </c>
       <c r="P90">
-        <v>-1104.7706038432</v>
+        <v>-1117.8577061596</v>
       </c>
       <c r="Q90">
-        <v>-922.5706038431999</v>
+        <v>-935.6577061595999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5027745018820766</v>
+        <v>0.5443176384168109</v>
       </c>
       <c r="T90">
-        <v>10.55368364623734</v>
+        <v>11.51310943225891</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.01050544660089998</v>
+        <v>0.01038740787504717</v>
       </c>
       <c r="W90">
-        <v>0.2333228156915078</v>
+        <v>0.2333506492230639</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.0407187852748061</v>
+        <v>0.04026127083351616</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -9091,22 +9091,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.267557018034376</v>
+        <v>0.2694570180343761</v>
       </c>
       <c r="C91">
-        <v>-4632.187950728794</v>
+        <v>-4721.965795672082</v>
       </c>
       <c r="D91">
-        <v>1763.223049271206</v>
+        <v>1748.244204327917</v>
       </c>
       <c r="E91">
-        <v>6194.111</v>
+        <v>6268.91</v>
       </c>
       <c r="F91">
-        <v>6657.111</v>
+        <v>6731.91</v>
       </c>
       <c r="G91">
         <v>261.7</v>
@@ -9127,37 +9127,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M91">
-        <v>1569.7467738</v>
+        <v>1587.384378</v>
       </c>
       <c r="N91">
-        <v>-1506.5467738</v>
+        <v>-1524.184378</v>
       </c>
       <c r="O91">
-        <v>-388.6890676404</v>
+        <v>-393.239569524</v>
       </c>
       <c r="P91">
-        <v>-1117.8577061596</v>
+        <v>-1130.944808476</v>
       </c>
       <c r="Q91">
-        <v>-935.6577061595999</v>
+        <v>-948.7448084759999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5443176384168109</v>
+        <v>0.594169402258492</v>
       </c>
       <c r="T91">
-        <v>11.51310943225891</v>
+        <v>12.66442037548481</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.01038740787504717</v>
+        <v>0.01027199223199109</v>
       </c>
       <c r="W91">
-        <v>0.2333506492230639</v>
+        <v>0.2333778642316965</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.04026127083351616</v>
+        <v>0.03981392337981049</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9173,22 +9173,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2694570180343761</v>
+        <v>0.2713570180343761</v>
       </c>
       <c r="C92">
-        <v>-4721.965795672082</v>
+        <v>-4811.491289297374</v>
       </c>
       <c r="D92">
-        <v>1748.244204327917</v>
+        <v>1733.517710702625</v>
       </c>
       <c r="E92">
-        <v>6268.91</v>
+        <v>6343.709</v>
       </c>
       <c r="F92">
-        <v>6731.91</v>
+        <v>6806.709</v>
       </c>
       <c r="G92">
         <v>261.7</v>
@@ -9209,37 +9209,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M92">
-        <v>1587.384378</v>
+        <v>1605.0219822</v>
       </c>
       <c r="N92">
-        <v>-1524.184378</v>
+        <v>-1541.8219822</v>
       </c>
       <c r="O92">
-        <v>-393.239569524</v>
+        <v>-397.7900714076</v>
       </c>
       <c r="P92">
-        <v>-1130.944808476</v>
+        <v>-1144.0319107924</v>
       </c>
       <c r="Q92">
-        <v>-948.7448084759999</v>
+        <v>-961.8319107924001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.594169402258492</v>
+        <v>0.655099335842769</v>
       </c>
       <c r="T92">
-        <v>12.66442037548481</v>
+        <v>14.07157819498312</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.01027199223199109</v>
+        <v>0.0101591131964747</v>
       </c>
       <c r="W92">
-        <v>0.2333778642316965</v>
+        <v>0.2334044811082713</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.03981392337981049</v>
+        <v>0.039376407738274</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9255,22 +9255,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2713570180343761</v>
+        <v>0.2732570180343761</v>
       </c>
       <c r="C93">
-        <v>-4811.491289297374</v>
+        <v>-4900.770755447851</v>
       </c>
       <c r="D93">
-        <v>1733.517710702625</v>
+        <v>1719.037244552149</v>
       </c>
       <c r="E93">
-        <v>6343.709</v>
+        <v>6418.508</v>
       </c>
       <c r="F93">
-        <v>6806.709</v>
+        <v>6881.508</v>
       </c>
       <c r="G93">
         <v>261.7</v>
@@ -9291,37 +9291,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M93">
-        <v>1605.0219822</v>
+        <v>1622.6595864</v>
       </c>
       <c r="N93">
-        <v>-1541.8219822</v>
+        <v>-1559.4595864</v>
       </c>
       <c r="O93">
-        <v>-397.7900714076</v>
+        <v>-402.3405732912</v>
       </c>
       <c r="P93">
-        <v>-1144.0319107924</v>
+        <v>-1157.1190131088</v>
       </c>
       <c r="Q93">
-        <v>-961.8319107924001</v>
+        <v>-974.9190131088001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.655099335842769</v>
+        <v>0.7312617528231153</v>
       </c>
       <c r="T93">
-        <v>14.07157819498312</v>
+        <v>15.83052546935601</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0101591131964747</v>
+        <v>0.01004868805303476</v>
       </c>
       <c r="W93">
-        <v>0.2334044811082713</v>
+        <v>0.2334305193570944</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.039376407738274</v>
+        <v>0.03894840330633631</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9337,22 +9337,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2732570180343761</v>
+        <v>0.2751570180343761</v>
       </c>
       <c r="C94">
-        <v>-4900.770755447851</v>
+        <v>-4989.810308419112</v>
       </c>
       <c r="D94">
-        <v>1719.037244552149</v>
+        <v>1704.796691580888</v>
       </c>
       <c r="E94">
-        <v>6418.508</v>
+        <v>6493.307</v>
       </c>
       <c r="F94">
-        <v>6881.508</v>
+        <v>6956.307</v>
       </c>
       <c r="G94">
         <v>261.7</v>
@@ -9373,37 +9373,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M94">
-        <v>1622.6595864</v>
+        <v>1640.2971906</v>
       </c>
       <c r="N94">
-        <v>-1559.4595864</v>
+        <v>-1577.0971906</v>
       </c>
       <c r="O94">
-        <v>-402.3405732912</v>
+        <v>-406.8910751748</v>
       </c>
       <c r="P94">
-        <v>-1157.1190131088</v>
+        <v>-1170.2061154252</v>
       </c>
       <c r="Q94">
-        <v>-974.9190131088001</v>
+        <v>-988.0061154252001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7312617528231153</v>
+        <v>0.8291848603692747</v>
       </c>
       <c r="T94">
-        <v>15.83052546935601</v>
+        <v>18.09202910783545</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.01004868805303476</v>
+        <v>0.009940637643862342</v>
       </c>
       <c r="W94">
-        <v>0.2334305193570944</v>
+        <v>0.2334559976435773</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.03894840330633631</v>
+        <v>0.03852960327078425</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9419,22 +9419,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2751570180343761</v>
+        <v>0.277057018034376</v>
       </c>
       <c r="C95">
-        <v>-4989.810308419112</v>
+        <v>-5078.615861567359</v>
       </c>
       <c r="D95">
-        <v>1704.796691580888</v>
+        <v>1690.790138432641</v>
       </c>
       <c r="E95">
-        <v>6493.307</v>
+        <v>6568.106</v>
       </c>
       <c r="F95">
-        <v>6956.307</v>
+        <v>7031.106</v>
       </c>
       <c r="G95">
         <v>261.7</v>
@@ -9455,37 +9455,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M95">
-        <v>1640.2971906</v>
+        <v>1657.9347948</v>
       </c>
       <c r="N95">
-        <v>-1577.0971906</v>
+        <v>-1594.7347948</v>
       </c>
       <c r="O95">
-        <v>-406.8910751748</v>
+        <v>-411.4415770584</v>
       </c>
       <c r="P95">
-        <v>-1170.2061154252</v>
+        <v>-1183.2932177416</v>
       </c>
       <c r="Q95">
-        <v>-988.0061154252001</v>
+        <v>-1001.0932177416</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8291848603692747</v>
+        <v>0.9597490037641541</v>
       </c>
       <c r="T95">
-        <v>18.09202910783545</v>
+        <v>21.10736729247469</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.009940637643862342</v>
+        <v>0.009834886179565936</v>
       </c>
       <c r="W95">
-        <v>0.2334559976435773</v>
+        <v>0.2334809338388583</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.03852960327078425</v>
+        <v>0.03811971387428659</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9501,22 +9501,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.277057018034376</v>
+        <v>0.2789570180343761</v>
       </c>
       <c r="C96">
-        <v>-5078.615861567359</v>
+        <v>-5167.193135496684</v>
       </c>
       <c r="D96">
-        <v>1690.790138432641</v>
+        <v>1677.011864503316</v>
       </c>
       <c r="E96">
-        <v>6568.106</v>
+        <v>6642.905</v>
       </c>
       <c r="F96">
-        <v>7031.106</v>
+        <v>7105.905</v>
       </c>
       <c r="G96">
         <v>261.7</v>
@@ -9537,37 +9537,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M96">
-        <v>1657.9347948</v>
+        <v>1675.572399</v>
       </c>
       <c r="N96">
-        <v>-1594.7347948</v>
+        <v>-1612.372399</v>
       </c>
       <c r="O96">
-        <v>-411.4415770584</v>
+        <v>-415.992078942</v>
       </c>
       <c r="P96">
-        <v>-1183.2932177416</v>
+        <v>-1196.380320058</v>
       </c>
       <c r="Q96">
-        <v>-1001.0932177416</v>
+        <v>-1014.180320058</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9597490037641541</v>
+        <v>1.142538804516986</v>
       </c>
       <c r="T96">
-        <v>21.10736729247469</v>
+        <v>25.32884075096964</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.009834886179565936</v>
+        <v>0.009731361061886296</v>
       </c>
       <c r="W96">
-        <v>0.2334809338388583</v>
+        <v>0.2335053450616072</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.03811971387428659</v>
+        <v>0.03771845372824145</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9583,22 +9583,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2789570180343761</v>
+        <v>0.2808570180343761</v>
       </c>
       <c r="C97">
-        <v>-5167.193135496684</v>
+        <v>-5255.547665849283</v>
       </c>
       <c r="D97">
-        <v>1677.011864503316</v>
+        <v>1663.456334150718</v>
       </c>
       <c r="E97">
-        <v>6642.905</v>
+        <v>6717.704000000001</v>
       </c>
       <c r="F97">
-        <v>7105.905</v>
+        <v>7180.704000000001</v>
       </c>
       <c r="G97">
         <v>261.7</v>
@@ -9619,37 +9619,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M97">
-        <v>1675.572399</v>
+        <v>1693.2100032</v>
       </c>
       <c r="N97">
-        <v>-1612.372399</v>
+        <v>-1630.0100032</v>
       </c>
       <c r="O97">
-        <v>-415.992078942</v>
+        <v>-420.5425808256001</v>
       </c>
       <c r="P97">
-        <v>-1196.380320058</v>
+        <v>-1209.4674223744</v>
       </c>
       <c r="Q97">
-        <v>-1014.180320058</v>
+        <v>-1027.2674223744</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.142538804516986</v>
+        <v>1.416723505646232</v>
       </c>
       <c r="T97">
-        <v>25.32884075096964</v>
+        <v>31.66105093871207</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.009731361061886296</v>
+        <v>0.009629992717491643</v>
       </c>
       <c r="W97">
-        <v>0.2335053450616072</v>
+        <v>0.2335292477172155</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.03771845372824145</v>
+        <v>0.03732555316857222</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9665,22 +9665,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.280857018034376</v>
+        <v>0.2827570180343761</v>
       </c>
       <c r="C98">
-        <v>-5255.547665849282</v>
+        <v>-5343.684810720888</v>
       </c>
       <c r="D98">
-        <v>1663.456334150718</v>
+        <v>1650.118189279111</v>
       </c>
       <c r="E98">
-        <v>6717.704</v>
+        <v>6792.503</v>
       </c>
       <c r="F98">
-        <v>7180.704</v>
+        <v>7255.503</v>
       </c>
       <c r="G98">
         <v>261.7</v>
@@ -9701,37 +9701,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M98">
-        <v>1693.2100032</v>
+        <v>1710.8476074</v>
       </c>
       <c r="N98">
-        <v>-1630.0100032</v>
+        <v>-1647.6476074</v>
       </c>
       <c r="O98">
-        <v>-420.5425808256</v>
+        <v>-425.0930827092</v>
       </c>
       <c r="P98">
-        <v>-1209.4674223744</v>
+        <v>-1222.5545246908</v>
       </c>
       <c r="Q98">
-        <v>-1027.2674223744</v>
+        <v>-1040.3545246908</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.416723505646229</v>
+        <v>1.873698007528305</v>
       </c>
       <c r="T98">
-        <v>31.66105093871198</v>
+        <v>42.21473458494931</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.009629992717491645</v>
+        <v>0.009530714442053587</v>
       </c>
       <c r="W98">
-        <v>0.2335292477172155</v>
+        <v>0.2335526575345638</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.03732555316857233</v>
+        <v>0.03694075365137051</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9747,22 +9747,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2827570180343761</v>
+        <v>0.284657018034376</v>
       </c>
       <c r="C99">
-        <v>-5343.684810720888</v>
+        <v>-5431.609757722283</v>
       </c>
       <c r="D99">
-        <v>1650.118189279111</v>
+        <v>1636.992242277717</v>
       </c>
       <c r="E99">
-        <v>6792.503</v>
+        <v>6867.302</v>
       </c>
       <c r="F99">
-        <v>7255.503</v>
+        <v>7330.302</v>
       </c>
       <c r="G99">
         <v>261.7</v>
@@ -9783,37 +9783,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M99">
-        <v>1710.8476074</v>
+        <v>1728.4852116</v>
       </c>
       <c r="N99">
-        <v>-1647.6476074</v>
+        <v>-1665.2852116</v>
       </c>
       <c r="O99">
-        <v>-425.0930827092</v>
+        <v>-429.6435845928</v>
       </c>
       <c r="P99">
-        <v>-1222.5545246908</v>
+        <v>-1235.6416270072</v>
       </c>
       <c r="Q99">
-        <v>-1040.3545246908</v>
+        <v>-1053.4416270072</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.873698007528305</v>
+        <v>2.787647011292457</v>
       </c>
       <c r="T99">
-        <v>42.21473458494931</v>
+        <v>63.32210187742396</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.009530714442053587</v>
+        <v>0.009433462253869367</v>
       </c>
       <c r="W99">
-        <v>0.2335526575345638</v>
+        <v>0.2335755896005376</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.03694075365137051</v>
+        <v>0.0365638071855402</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9829,22 +9829,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.284657018034376</v>
+        <v>0.2865570180343761</v>
       </c>
       <c r="C100">
-        <v>-5431.609757722283</v>
+        <v>-5519.327530706435</v>
       </c>
       <c r="D100">
-        <v>1636.992242277717</v>
+        <v>1624.073469293565</v>
       </c>
       <c r="E100">
-        <v>6867.302</v>
+        <v>6942.101</v>
       </c>
       <c r="F100">
-        <v>7330.302</v>
+        <v>7405.101</v>
       </c>
       <c r="G100">
         <v>261.7</v>
@@ -9865,37 +9865,37 @@
         <v>63.20000000000002</v>
       </c>
       <c r="M100">
-        <v>1728.4852116</v>
+        <v>1746.1228158</v>
       </c>
       <c r="N100">
-        <v>-1665.2852116</v>
+        <v>-1682.9228158</v>
       </c>
       <c r="O100">
-        <v>-429.6435845928</v>
+        <v>-434.1940864763999</v>
       </c>
       <c r="P100">
-        <v>-1235.6416270072</v>
+        <v>-1248.7287293236</v>
       </c>
       <c r="Q100">
-        <v>-1053.4416270072</v>
+        <v>-1066.5287293236</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.787647011292457</v>
+        <v>5.529494022584915</v>
       </c>
       <c r="T100">
-        <v>63.32210187742396</v>
+        <v>126.6442037548479</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.009433462253869367</v>
+        <v>0.009338174756355535</v>
       </c>
       <c r="W100">
-        <v>0.2335755896005376</v>
+        <v>0.2335980583924514</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9903,91 +9903,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.0365638071855402</v>
+        <v>0.03619447579982771</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2865570180343761</v>
-      </c>
-      <c r="C101">
-        <v>-5519.327530706435</v>
-      </c>
-      <c r="D101">
-        <v>1624.073469293565</v>
-      </c>
-      <c r="E101">
-        <v>6942.101</v>
-      </c>
-      <c r="F101">
-        <v>7405.101</v>
-      </c>
-      <c r="G101">
-        <v>261.7</v>
-      </c>
-      <c r="H101">
-        <v>7016.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>245.4</v>
-      </c>
-      <c r="K101">
-        <v>182.2</v>
-      </c>
-      <c r="L101">
-        <v>63.20000000000002</v>
-      </c>
-      <c r="M101">
-        <v>1746.1228158</v>
-      </c>
-      <c r="N101">
-        <v>-1682.9228158</v>
-      </c>
-      <c r="O101">
-        <v>-434.1940864763999</v>
-      </c>
-      <c r="P101">
-        <v>-1248.7287293236</v>
-      </c>
-      <c r="Q101">
-        <v>-1066.5287293236</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.529494022584915</v>
-      </c>
-      <c r="T101">
-        <v>126.6442037548479</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.009338174756355535</v>
-      </c>
-      <c r="W101">
-        <v>0.2335980583924514</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.03619447579982771</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
